--- a/AAII_Financials/Quarterly/LAW_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LAW_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="92">
   <si>
     <t>LAW</t>
   </si>
@@ -656,251 +656,263 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:S102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>35700</v>
+      </c>
+      <c r="E8" s="3">
         <v>34900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>34300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>33100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>32500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>34500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>33700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>34500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>33800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>29900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>29500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>21100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>19200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>17900</v>
-      </c>
-      <c r="Q8" s="3">
-        <v>15700</v>
       </c>
       <c r="R8" s="3">
         <v>15700</v>
       </c>
       <c r="S8" s="3">
+        <v>15700</v>
+      </c>
+      <c r="T8" s="3">
         <v>14200</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>8700</v>
+      </c>
+      <c r="E9" s="3">
         <v>8900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>9000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>8300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>8100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>8600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>8500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>9000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>8800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>7800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>8700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>5800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>5300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>5500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>4500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>5100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>4600</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>27000</v>
+      </c>
+      <c r="E10" s="3">
         <v>26000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>25300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>24800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>24400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>25900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>25200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>25500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>25000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>22100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>20800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>15300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>13900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>12400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>11200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>10600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>9600</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -920,61 +932,65 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>10500</v>
+      </c>
+      <c r="E12" s="3">
         <v>12100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>12300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>15300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>16100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>15700</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>15200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>12300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>10600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>9700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>7900</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>6300</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>6000</v>
-      </c>
-      <c r="P12" s="3">
-        <v>6200</v>
       </c>
       <c r="Q12" s="3">
         <v>6200</v>
       </c>
       <c r="R12" s="3">
+        <v>6200</v>
+      </c>
+      <c r="S12" s="3">
         <v>8200</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>6900</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1026,23 +1042,26 @@
       <c r="S13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>10</v>
+      <c r="D14" s="3">
+        <v>0</v>
       </c>
       <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
         <v>1600</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>1000</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="H14" s="3" t="s">
         <v>10</v>
       </c>
@@ -1052,35 +1071,38 @@
       <c r="J14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="N14" s="3">
-        <v>0</v>
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="O14" s="3">
         <v>0</v>
       </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
       <c r="S14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1132,8 +1154,11 @@
       <c r="S15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1150,114 +1175,121 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>43400</v>
+      </c>
+      <c r="E17" s="3">
         <v>37800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>51300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>55400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>52600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>54500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>53700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>46200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>42800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>38900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>32500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>24000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>22100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>20900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>21000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>26900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>22500</v>
       </c>
     </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-7700</v>
+      </c>
+      <c r="E18" s="3">
         <v>-2900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-17000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-22300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-20100</v>
-      </c>
-      <c r="H18" s="3">
-        <v>-20000</v>
       </c>
       <c r="I18" s="3">
         <v>-20000</v>
       </c>
       <c r="J18" s="3">
+        <v>-20000</v>
+      </c>
+      <c r="K18" s="3">
         <v>-11700</v>
-      </c>
-      <c r="K18" s="3">
-        <v>-9000</v>
       </c>
       <c r="L18" s="3">
         <v>-9000</v>
       </c>
       <c r="M18" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="N18" s="3">
         <v>-3000</v>
-      </c>
-      <c r="N18" s="3">
-        <v>-2900</v>
       </c>
       <c r="O18" s="3">
         <v>-2900</v>
       </c>
       <c r="P18" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="Q18" s="3">
         <v>-3000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-5300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-11200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-8300</v>
       </c>
     </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1277,40 +1309,41 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E20" s="3">
         <v>2000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>2100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>2000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>1500</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
       <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
         <v>-200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-100</v>
-      </c>
-      <c r="K20" s="3">
-        <v>-200</v>
       </c>
       <c r="L20" s="3">
         <v>-200</v>
       </c>
       <c r="M20" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="N20" s="3">
         <v>0</v>
@@ -1319,72 +1352,78 @@
         <v>0</v>
       </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-200</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>-100</v>
       </c>
       <c r="R20" s="3">
         <v>-100</v>
       </c>
       <c r="S20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="T20" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="E21" s="3">
         <v>100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-13900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-19400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-17700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-19100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-19400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-11400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-8700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-8800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-2600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-2500</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="P21" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R21" s="3">
         <v>-4700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-10800</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T21" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1436,79 +1475,85 @@
       <c r="S22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-1000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-14900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-20300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-18600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-20000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-20100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-11800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-9100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-9200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-3000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-2900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-3000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-3200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-5500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-11200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-8200</v>
       </c>
     </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="E24" s="3">
         <v>100</v>
       </c>
       <c r="F24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3">
         <v>100</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
       <c r="I24" s="3">
         <v>0</v>
       </c>
@@ -1542,8 +1587,11 @@
       <c r="S24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1595,114 +1643,123 @@
       <c r="S25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="E26" s="3">
         <v>-1000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-14900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-20400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-18700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-20100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-20200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-11800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-9100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-9200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-3100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-2900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-3000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-3200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-5500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-11200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-8200</v>
       </c>
     </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-1000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-14900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-20400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-18700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-20100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-20200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-11800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-9100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-9200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-3100</v>
-      </c>
-      <c r="N27" s="3">
-        <v>-3000</v>
       </c>
       <c r="O27" s="3">
         <v>-3000</v>
       </c>
       <c r="P27" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="Q27" s="3">
         <v>-3200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-5500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-11300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-8200</v>
       </c>
     </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1754,8 +1811,11 @@
       <c r="S28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1807,8 +1867,11 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1860,8 +1923,11 @@
       <c r="S30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1913,40 +1979,43 @@
       <c r="S31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E32" s="3">
         <v>-2000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-2100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-2000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-1500</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
       <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
         <v>200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>100</v>
-      </c>
-      <c r="K32" s="3">
-        <v>200</v>
       </c>
       <c r="L32" s="3">
         <v>200</v>
       </c>
       <c r="M32" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="N32" s="3">
         <v>0</v>
@@ -1955,72 +2024,78 @@
         <v>0</v>
       </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>200</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>100</v>
       </c>
       <c r="R32" s="3">
         <v>100</v>
       </c>
       <c r="S32" s="3">
+        <v>100</v>
+      </c>
+      <c r="T32" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-1000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-14900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-20400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-18700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-20100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-20200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-11800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-9100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-9200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-3100</v>
-      </c>
-      <c r="N33" s="3">
-        <v>-3000</v>
       </c>
       <c r="O33" s="3">
         <v>-3000</v>
       </c>
       <c r="P33" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="Q33" s="3">
         <v>-3200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-5500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-11300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-8200</v>
       </c>
     </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2072,119 +2147,128 @@
       <c r="S34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-1000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-14900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-20400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-18700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-20100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-20200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-11800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-9100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-9200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-3100</v>
-      </c>
-      <c r="N35" s="3">
-        <v>-3000</v>
       </c>
       <c r="O35" s="3">
         <v>-3000</v>
       </c>
       <c r="P35" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="Q35" s="3">
         <v>-3200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-5500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-11300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-8200</v>
       </c>
     </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
     </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2204,8 +2288,9 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T39" s="3"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2225,47 +2310,48 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T40" s="3"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>159600</v>
+      </c>
+      <c r="E41" s="3">
         <v>157700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>178900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>187600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>203200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>213100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>228200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>238600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>255500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>258500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>47000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>53600</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="P41" s="3" t="s">
         <v>10</v>
       </c>
@@ -2278,8 +2364,11 @@
       <c r="S41" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T41" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2331,47 +2420,50 @@
       <c r="S42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>27000</v>
+      </c>
+      <c r="E43" s="3">
         <v>27100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>24600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>23900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>22700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>22200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>24300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>24900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>20700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>23200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>21200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>15000</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="P43" s="3" t="s">
         <v>10</v>
       </c>
@@ -2384,8 +2476,11 @@
       <c r="S43" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T43" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2437,47 +2532,50 @@
       <c r="S44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E45" s="3">
         <v>6300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>3700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>4900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>5600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>6400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>3000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>3700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>4600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>6600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>4300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1400</v>
       </c>
-      <c r="O45" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="P45" s="3" t="s">
         <v>10</v>
       </c>
@@ -2490,47 +2588,50 @@
       <c r="S45" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T45" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>192300</v>
+      </c>
+      <c r="E46" s="3">
         <v>191000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>207200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>216400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>231500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>241800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>255400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>267200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>280900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>288200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>72600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>70000</v>
       </c>
-      <c r="O46" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="P46" s="3" t="s">
         <v>10</v>
       </c>
@@ -2543,8 +2644,11 @@
       <c r="S46" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T46" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2596,8 +2700,11 @@
       <c r="S47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2608,35 +2715,35 @@
         <v>17800</v>
       </c>
       <c r="F48" s="3">
+        <v>17800</v>
+      </c>
+      <c r="G48" s="3">
         <v>17400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>17300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>17800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>18200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>6500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>6200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>6100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>5900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>5600</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="P48" s="3" t="s">
         <v>10</v>
       </c>
@@ -2649,8 +2756,11 @@
       <c r="S48" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T48" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2658,26 +2768,26 @@
         <v>20600</v>
       </c>
       <c r="E49" s="3">
+        <v>20600</v>
+      </c>
+      <c r="F49" s="3">
         <v>6700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>6800</v>
-      </c>
-      <c r="G49" s="3">
-        <v>6900</v>
       </c>
       <c r="H49" s="3">
         <v>6900</v>
       </c>
       <c r="I49" s="3">
+        <v>6900</v>
+      </c>
+      <c r="J49" s="3">
         <v>7000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>7100</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="L49" s="3" t="s">
         <v>10</v>
       </c>
@@ -2690,8 +2800,8 @@
       <c r="O49" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P49" s="3">
-        <v>0</v>
+      <c r="P49" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Q49" s="3">
         <v>0</v>
@@ -2702,8 +2812,11 @@
       <c r="S49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2755,8 +2868,11 @@
       <c r="S50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2808,13 +2924,16 @@
       <c r="S51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="E52" s="3">
         <v>700</v>
@@ -2823,22 +2942,22 @@
         <v>700</v>
       </c>
       <c r="G52" s="3">
+        <v>700</v>
+      </c>
+      <c r="H52" s="3">
         <v>600</v>
-      </c>
-      <c r="H52" s="3">
-        <v>700</v>
       </c>
       <c r="I52" s="3">
         <v>700</v>
       </c>
       <c r="J52" s="3">
-        <v>400</v>
+        <v>700</v>
       </c>
       <c r="K52" s="3">
         <v>400</v>
       </c>
       <c r="L52" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="M52" s="3">
         <v>500</v>
@@ -2846,8 +2965,8 @@
       <c r="N52" s="3">
         <v>500</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>10</v>
+      <c r="O52" s="3">
+        <v>500</v>
       </c>
       <c r="P52" s="3" t="s">
         <v>10</v>
@@ -2861,8 +2980,11 @@
       <c r="S52" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T52" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2914,47 +3036,50 @@
       <c r="S53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>231500</v>
+      </c>
+      <c r="E54" s="3">
         <v>230200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>232400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>241300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>256300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>267200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>281300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>281100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>287400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>294800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>78900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>76200</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="P54" s="3" t="s">
         <v>10</v>
       </c>
@@ -2967,8 +3092,11 @@
       <c r="S54" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T54" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2988,8 +3116,9 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3009,47 +3138,48 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E57" s="3">
         <v>6500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>5100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>6500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>8500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>6800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>8600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>7500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>4700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>8000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>6100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>4300</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="P57" s="3" t="s">
         <v>10</v>
       </c>
@@ -3062,8 +3192,11 @@
       <c r="S57" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T57" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3086,7 +3219,7 @@
         <v>0</v>
       </c>
       <c r="J58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K58" s="3">
         <v>100</v>
@@ -3100,8 +3233,8 @@
       <c r="N58" s="3">
         <v>100</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>10</v>
+      <c r="O58" s="3">
+        <v>100</v>
       </c>
       <c r="P58" s="3" t="s">
         <v>10</v>
@@ -3115,47 +3248,50 @@
       <c r="S58" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T58" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>17800</v>
+      </c>
+      <c r="E59" s="3">
         <v>14600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>14800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>13800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>14200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>15400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>14300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>12000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>13900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>12700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>10200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>7500</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="P59" s="3" t="s">
         <v>10</v>
       </c>
@@ -3168,47 +3304,50 @@
       <c r="S59" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T59" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>23100</v>
+      </c>
+      <c r="E60" s="3">
         <v>21100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>20000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>20400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>22800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>22300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>22900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>19600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>18600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>20700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>16500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>11900</v>
       </c>
-      <c r="O60" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="P60" s="3" t="s">
         <v>10</v>
       </c>
@@ -3221,8 +3360,11 @@
       <c r="S60" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T60" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3245,7 +3387,7 @@
         <v>200</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -3257,11 +3399,11 @@
         <v>0</v>
       </c>
       <c r="N61" s="3">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3">
         <v>100</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
@@ -3274,8 +3416,11 @@
       <c r="S61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3283,38 +3428,38 @@
         <v>7900</v>
       </c>
       <c r="E62" s="3">
+        <v>7900</v>
+      </c>
+      <c r="F62" s="3">
         <v>8400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>8900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>9700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>9900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>10300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>700</v>
-      </c>
-      <c r="K62" s="3">
-        <v>100</v>
       </c>
       <c r="L62" s="3">
         <v>100</v>
       </c>
       <c r="M62" s="3">
+        <v>100</v>
+      </c>
+      <c r="N62" s="3">
         <v>400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>600</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="P62" s="3" t="s">
         <v>10</v>
       </c>
@@ -3327,8 +3472,11 @@
       <c r="S62" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T62" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3380,8 +3528,11 @@
       <c r="S63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3433,8 +3584,11 @@
       <c r="S64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3486,47 +3640,50 @@
       <c r="S65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>31200</v>
+      </c>
+      <c r="E66" s="3">
         <v>29200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>28500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>29500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>32700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>32400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>33500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>20200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>18700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>20800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>16900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>12600</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="P66" s="3" t="s">
         <v>10</v>
       </c>
@@ -3539,8 +3696,11 @@
       <c r="S66" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T66" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3560,8 +3720,9 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T67" s="3"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3613,8 +3774,11 @@
       <c r="S68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3666,8 +3830,11 @@
       <c r="S69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3699,14 +3866,14 @@
         <v>0</v>
       </c>
       <c r="M70" s="3">
+        <v>0</v>
+      </c>
+      <c r="N70" s="3">
         <v>160900</v>
       </c>
-      <c r="N70" s="3">
+      <c r="O70" s="3">
         <v>160800</v>
       </c>
-      <c r="O70" s="3">
-        <v>0</v>
-      </c>
       <c r="P70" s="3">
         <v>0</v>
       </c>
@@ -3719,8 +3886,11 @@
       <c r="S70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3772,47 +3942,50 @@
       <c r="S71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-240400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-234500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-233500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-218600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-198200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-179500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-159500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-139300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-127500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-118400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-109100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-106000</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="P72" s="3" t="s">
         <v>10</v>
       </c>
@@ -3825,8 +3998,11 @@
       <c r="S72" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T72" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3878,8 +4054,11 @@
       <c r="S73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3931,8 +4110,11 @@
       <c r="S74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3984,47 +4166,50 @@
       <c r="S75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>200300</v>
+      </c>
+      <c r="E76" s="3">
         <v>201000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>203900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>211800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>223600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>234800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>247800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>260800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>268700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>274000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-98800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-97200</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="P76" s="3" t="s">
         <v>10</v>
       </c>
@@ -4037,8 +4222,11 @@
       <c r="S76" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T76" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4090,119 +4278,128 @@
       <c r="S77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
     </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-1000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-14900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-20400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-18700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-20100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-20200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-11800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-9100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-9200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-3100</v>
-      </c>
-      <c r="N81" s="3">
-        <v>-3000</v>
       </c>
       <c r="O81" s="3">
         <v>-3000</v>
       </c>
       <c r="P81" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="Q81" s="3">
         <v>-3200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-5500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-11300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-8200</v>
       </c>
     </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4222,8 +4419,9 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4231,25 +4429,25 @@
         <v>1100</v>
       </c>
       <c r="E83" s="3">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="F83" s="3">
         <v>1000</v>
       </c>
       <c r="G83" s="3">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="H83" s="3">
         <v>900</v>
       </c>
       <c r="I83" s="3">
+        <v>900</v>
+      </c>
+      <c r="J83" s="3">
         <v>700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>500</v>
-      </c>
-      <c r="K83" s="3">
-        <v>400</v>
       </c>
       <c r="L83" s="3">
         <v>400</v>
@@ -4260,23 +4458,26 @@
       <c r="N83" s="3">
         <v>400</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>10</v>
+      <c r="O83" s="3">
+        <v>400</v>
       </c>
       <c r="P83" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="Q83" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R83" s="3">
         <v>800</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="S83" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T83" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4328,8 +4529,11 @@
       <c r="S84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4381,8 +4585,11 @@
       <c r="S85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4434,8 +4641,11 @@
       <c r="S86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4487,8 +4697,11 @@
       <c r="S87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4540,61 +4753,67 @@
       <c r="S88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E89" s="3">
         <v>-6900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-7100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-14800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-9400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-14500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-10800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-11400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-2800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-8600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-5700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-4500</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="P89" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="Q89" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R89" s="3">
         <v>-15100</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="S89" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T89" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4614,61 +4833,65 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-15100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-800</v>
-      </c>
-      <c r="L91" s="3">
-        <v>-900</v>
       </c>
       <c r="M91" s="3">
         <v>-900</v>
       </c>
       <c r="N91" s="3">
+        <v>-900</v>
+      </c>
+      <c r="O91" s="3">
         <v>-600</v>
       </c>
-      <c r="O91" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="P91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="Q91" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R91" s="3">
         <v>-1000</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="S91" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T91" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4720,8 +4943,11 @@
       <c r="S92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4773,61 +4999,67 @@
       <c r="S93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-15100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-2000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-5900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-800</v>
-      </c>
-      <c r="L94" s="3">
-        <v>-900</v>
       </c>
       <c r="M94" s="3">
         <v>-900</v>
       </c>
       <c r="N94" s="3">
+        <v>-900</v>
+      </c>
+      <c r="O94" s="3">
         <v>-600</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="P94" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="Q94" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R94" s="3">
         <v>-1000</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="S94" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T94" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4847,8 +5079,9 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4900,8 +5133,11 @@
       <c r="S96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4953,8 +5189,11 @@
       <c r="S97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5006,8 +5245,11 @@
       <c r="S98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5059,61 +5301,67 @@
       <c r="S99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
         <v>700</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
       <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>1200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>221000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>100</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="P100" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="Q100" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R100" s="3">
         <v>16900</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="S100" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T100" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5165,57 +5413,63 @@
       <c r="S101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-21300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-8700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-15600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-9900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-15100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-10400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-16900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-3000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>211500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-6600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-4900</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="P102" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="Q102" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R102" s="3">
         <v>800</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="S102" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="T102" s="3" t="s">
         <v>10</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LAW_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LAW_QTR_FIN.xlsx
@@ -656,263 +656,276 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>35600</v>
+      </c>
+      <c r="E8" s="3">
         <v>35700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>34900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>34300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>33100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>32500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>34500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>33700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>34500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>33800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>29900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>29500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>21100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>19200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>17900</v>
-      </c>
-      <c r="R8" s="3">
-        <v>15700</v>
       </c>
       <c r="S8" s="3">
         <v>15700</v>
       </c>
       <c r="T8" s="3">
+        <v>15700</v>
+      </c>
+      <c r="U8" s="3">
         <v>14200</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>8900</v>
+      </c>
+      <c r="E9" s="3">
         <v>8700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>8900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>9000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>8300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>8100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>8600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>8500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>9000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>8800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>7800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>8700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>5800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>5300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>5500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>4500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>5100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>4600</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>26700</v>
+      </c>
+      <c r="E10" s="3">
         <v>27000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>26000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>25300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>24800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>24400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>25900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>25200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>25500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>25000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>22100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>20800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>15300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>13900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>12400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>11200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>10600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>9600</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -933,64 +946,68 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>12100</v>
+      </c>
+      <c r="E12" s="3">
         <v>10500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>12100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>12300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>15300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>16100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>15700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>15200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>12300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>10600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>9700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>7900</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>6300</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>6000</v>
-      </c>
-      <c r="Q12" s="3">
-        <v>6200</v>
       </c>
       <c r="R12" s="3">
         <v>6200</v>
       </c>
       <c r="S12" s="3">
+        <v>6200</v>
+      </c>
+      <c r="T12" s="3">
         <v>8200</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>6900</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1045,8 +1062,11 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1057,14 +1077,14 @@
         <v>0</v>
       </c>
       <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
         <v>1600</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>1000</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="I14" s="3" t="s">
         <v>10</v>
       </c>
@@ -1074,35 +1094,38 @@
       <c r="K14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
       </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>-1100</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
       <c r="S14" s="3">
         <v>0</v>
       </c>
       <c r="T14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1157,8 +1180,11 @@
       <c r="T15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1176,120 +1202,127 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>47900</v>
+      </c>
+      <c r="E17" s="3">
         <v>43400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>37800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>51300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>55400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>52600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>54500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>53700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>46200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>42800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>38900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>32500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>24000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>22100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>20900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>21000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>26900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>22500</v>
       </c>
     </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-12300</v>
+      </c>
+      <c r="E18" s="3">
         <v>-7700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-2900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-17000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-22300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-20100</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-20000</v>
       </c>
       <c r="J18" s="3">
         <v>-20000</v>
       </c>
       <c r="K18" s="3">
+        <v>-20000</v>
+      </c>
+      <c r="L18" s="3">
         <v>-11700</v>
-      </c>
-      <c r="L18" s="3">
-        <v>-9000</v>
       </c>
       <c r="M18" s="3">
         <v>-9000</v>
       </c>
       <c r="N18" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="O18" s="3">
         <v>-3000</v>
-      </c>
-      <c r="O18" s="3">
-        <v>-2900</v>
       </c>
       <c r="P18" s="3">
         <v>-2900</v>
       </c>
       <c r="Q18" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="R18" s="3">
         <v>-3000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-5300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-11200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-8300</v>
       </c>
     </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1310,43 +1343,44 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E20" s="3">
         <v>2200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>2000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>2100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>2000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>1500</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>-200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-100</v>
-      </c>
-      <c r="L20" s="3">
-        <v>-200</v>
       </c>
       <c r="M20" s="3">
         <v>-200</v>
       </c>
       <c r="N20" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="O20" s="3">
         <v>0</v>
@@ -1355,75 +1389,81 @@
         <v>0</v>
       </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>-200</v>
-      </c>
-      <c r="R20" s="3">
-        <v>-100</v>
       </c>
       <c r="S20" s="3">
         <v>-100</v>
       </c>
       <c r="T20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="U20" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-9400</v>
+      </c>
+      <c r="E21" s="3">
         <v>-4400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-13900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-19400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-17700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-19100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-19400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-11400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-8700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-8800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-2600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-2500</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="R21" s="3">
+      <c r="R21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="S21" s="3">
         <v>-4700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-10800</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U21" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1478,85 +1518,91 @@
       <c r="T22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-10500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-5600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-1000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-14900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-20300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-18600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-20000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-20100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-11800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-9100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-9200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-3000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-2900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-3000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-3200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-5500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-11200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-8200</v>
       </c>
     </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>100</v>
+      </c>
+      <c r="E24" s="3">
         <v>300</v>
-      </c>
-      <c r="E24" s="3">
-        <v>100</v>
       </c>
       <c r="F24" s="3">
         <v>100</v>
       </c>
       <c r="G24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
         <v>100</v>
       </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
       <c r="J24" s="3">
         <v>0</v>
       </c>
@@ -1590,8 +1636,11 @@
       <c r="T24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1646,120 +1695,129 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-10600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-5800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-14900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-20400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-18700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-20100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-20200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-11800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-9100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-9200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-3100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-2900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-3000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-3200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-5500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-11200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-8200</v>
       </c>
     </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-10600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-5800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-14900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-20400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-18700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-20100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-20200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-11800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-9100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-9200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-3100</v>
-      </c>
-      <c r="O27" s="3">
-        <v>-3000</v>
       </c>
       <c r="P27" s="3">
         <v>-3000</v>
       </c>
       <c r="Q27" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="R27" s="3">
         <v>-3200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-5500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-11300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-8200</v>
       </c>
     </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1814,8 +1872,11 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1870,8 +1931,11 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1926,8 +1990,11 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1982,43 +2049,46 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E32" s="3">
         <v>-2200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-2000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-2100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-2000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-1500</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>100</v>
-      </c>
-      <c r="L32" s="3">
-        <v>200</v>
       </c>
       <c r="M32" s="3">
         <v>200</v>
       </c>
       <c r="N32" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="O32" s="3">
         <v>0</v>
@@ -2027,75 +2097,81 @@
         <v>0</v>
       </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>200</v>
-      </c>
-      <c r="R32" s="3">
-        <v>100</v>
       </c>
       <c r="S32" s="3">
         <v>100</v>
       </c>
       <c r="T32" s="3">
+        <v>100</v>
+      </c>
+      <c r="U32" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-10600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-5800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-14900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-20400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-18700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-20100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-20200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-11800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-9100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-9200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-3100</v>
-      </c>
-      <c r="O33" s="3">
-        <v>-3000</v>
       </c>
       <c r="P33" s="3">
         <v>-3000</v>
       </c>
       <c r="Q33" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="R33" s="3">
         <v>-3200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-5500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-11300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-8200</v>
       </c>
     </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2150,125 +2226,134 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-10600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-5800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-14900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-20400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-18700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-20100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-20200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-11800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-9100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-9200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-3100</v>
-      </c>
-      <c r="O35" s="3">
-        <v>-3000</v>
       </c>
       <c r="P35" s="3">
         <v>-3000</v>
       </c>
       <c r="Q35" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="R35" s="3">
         <v>-3200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-5500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-11300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-8200</v>
       </c>
     </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
     </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2289,8 +2374,9 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2311,50 +2397,51 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>148700</v>
+      </c>
+      <c r="E41" s="3">
         <v>159600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>157700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>178900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>187600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>203200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>213100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>228200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>238600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>255500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>258500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>47000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>53600</v>
       </c>
-      <c r="P41" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Q41" s="3" t="s">
         <v>10</v>
       </c>
@@ -2367,8 +2454,11 @@
       <c r="T41" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U41" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2423,50 +2513,53 @@
       <c r="T42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>24500</v>
+      </c>
+      <c r="E43" s="3">
         <v>27000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>27100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>24600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>23900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>22700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>22200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>24300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>24900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>20700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>23200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>21200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>15000</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Q43" s="3" t="s">
         <v>10</v>
       </c>
@@ -2479,8 +2572,11 @@
       <c r="T43" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U43" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2535,50 +2631,53 @@
       <c r="T44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E45" s="3">
         <v>5800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>6300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>3700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>4900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>5600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>6400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>3000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>3700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>4600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>6600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>4300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1400</v>
       </c>
-      <c r="P45" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Q45" s="3" t="s">
         <v>10</v>
       </c>
@@ -2591,50 +2690,53 @@
       <c r="T45" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U45" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>178600</v>
+      </c>
+      <c r="E46" s="3">
         <v>192300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>191000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>207200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>216400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>231500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>241800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>255400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>267200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>280900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>288200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>72600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>70000</v>
       </c>
-      <c r="P46" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Q46" s="3" t="s">
         <v>10</v>
       </c>
@@ -2647,8 +2749,11 @@
       <c r="T46" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U46" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2703,13 +2808,16 @@
       <c r="T47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>17800</v>
+        <v>17400</v>
       </c>
       <c r="E48" s="3">
         <v>17800</v>
@@ -2718,35 +2826,35 @@
         <v>17800</v>
       </c>
       <c r="G48" s="3">
+        <v>17800</v>
+      </c>
+      <c r="H48" s="3">
         <v>17400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>17300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>17800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>18200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>6500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>6200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>6100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>5900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>5600</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Q48" s="3" t="s">
         <v>10</v>
       </c>
@@ -2759,38 +2867,41 @@
       <c r="T48" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U48" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>20600</v>
+        <v>20500</v>
       </c>
       <c r="E49" s="3">
         <v>20600</v>
       </c>
       <c r="F49" s="3">
+        <v>20600</v>
+      </c>
+      <c r="G49" s="3">
         <v>6700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>6800</v>
-      </c>
-      <c r="H49" s="3">
-        <v>6900</v>
       </c>
       <c r="I49" s="3">
         <v>6900</v>
       </c>
       <c r="J49" s="3">
+        <v>6900</v>
+      </c>
+      <c r="K49" s="3">
         <v>7000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>7100</v>
       </c>
-      <c r="L49" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="M49" s="3" t="s">
         <v>10</v>
       </c>
@@ -2803,8 +2914,8 @@
       <c r="P49" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q49" s="3">
-        <v>0</v>
+      <c r="Q49" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="R49" s="3">
         <v>0</v>
@@ -2815,8 +2926,11 @@
       <c r="T49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2871,8 +2985,11 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2927,8 +3044,11 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2936,7 +3056,7 @@
         <v>800</v>
       </c>
       <c r="E52" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="F52" s="3">
         <v>700</v>
@@ -2945,22 +3065,22 @@
         <v>700</v>
       </c>
       <c r="H52" s="3">
+        <v>700</v>
+      </c>
+      <c r="I52" s="3">
         <v>600</v>
-      </c>
-      <c r="I52" s="3">
-        <v>700</v>
       </c>
       <c r="J52" s="3">
         <v>700</v>
       </c>
       <c r="K52" s="3">
-        <v>400</v>
+        <v>700</v>
       </c>
       <c r="L52" s="3">
         <v>400</v>
       </c>
       <c r="M52" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="N52" s="3">
         <v>500</v>
@@ -2968,8 +3088,8 @@
       <c r="O52" s="3">
         <v>500</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>10</v>
+      <c r="P52" s="3">
+        <v>500</v>
       </c>
       <c r="Q52" s="3" t="s">
         <v>10</v>
@@ -2983,8 +3103,11 @@
       <c r="T52" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U52" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3039,50 +3162,53 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>217300</v>
+      </c>
+      <c r="E54" s="3">
         <v>231500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>230200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>232400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>241300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>256300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>267200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>281300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>281100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>287400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>294800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>78900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>76200</v>
       </c>
-      <c r="P54" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Q54" s="3" t="s">
         <v>10</v>
       </c>
@@ -3095,8 +3221,11 @@
       <c r="T54" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U54" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3117,8 +3246,9 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3139,50 +3269,51 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E57" s="3">
         <v>5200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>6500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>5100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>6500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>8500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>6800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>8600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>7500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>4700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>8000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>6100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>4300</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Q57" s="3" t="s">
         <v>10</v>
       </c>
@@ -3195,8 +3326,11 @@
       <c r="T57" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U57" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3222,7 +3356,7 @@
         <v>0</v>
       </c>
       <c r="K58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L58" s="3">
         <v>100</v>
@@ -3236,8 +3370,8 @@
       <c r="O58" s="3">
         <v>100</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>10</v>
+      <c r="P58" s="3">
+        <v>100</v>
       </c>
       <c r="Q58" s="3" t="s">
         <v>10</v>
@@ -3251,50 +3385,53 @@
       <c r="T58" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U58" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E59" s="3">
         <v>17800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>14600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>14800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>13800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>14200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>15400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>14300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>12000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>13900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>12700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>10200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>7500</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Q59" s="3" t="s">
         <v>10</v>
       </c>
@@ -3307,50 +3444,53 @@
       <c r="T59" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U59" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>17000</v>
+      </c>
+      <c r="E60" s="3">
         <v>23100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>21100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>20000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>20400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>22800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>22300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>22900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>19600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>18600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>20700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>16500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>11900</v>
       </c>
-      <c r="P60" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Q60" s="3" t="s">
         <v>10</v>
       </c>
@@ -3363,13 +3503,16 @@
       <c r="T60" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U60" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E61" s="3">
         <v>200</v>
@@ -3390,7 +3533,7 @@
         <v>200</v>
       </c>
       <c r="K61" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="L61" s="3">
         <v>0</v>
@@ -3402,11 +3545,11 @@
         <v>0</v>
       </c>
       <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3">
         <v>100</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -3419,50 +3562,53 @@
       <c r="T61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>7900</v>
+        <v>7000</v>
       </c>
       <c r="E62" s="3">
         <v>7900</v>
       </c>
       <c r="F62" s="3">
+        <v>7900</v>
+      </c>
+      <c r="G62" s="3">
         <v>8400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>8900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>9700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>9900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>10300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>700</v>
-      </c>
-      <c r="L62" s="3">
-        <v>100</v>
       </c>
       <c r="M62" s="3">
         <v>100</v>
       </c>
       <c r="N62" s="3">
+        <v>100</v>
+      </c>
+      <c r="O62" s="3">
         <v>400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>600</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Q62" s="3" t="s">
         <v>10</v>
       </c>
@@ -3475,8 +3621,11 @@
       <c r="T62" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U62" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3531,8 +3680,11 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3587,8 +3739,11 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3643,50 +3798,53 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>24100</v>
+      </c>
+      <c r="E66" s="3">
         <v>31200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>29200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>28500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>29500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>32700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>32400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>33500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>20200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>18700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>20800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>16900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>12600</v>
       </c>
-      <c r="P66" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Q66" s="3" t="s">
         <v>10</v>
       </c>
@@ -3699,8 +3857,11 @@
       <c r="T66" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U66" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3721,8 +3882,9 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3777,8 +3939,11 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3833,8 +3998,11 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3869,14 +4037,14 @@
         <v>0</v>
       </c>
       <c r="N70" s="3">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3">
         <v>160900</v>
       </c>
-      <c r="O70" s="3">
+      <c r="P70" s="3">
         <v>160800</v>
       </c>
-      <c r="P70" s="3">
-        <v>0</v>
-      </c>
       <c r="Q70" s="3">
         <v>0</v>
       </c>
@@ -3889,8 +4057,11 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3945,50 +4116,53 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-251200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-240400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-234500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-233500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-218600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-198200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-179500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-159500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-139300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-127500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-118400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-109100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-106000</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Q72" s="3" t="s">
         <v>10</v>
       </c>
@@ -4001,8 +4175,11 @@
       <c r="T72" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U72" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4057,8 +4234,11 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4113,8 +4293,11 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4169,50 +4352,53 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>193200</v>
+      </c>
+      <c r="E76" s="3">
         <v>200300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>201000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>203900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>211800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>223600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>234800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>247800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>260800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>268700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>274000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-98800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-97200</v>
       </c>
-      <c r="P76" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Q76" s="3" t="s">
         <v>10</v>
       </c>
@@ -4225,8 +4411,11 @@
       <c r="T76" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U76" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4281,125 +4470,134 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
     </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-10600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-5800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-14900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-20400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-18700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-20100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-20200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-11800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-9100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-9200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-3100</v>
-      </c>
-      <c r="O81" s="3">
-        <v>-3000</v>
       </c>
       <c r="P81" s="3">
         <v>-3000</v>
       </c>
       <c r="Q81" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="R81" s="3">
         <v>-3200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-5500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-11300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-8200</v>
       </c>
     </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4420,8 +4618,9 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4432,25 +4631,25 @@
         <v>1100</v>
       </c>
       <c r="F83" s="3">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="G83" s="3">
         <v>1000</v>
       </c>
       <c r="H83" s="3">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="I83" s="3">
         <v>900</v>
       </c>
       <c r="J83" s="3">
+        <v>900</v>
+      </c>
+      <c r="K83" s="3">
         <v>700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>500</v>
-      </c>
-      <c r="L83" s="3">
-        <v>400</v>
       </c>
       <c r="M83" s="3">
         <v>400</v>
@@ -4461,23 +4660,26 @@
       <c r="O83" s="3">
         <v>400</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>10</v>
+      <c r="P83" s="3">
+        <v>400</v>
       </c>
       <c r="Q83" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="R83" s="3">
+      <c r="R83" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="S83" s="3">
         <v>800</v>
       </c>
-      <c r="S83" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="T83" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U83" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4532,8 +4734,11 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4588,8 +4793,11 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4644,8 +4852,11 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4700,8 +4911,11 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4756,64 +4970,70 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-7300</v>
+      </c>
+      <c r="E89" s="3">
         <v>3200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-6900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-7100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-14800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-9400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-14500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-10800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-11400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-2800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-8600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-5700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-4500</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Q89" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="R89" s="3">
+      <c r="R89" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="S89" s="3">
         <v>-15100</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="T89" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U89" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4834,64 +5054,68 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-15100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-800</v>
-      </c>
-      <c r="M91" s="3">
-        <v>-900</v>
       </c>
       <c r="N91" s="3">
         <v>-900</v>
       </c>
       <c r="O91" s="3">
+        <v>-900</v>
+      </c>
+      <c r="P91" s="3">
         <v>-600</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Q91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="R91" s="3">
+      <c r="R91" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="S91" s="3">
         <v>-1000</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="T91" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U91" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4946,8 +5170,11 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5002,64 +5229,70 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-15100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-2000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-5900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-800</v>
-      </c>
-      <c r="M94" s="3">
-        <v>-900</v>
       </c>
       <c r="N94" s="3">
         <v>-900</v>
       </c>
       <c r="O94" s="3">
+        <v>-900</v>
+      </c>
+      <c r="P94" s="3">
         <v>-600</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Q94" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="R94" s="3">
+      <c r="R94" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="S94" s="3">
         <v>-1000</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="T94" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U94" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5080,8 +5313,9 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5136,8 +5370,11 @@
       <c r="T96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5192,8 +5429,11 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5248,8 +5488,11 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5304,64 +5547,70 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>-2900</v>
       </c>
       <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
         <v>700</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>1200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>221000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>100</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Q100" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="R100" s="3">
+      <c r="R100" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="S100" s="3">
         <v>16900</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="T100" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U100" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5416,60 +5665,66 @@
       <c r="T101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-10900</v>
+      </c>
+      <c r="E102" s="3">
         <v>1900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-21300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-8700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-15600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-9900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-15100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-10400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-16900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-3000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>211500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-6600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-4900</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Q102" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="R102" s="3">
+      <c r="R102" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="S102" s="3">
         <v>800</v>
       </c>
-      <c r="S102" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="T102" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="U102" s="3" t="s">
         <v>10</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LAW_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LAW_QTR_FIN.xlsx
@@ -656,217 +656,227 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>36000</v>
+      </c>
+      <c r="E8" s="3">
         <v>35600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>35700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>34900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>34300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>33100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>32500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>34500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>33700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>34500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>33800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>29900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>29500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>21100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>19200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>17900</v>
-      </c>
-      <c r="S8" s="3">
-        <v>15700</v>
       </c>
       <c r="T8" s="3">
         <v>15700</v>
       </c>
       <c r="U8" s="3">
+        <v>15700</v>
+      </c>
+      <c r="V8" s="3">
         <v>14200</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>9300</v>
+      </c>
+      <c r="E9" s="3">
         <v>8900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>8700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>8900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>9000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>8300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>8100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>8600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>8500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>9000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>8800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>7800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>8700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>5800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>5300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>5500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>4500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>5100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>4600</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -874,58 +884,61 @@
         <v>26700</v>
       </c>
       <c r="E10" s="3">
+        <v>26700</v>
+      </c>
+      <c r="F10" s="3">
         <v>27000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>26000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>25300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>24800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>24400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>25900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>25200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>25500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>25000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>22100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>20800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>15300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>13900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>12400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>11200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>10600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>9600</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -947,67 +960,71 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>12900</v>
+      </c>
+      <c r="E12" s="3">
         <v>12100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>10500</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>12100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>12300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>15300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>16100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>15700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>15200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>12300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>10600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>9700</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>7900</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>6300</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>6000</v>
-      </c>
-      <c r="R12" s="3">
-        <v>6200</v>
       </c>
       <c r="S12" s="3">
         <v>6200</v>
       </c>
       <c r="T12" s="3">
+        <v>6200</v>
+      </c>
+      <c r="U12" s="3">
         <v>8200</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>6900</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1065,29 +1082,32 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="E14" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F14" s="3">
         <v>0</v>
       </c>
       <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
         <v>1600</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>1000</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="J14" s="3" t="s">
         <v>10</v>
       </c>
@@ -1097,35 +1117,38 @@
       <c r="L14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
       </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>-1100</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
       <c r="T14" s="3">
         <v>0</v>
       </c>
       <c r="U14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1183,8 +1206,11 @@
       <c r="U15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1203,126 +1229,133 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>48400</v>
+      </c>
+      <c r="E17" s="3">
         <v>47900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>43400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>37800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>51300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>55400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>52600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>54500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>53700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>46200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>42800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>38900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>32500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>24000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>22100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>20900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>21000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>26900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>22500</v>
       </c>
     </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-12400</v>
+      </c>
+      <c r="E18" s="3">
         <v>-12300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-7700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-2900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-17000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-22300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-20100</v>
-      </c>
-      <c r="J18" s="3">
-        <v>-20000</v>
       </c>
       <c r="K18" s="3">
         <v>-20000</v>
       </c>
       <c r="L18" s="3">
+        <v>-20000</v>
+      </c>
+      <c r="M18" s="3">
         <v>-11700</v>
-      </c>
-      <c r="M18" s="3">
-        <v>-9000</v>
       </c>
       <c r="N18" s="3">
         <v>-9000</v>
       </c>
       <c r="O18" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="P18" s="3">
         <v>-3000</v>
-      </c>
-      <c r="P18" s="3">
-        <v>-2900</v>
       </c>
       <c r="Q18" s="3">
         <v>-2900</v>
       </c>
       <c r="R18" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="S18" s="3">
         <v>-3000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-5300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-11200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-8300</v>
       </c>
     </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1344,46 +1377,47 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E20" s="3">
         <v>1800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>2200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>2000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>2100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>2000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>1500</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>-200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-100</v>
-      </c>
-      <c r="M20" s="3">
-        <v>-200</v>
       </c>
       <c r="N20" s="3">
         <v>-200</v>
       </c>
       <c r="O20" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="P20" s="3">
         <v>0</v>
@@ -1392,78 +1426,84 @@
         <v>0</v>
       </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>-200</v>
-      </c>
-      <c r="S20" s="3">
-        <v>-100</v>
       </c>
       <c r="T20" s="3">
         <v>-100</v>
       </c>
       <c r="U20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="V20" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-9700</v>
+      </c>
+      <c r="E21" s="3">
         <v>-9400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-4400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-13900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-19400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-17700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-19100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-19400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-11400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-8700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-8800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-2600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="S21" s="3">
+      <c r="S21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="T21" s="3">
         <v>-4700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-10800</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V21" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1521,67 +1561,73 @@
       <c r="U22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-10700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-10500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-5600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-1000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-14900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-20300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-18600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-20000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-20100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-11800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-9100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-9200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-3000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-2900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-3000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-3200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-5500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-11200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-8200</v>
       </c>
     </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1589,23 +1635,23 @@
         <v>100</v>
       </c>
       <c r="E24" s="3">
+        <v>100</v>
+      </c>
+      <c r="F24" s="3">
         <v>300</v>
-      </c>
-      <c r="F24" s="3">
-        <v>100</v>
       </c>
       <c r="G24" s="3">
         <v>100</v>
       </c>
       <c r="H24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3">
         <v>100</v>
       </c>
-      <c r="J24" s="3">
-        <v>0</v>
-      </c>
       <c r="K24" s="3">
         <v>0</v>
       </c>
@@ -1639,8 +1685,11 @@
       <c r="U24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1698,126 +1747,135 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-10800</v>
+      </c>
+      <c r="E26" s="3">
         <v>-10600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-5800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-1000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-14900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-20400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-18700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-20100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-20200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-11800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-9100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-9200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-3100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-2900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-3000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-3200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-5500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-11200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-8200</v>
       </c>
     </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-10800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-10600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-5800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-1000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-14900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-20400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-18700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-20100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-20200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-11800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-9100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-9200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-3100</v>
-      </c>
-      <c r="P27" s="3">
-        <v>-3000</v>
       </c>
       <c r="Q27" s="3">
         <v>-3000</v>
       </c>
       <c r="R27" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="S27" s="3">
         <v>-3200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-5500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-11300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-8200</v>
       </c>
     </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1875,8 +1933,11 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1934,8 +1995,11 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1993,8 +2057,11 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2052,46 +2119,49 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-2200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-2000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-2100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-2000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-1500</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>100</v>
-      </c>
-      <c r="M32" s="3">
-        <v>200</v>
       </c>
       <c r="N32" s="3">
         <v>200</v>
       </c>
       <c r="O32" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="P32" s="3">
         <v>0</v>
@@ -2100,78 +2170,84 @@
         <v>0</v>
       </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>200</v>
-      </c>
-      <c r="S32" s="3">
-        <v>100</v>
       </c>
       <c r="T32" s="3">
         <v>100</v>
       </c>
       <c r="U32" s="3">
+        <v>100</v>
+      </c>
+      <c r="V32" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-10800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-10600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-5800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-1000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-14900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-20400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-18700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-20100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-20200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-11800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-9100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-9200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-3100</v>
-      </c>
-      <c r="P33" s="3">
-        <v>-3000</v>
       </c>
       <c r="Q33" s="3">
         <v>-3000</v>
       </c>
       <c r="R33" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="S33" s="3">
         <v>-3200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-5500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-11300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-8200</v>
       </c>
     </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2229,131 +2305,140 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-10800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-10600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-5800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-1000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-14900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-20400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-18700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-20100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-20200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-11800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-9100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-9200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-3100</v>
-      </c>
-      <c r="P35" s="3">
-        <v>-3000</v>
       </c>
       <c r="Q35" s="3">
         <v>-3000</v>
       </c>
       <c r="R35" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="S35" s="3">
         <v>-3200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-5500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-11300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-8200</v>
       </c>
     </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
     </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2375,8 +2460,9 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2398,53 +2484,54 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>130000</v>
+      </c>
+      <c r="E41" s="3">
         <v>148700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>159600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>157700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>178900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>187600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>203200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>213100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>228200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>238600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>255500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>258500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>47000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>53600</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="R41" s="3" t="s">
         <v>10</v>
       </c>
@@ -2457,8 +2544,11 @@
       <c r="U41" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V41" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2516,53 +2606,56 @@
       <c r="U42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>25300</v>
+      </c>
+      <c r="E43" s="3">
         <v>24500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>27000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>27100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>24600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>23900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>22700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>22200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>24300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>24900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>20700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>23200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>21200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>15000</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="R43" s="3" t="s">
         <v>10</v>
       </c>
@@ -2575,8 +2668,11 @@
       <c r="U43" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V43" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2634,53 +2730,56 @@
       <c r="U44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E45" s="3">
         <v>5400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>5800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>6300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>3700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>4900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>5600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>6400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>3000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>3700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>4600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>6600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>4300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1400</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="R45" s="3" t="s">
         <v>10</v>
       </c>
@@ -2693,53 +2792,56 @@
       <c r="U45" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V45" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>160200</v>
+      </c>
+      <c r="E46" s="3">
         <v>178600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>192300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>191000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>207200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>216400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>231500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>241800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>255400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>267200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>280900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>288200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>72600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>70000</v>
       </c>
-      <c r="Q46" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="R46" s="3" t="s">
         <v>10</v>
       </c>
@@ -2752,8 +2854,11 @@
       <c r="U46" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V46" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2811,16 +2916,19 @@
       <c r="U47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>16600</v>
+      </c>
+      <c r="E48" s="3">
         <v>17400</v>
-      </c>
-      <c r="E48" s="3">
-        <v>17800</v>
       </c>
       <c r="F48" s="3">
         <v>17800</v>
@@ -2829,35 +2937,35 @@
         <v>17800</v>
       </c>
       <c r="H48" s="3">
+        <v>17800</v>
+      </c>
+      <c r="I48" s="3">
         <v>17400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>17300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>17800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>18200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>6500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>6200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>6100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>5900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>5600</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="R48" s="3" t="s">
         <v>10</v>
       </c>
@@ -2870,41 +2978,44 @@
       <c r="U48" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V48" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>20400</v>
+      </c>
+      <c r="E49" s="3">
         <v>20500</v>
-      </c>
-      <c r="E49" s="3">
-        <v>20600</v>
       </c>
       <c r="F49" s="3">
         <v>20600</v>
       </c>
       <c r="G49" s="3">
+        <v>20600</v>
+      </c>
+      <c r="H49" s="3">
         <v>6700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>6800</v>
-      </c>
-      <c r="I49" s="3">
-        <v>6900</v>
       </c>
       <c r="J49" s="3">
         <v>6900</v>
       </c>
       <c r="K49" s="3">
+        <v>6900</v>
+      </c>
+      <c r="L49" s="3">
         <v>7000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>7100</v>
       </c>
-      <c r="M49" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="N49" s="3" t="s">
         <v>10</v>
       </c>
@@ -2917,8 +3028,8 @@
       <c r="Q49" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="R49" s="3">
-        <v>0</v>
+      <c r="R49" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="S49" s="3">
         <v>0</v>
@@ -2929,8 +3040,11 @@
       <c r="U49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2988,8 +3102,11 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3047,8 +3164,11 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3059,7 +3179,7 @@
         <v>800</v>
       </c>
       <c r="F52" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="G52" s="3">
         <v>700</v>
@@ -3068,22 +3188,22 @@
         <v>700</v>
       </c>
       <c r="I52" s="3">
+        <v>700</v>
+      </c>
+      <c r="J52" s="3">
         <v>600</v>
-      </c>
-      <c r="J52" s="3">
-        <v>700</v>
       </c>
       <c r="K52" s="3">
         <v>700</v>
       </c>
       <c r="L52" s="3">
-        <v>400</v>
+        <v>700</v>
       </c>
       <c r="M52" s="3">
         <v>400</v>
       </c>
       <c r="N52" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="O52" s="3">
         <v>500</v>
@@ -3091,8 +3211,8 @@
       <c r="P52" s="3">
         <v>500</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>10</v>
+      <c r="Q52" s="3">
+        <v>500</v>
       </c>
       <c r="R52" s="3" t="s">
         <v>10</v>
@@ -3106,8 +3226,11 @@
       <c r="U52" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V52" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3165,53 +3288,56 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>198000</v>
+      </c>
+      <c r="E54" s="3">
         <v>217300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>231500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>230200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>232400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>241300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>256300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>267200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>281300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>281100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>287400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>294800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>78900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>76200</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="R54" s="3" t="s">
         <v>10</v>
       </c>
@@ -3224,8 +3350,11 @@
       <c r="U54" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V54" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3247,8 +3376,9 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3270,53 +3400,54 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E57" s="3">
         <v>2000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>5200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>6500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>5100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>6500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>8500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>6800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>8600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>7500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>4700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>8000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>6100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>4300</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="R57" s="3" t="s">
         <v>10</v>
       </c>
@@ -3329,8 +3460,11 @@
       <c r="U57" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V57" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3359,7 +3493,7 @@
         <v>0</v>
       </c>
       <c r="L58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M58" s="3">
         <v>100</v>
@@ -3373,8 +3507,8 @@
       <c r="P58" s="3">
         <v>100</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>10</v>
+      <c r="Q58" s="3">
+        <v>100</v>
       </c>
       <c r="R58" s="3" t="s">
         <v>10</v>
@@ -3388,53 +3522,56 @@
       <c r="U58" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V58" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>16400</v>
+      </c>
+      <c r="E59" s="3">
         <v>15000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>17800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>14600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>14800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>13800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>14200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>15400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>14300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>12000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>13900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>12700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>10200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>7500</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="R59" s="3" t="s">
         <v>10</v>
       </c>
@@ -3447,53 +3584,56 @@
       <c r="U59" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V59" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>20500</v>
+      </c>
+      <c r="E60" s="3">
         <v>17000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>23100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>21100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>20000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>20400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>22800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>22300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>22900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>19600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>18600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>20700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>16500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>11900</v>
       </c>
-      <c r="Q60" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="R60" s="3" t="s">
         <v>10</v>
       </c>
@@ -3506,8 +3646,11 @@
       <c r="U60" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V60" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3515,7 +3658,7 @@
         <v>100</v>
       </c>
       <c r="E61" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F61" s="3">
         <v>200</v>
@@ -3536,7 +3679,7 @@
         <v>200</v>
       </c>
       <c r="L61" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="M61" s="3">
         <v>0</v>
@@ -3548,11 +3691,11 @@
         <v>0</v>
       </c>
       <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3">
         <v>100</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
@@ -3565,53 +3708,56 @@
       <c r="U61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E62" s="3">
         <v>7000</v>
-      </c>
-      <c r="E62" s="3">
-        <v>7900</v>
       </c>
       <c r="F62" s="3">
         <v>7900</v>
       </c>
       <c r="G62" s="3">
+        <v>7900</v>
+      </c>
+      <c r="H62" s="3">
         <v>8400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>8900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>9700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>9900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>10300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>700</v>
-      </c>
-      <c r="M62" s="3">
-        <v>100</v>
       </c>
       <c r="N62" s="3">
         <v>100</v>
       </c>
       <c r="O62" s="3">
+        <v>100</v>
+      </c>
+      <c r="P62" s="3">
         <v>400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>600</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="R62" s="3" t="s">
         <v>10</v>
       </c>
@@ -3624,8 +3770,11 @@
       <c r="U62" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V62" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3683,8 +3832,11 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3742,8 +3894,11 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3801,53 +3956,56 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>27100</v>
+      </c>
+      <c r="E66" s="3">
         <v>24100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>31200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>29200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>28500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>29500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>32700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>32400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>33500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>20200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>18700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>20800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>16900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>12600</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="R66" s="3" t="s">
         <v>10</v>
       </c>
@@ -3860,8 +4018,11 @@
       <c r="U66" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V66" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3883,8 +4044,9 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3942,8 +4104,11 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4001,8 +4166,11 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4040,14 +4208,14 @@
         <v>0</v>
       </c>
       <c r="O70" s="3">
+        <v>0</v>
+      </c>
+      <c r="P70" s="3">
         <v>160900</v>
       </c>
-      <c r="P70" s="3">
+      <c r="Q70" s="3">
         <v>160800</v>
       </c>
-      <c r="Q70" s="3">
-        <v>0</v>
-      </c>
       <c r="R70" s="3">
         <v>0</v>
       </c>
@@ -4060,8 +4228,11 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4119,53 +4290,56 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-263100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-251200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-240400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-234500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-233500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-218600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-198200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-179500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-159500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-139300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-127500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-118400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-109100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-106000</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="R72" s="3" t="s">
         <v>10</v>
       </c>
@@ -4178,8 +4352,11 @@
       <c r="U72" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V72" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4237,8 +4414,11 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4296,8 +4476,11 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4355,53 +4538,56 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>170900</v>
+      </c>
+      <c r="E76" s="3">
         <v>193200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>200300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>201000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>203900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>211800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>223600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>234800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>247800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>260800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>268700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>274000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-98800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-97200</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="R76" s="3" t="s">
         <v>10</v>
       </c>
@@ -4414,8 +4600,11 @@
       <c r="U76" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V76" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4473,131 +4662,140 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
     </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-10800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-10600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-5800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-1000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-14900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-20400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-18700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-20100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-20200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-11800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-9100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-9200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-3100</v>
-      </c>
-      <c r="P81" s="3">
-        <v>-3000</v>
       </c>
       <c r="Q81" s="3">
         <v>-3000</v>
       </c>
       <c r="R81" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="S81" s="3">
         <v>-3200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-5500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-11300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-8200</v>
       </c>
     </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4619,13 +4817,14 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="E83" s="3">
         <v>1100</v>
@@ -4634,25 +4833,25 @@
         <v>1100</v>
       </c>
       <c r="G83" s="3">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="H83" s="3">
         <v>1000</v>
       </c>
       <c r="I83" s="3">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="J83" s="3">
         <v>900</v>
       </c>
       <c r="K83" s="3">
+        <v>900</v>
+      </c>
+      <c r="L83" s="3">
         <v>700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>500</v>
-      </c>
-      <c r="M83" s="3">
-        <v>400</v>
       </c>
       <c r="N83" s="3">
         <v>400</v>
@@ -4663,23 +4862,26 @@
       <c r="P83" s="3">
         <v>400</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>10</v>
+      <c r="Q83" s="3">
+        <v>400</v>
       </c>
       <c r="R83" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="S83" s="3">
+      <c r="S83" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="T83" s="3">
         <v>800</v>
       </c>
-      <c r="T83" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="U83" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V83" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4737,8 +4939,11 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4796,8 +5001,11 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4855,8 +5063,11 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4914,8 +5125,11 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4973,67 +5187,73 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E89" s="3">
         <v>-7300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>3200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-6900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-7100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-14800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-9400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-14500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-10800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-11400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-2800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-8600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-5700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-4500</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="R89" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="S89" s="3">
+      <c r="S89" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="T89" s="3">
         <v>-15100</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="U89" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V89" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5055,8 +5275,9 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5064,58 +5285,61 @@
         <v>-700</v>
       </c>
       <c r="E91" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F91" s="3">
         <v>-1300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-15100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-800</v>
-      </c>
-      <c r="N91" s="3">
-        <v>-900</v>
       </c>
       <c r="O91" s="3">
         <v>-900</v>
       </c>
       <c r="P91" s="3">
+        <v>-900</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-600</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="R91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="S91" s="3">
+      <c r="S91" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="T91" s="3">
         <v>-1000</v>
       </c>
-      <c r="T91" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="U91" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V91" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5173,8 +5397,11 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5232,8 +5459,11 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -5241,58 +5471,61 @@
         <v>-700</v>
       </c>
       <c r="E94" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F94" s="3">
         <v>-1300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-15100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-2000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-5900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-800</v>
-      </c>
-      <c r="N94" s="3">
-        <v>-900</v>
       </c>
       <c r="O94" s="3">
         <v>-900</v>
       </c>
       <c r="P94" s="3">
+        <v>-900</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-600</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="R94" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="S94" s="3">
+      <c r="S94" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="T94" s="3">
         <v>-1000</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="U94" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V94" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5314,8 +5547,9 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5373,8 +5607,11 @@
       <c r="U96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5432,8 +5669,11 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5491,8 +5731,11 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5550,67 +5793,73 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-17400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-2900</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
       <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>700</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
       <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>1200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>221000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>100</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="R100" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="S100" s="3">
+      <c r="S100" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="T100" s="3">
         <v>16900</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="U100" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V100" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5668,63 +5917,69 @@
       <c r="U101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-18700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-10900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-21300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-8700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-15600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-9900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-15100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-10400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-16900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-3000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>211500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-6600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-4900</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="R102" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="S102" s="3">
+      <c r="S102" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="T102" s="3">
         <v>800</v>
       </c>
-      <c r="T102" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="U102" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="V102" s="3" t="s">
         <v>10</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LAW_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LAW_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="92">
   <si>
     <t>LAW</t>
   </si>
@@ -656,289 +656,302 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>36300</v>
+      </c>
+      <c r="E8" s="3">
         <v>36000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>35600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>35700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>34900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>34300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>33100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>32500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>34500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>33700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>34500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>33800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>29900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>29500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>21100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>19200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>17900</v>
-      </c>
-      <c r="T8" s="3">
-        <v>15700</v>
       </c>
       <c r="U8" s="3">
         <v>15700</v>
       </c>
       <c r="V8" s="3">
+        <v>15700</v>
+      </c>
+      <c r="W8" s="3">
         <v>14200</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>9700</v>
+      </c>
+      <c r="E9" s="3">
         <v>9300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>8900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>8700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>8900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>9000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>8300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>8100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>8600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>8500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>9000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>8800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>7800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>8700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>5800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>5300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>5500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>4500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>5100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>4600</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>26700</v>
+        <v>26500</v>
       </c>
       <c r="E10" s="3">
         <v>26700</v>
       </c>
       <c r="F10" s="3">
+        <v>26700</v>
+      </c>
+      <c r="G10" s="3">
         <v>27000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>26000</v>
       </c>
-      <c r="H10" s="3">
-        <v>25300</v>
-      </c>
       <c r="I10" s="3">
-        <v>24800</v>
+        <v>25200</v>
       </c>
       <c r="J10" s="3">
+        <v>24900</v>
+      </c>
+      <c r="K10" s="3">
         <v>24400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>25900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>25200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>25500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>25000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>22100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>20800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>15300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>13900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>12400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>11200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>10600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>9600</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -961,70 +974,74 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>12800</v>
+      </c>
+      <c r="E12" s="3">
         <v>12900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>12100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>10500</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>12100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>12300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>15300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>16100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>15700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>15200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>12300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>10600</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>9700</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>7900</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>6300</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>6000</v>
-      </c>
-      <c r="S12" s="3">
-        <v>6200</v>
       </c>
       <c r="T12" s="3">
         <v>6200</v>
       </c>
       <c r="U12" s="3">
+        <v>6200</v>
+      </c>
+      <c r="V12" s="3">
         <v>8200</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>6900</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1085,32 +1102,35 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>100</v>
+      </c>
+      <c r="E14" s="3">
         <v>400</v>
       </c>
-      <c r="E14" s="3">
-        <v>200</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
+      <c r="F14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
+        <v>8200</v>
       </c>
       <c r="H14" s="3">
+        <v>-7700</v>
+      </c>
+      <c r="I14" s="3">
         <v>1600</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>1000</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>10</v>
       </c>
@@ -1120,58 +1140,61 @@
       <c r="M14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
+      <c r="N14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="O14" s="3">
         <v>0</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>-1100</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
       <c r="U14" s="3">
         <v>0</v>
       </c>
       <c r="V14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1209,8 +1232,11 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1230,132 +1256,139 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>48400</v>
+        <v>47000</v>
       </c>
       <c r="E17" s="3">
+        <v>48000</v>
+      </c>
+      <c r="F17" s="3">
         <v>47900</v>
       </c>
-      <c r="F17" s="3">
-        <v>43400</v>
-      </c>
       <c r="G17" s="3">
-        <v>37800</v>
+        <v>35200</v>
       </c>
       <c r="H17" s="3">
-        <v>51300</v>
+        <v>45500</v>
       </c>
       <c r="I17" s="3">
-        <v>55400</v>
+        <v>49700</v>
       </c>
       <c r="J17" s="3">
+        <v>54400</v>
+      </c>
+      <c r="K17" s="3">
         <v>52600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>54500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>53700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>46200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>42800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>38900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>32500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>24000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>22100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>20900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>21000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>26900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>22500</v>
       </c>
     </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-12400</v>
+        <v>-10700</v>
       </c>
       <c r="E18" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="F18" s="3">
         <v>-12300</v>
       </c>
-      <c r="F18" s="3">
-        <v>-7700</v>
-      </c>
       <c r="G18" s="3">
-        <v>-2900</v>
+        <v>500</v>
       </c>
       <c r="H18" s="3">
-        <v>-17000</v>
+        <v>-10600</v>
       </c>
       <c r="I18" s="3">
-        <v>-22300</v>
+        <v>-15400</v>
       </c>
       <c r="J18" s="3">
+        <v>-21300</v>
+      </c>
+      <c r="K18" s="3">
         <v>-20100</v>
-      </c>
-      <c r="K18" s="3">
-        <v>-20000</v>
       </c>
       <c r="L18" s="3">
         <v>-20000</v>
       </c>
       <c r="M18" s="3">
+        <v>-20000</v>
+      </c>
+      <c r="N18" s="3">
         <v>-11700</v>
-      </c>
-      <c r="N18" s="3">
-        <v>-9000</v>
       </c>
       <c r="O18" s="3">
         <v>-9000</v>
       </c>
       <c r="P18" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="Q18" s="3">
         <v>-3000</v>
-      </c>
-      <c r="Q18" s="3">
-        <v>-2900</v>
       </c>
       <c r="R18" s="3">
         <v>-2900</v>
       </c>
       <c r="S18" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="T18" s="3">
         <v>-3000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-5300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-11200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-8300</v>
       </c>
     </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1378,49 +1411,50 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>1700</v>
-      </c>
-      <c r="E20" s="3">
-        <v>1800</v>
-      </c>
-      <c r="F20" s="3">
-        <v>2200</v>
-      </c>
-      <c r="G20" s="3">
-        <v>2000</v>
-      </c>
-      <c r="H20" s="3">
-        <v>2100</v>
+        <v>-200</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="I20" s="3">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>1500</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>-200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-100</v>
-      </c>
-      <c r="N20" s="3">
-        <v>-200</v>
       </c>
       <c r="O20" s="3">
         <v>-200</v>
       </c>
       <c r="P20" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="Q20" s="3">
         <v>0</v>
@@ -1429,104 +1463,110 @@
         <v>0</v>
       </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>-200</v>
-      </c>
-      <c r="T20" s="3">
-        <v>-100</v>
       </c>
       <c r="U20" s="3">
         <v>-100</v>
       </c>
       <c r="V20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="W20" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-9700</v>
+        <v>-9600</v>
       </c>
       <c r="E21" s="3">
-        <v>-9400</v>
+        <v>-11000</v>
       </c>
       <c r="F21" s="3">
-        <v>-4400</v>
+        <v>-11300</v>
       </c>
       <c r="G21" s="3">
-        <v>100</v>
+        <v>1100</v>
       </c>
       <c r="H21" s="3">
-        <v>-13900</v>
+        <v>-9500</v>
       </c>
       <c r="I21" s="3">
+        <v>-14400</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-20300</v>
+      </c>
+      <c r="K21" s="3">
+        <v>-17700</v>
+      </c>
+      <c r="L21" s="3">
+        <v>-19100</v>
+      </c>
+      <c r="M21" s="3">
         <v>-19400</v>
       </c>
-      <c r="J21" s="3">
-        <v>-17700</v>
-      </c>
-      <c r="K21" s="3">
-        <v>-19100</v>
-      </c>
-      <c r="L21" s="3">
-        <v>-19400</v>
-      </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-11400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-8700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-8800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-2500</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="S21" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="T21" s="3">
+      <c r="T21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="U21" s="3">
         <v>-4700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-10800</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W21" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="E22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F22" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G22" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+        <v>300</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1564,70 +1604,76 @@
       <c r="V22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-10700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-10500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-5600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-1000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-14900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-20300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-18600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-20000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-20100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-11800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-9100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-9200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-3000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-2900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-3000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-3200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-5500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-11200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-8200</v>
       </c>
     </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1638,23 +1684,23 @@
         <v>100</v>
       </c>
       <c r="F24" s="3">
+        <v>100</v>
+      </c>
+      <c r="G24" s="3">
         <v>300</v>
-      </c>
-      <c r="G24" s="3">
-        <v>100</v>
       </c>
       <c r="H24" s="3">
         <v>100</v>
       </c>
       <c r="I24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J24" s="3">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3">
         <v>100</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
       <c r="L24" s="3">
         <v>0</v>
       </c>
@@ -1688,8 +1734,11 @@
       <c r="V24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1750,132 +1799,141 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-10800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-10600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-5800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-1000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-14900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-20400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-18700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-20100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-20200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-11800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-9100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-9200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-3100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-2900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-3000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-3200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-5500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-11200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-8200</v>
       </c>
     </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-10800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-10600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-5800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-1000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-14900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-20400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-18700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-20100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-20200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-11800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-9100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-9200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-3100</v>
-      </c>
-      <c r="Q27" s="3">
-        <v>-3000</v>
       </c>
       <c r="R27" s="3">
         <v>-3000</v>
       </c>
       <c r="S27" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="T27" s="3">
         <v>-3200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-5500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-11300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-8200</v>
       </c>
     </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1936,8 +1994,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1998,8 +2059,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2060,8 +2124,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2122,49 +2189,52 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="E32" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="F32" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-2000</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-2100</v>
+        <v>200</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="I32" s="3">
-        <v>-2000</v>
+        <v>0</v>
       </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>-1500</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>100</v>
-      </c>
-      <c r="N32" s="3">
-        <v>200</v>
       </c>
       <c r="O32" s="3">
         <v>200</v>
       </c>
       <c r="P32" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="Q32" s="3">
         <v>0</v>
@@ -2173,81 +2243,87 @@
         <v>0</v>
       </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>200</v>
-      </c>
-      <c r="T32" s="3">
-        <v>100</v>
       </c>
       <c r="U32" s="3">
         <v>100</v>
       </c>
       <c r="V32" s="3">
+        <v>100</v>
+      </c>
+      <c r="W32" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-10800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-10600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-5800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-1000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-14900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-20400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-18700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-20100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-20200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-11800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-9100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-9200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-3100</v>
-      </c>
-      <c r="Q33" s="3">
-        <v>-3000</v>
       </c>
       <c r="R33" s="3">
         <v>-3000</v>
       </c>
       <c r="S33" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="T33" s="3">
         <v>-3200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-5500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-11300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-8200</v>
       </c>
     </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2308,137 +2384,146 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-10800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-10600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-5800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-1000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-14900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-20400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-18700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-20100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-20200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-11800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-9100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-9200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-3100</v>
-      </c>
-      <c r="Q35" s="3">
-        <v>-3000</v>
       </c>
       <c r="R35" s="3">
         <v>-3000</v>
       </c>
       <c r="S35" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="T35" s="3">
         <v>-3200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-5500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-11300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-8200</v>
       </c>
     </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
     </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2461,8 +2546,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2485,56 +2571,57 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>76500</v>
+      </c>
+      <c r="E41" s="3">
         <v>130000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>148700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>159600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>157700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>178900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>187600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>203200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>213100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>228200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>238600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>255500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>258500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>47000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>53600</v>
       </c>
-      <c r="R41" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="S41" s="3" t="s">
         <v>10</v>
       </c>
@@ -2547,13 +2634,16 @@
       <c r="V41" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W41" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>50200</v>
       </c>
       <c r="E42" s="3">
         <v>0</v>
@@ -2609,56 +2699,59 @@
       <c r="V42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>24000</v>
+      </c>
+      <c r="E43" s="3">
         <v>25300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>24500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>27000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>27100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>24600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>23900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>22700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>22200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>24300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>24900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>20700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>23200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>21200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>15000</v>
       </c>
-      <c r="R43" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="S43" s="3" t="s">
         <v>10</v>
       </c>
@@ -2671,31 +2764,34 @@
       <c r="V43" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2733,56 +2829,59 @@
       <c r="V44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>4800</v>
-      </c>
-      <c r="E45" s="3">
-        <v>5400</v>
-      </c>
-      <c r="F45" s="3">
-        <v>5800</v>
-      </c>
-      <c r="G45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H45" s="3">
         <v>6300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>3700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>4900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>5600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>6400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>3000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>4600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>6600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>4300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1400</v>
       </c>
-      <c r="R45" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="S45" s="3" t="s">
         <v>10</v>
       </c>
@@ -2795,56 +2894,59 @@
       <c r="V45" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>157100</v>
+      </c>
+      <c r="E46" s="3">
         <v>160200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>178600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>192300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>191000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>207200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>216400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>231500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>241800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>255400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>267200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>280900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>288200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>72600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>70000</v>
       </c>
-      <c r="R46" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="S46" s="3" t="s">
         <v>10</v>
       </c>
@@ -2857,31 +2959,34 @@
       <c r="V46" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -2919,56 +3024,59 @@
       <c r="V47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>16100</v>
+      </c>
+      <c r="E48" s="3">
         <v>16600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>17400</v>
       </c>
-      <c r="F48" s="3">
-        <v>17800</v>
-      </c>
       <c r="G48" s="3">
-        <v>17800</v>
+        <v>11000</v>
       </c>
       <c r="H48" s="3">
         <v>17800</v>
       </c>
       <c r="I48" s="3">
+        <v>17800</v>
+      </c>
+      <c r="J48" s="3">
         <v>17400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>17300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>17800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>18200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>6500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>6200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>6100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>5900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>5600</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="S48" s="3" t="s">
         <v>10</v>
       </c>
@@ -2981,8 +3089,11 @@
       <c r="V48" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2990,35 +3101,35 @@
         <v>20400</v>
       </c>
       <c r="E49" s="3">
+        <v>20400</v>
+      </c>
+      <c r="F49" s="3">
         <v>20500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
+        <v>27400</v>
+      </c>
+      <c r="H49" s="3">
         <v>20600</v>
       </c>
-      <c r="G49" s="3">
-        <v>20600</v>
-      </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>6700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>6800</v>
-      </c>
-      <c r="J49" s="3">
-        <v>6900</v>
       </c>
       <c r="K49" s="3">
         <v>6900</v>
       </c>
       <c r="L49" s="3">
+        <v>6900</v>
+      </c>
+      <c r="M49" s="3">
         <v>7000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>7100</v>
       </c>
-      <c r="N49" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="O49" s="3" t="s">
         <v>10</v>
       </c>
@@ -3031,8 +3142,8 @@
       <c r="R49" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="S49" s="3">
-        <v>0</v>
+      <c r="S49" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="T49" s="3">
         <v>0</v>
@@ -3043,8 +3154,11 @@
       <c r="V49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3105,8 +3219,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3167,8 +3284,11 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3182,7 +3302,7 @@
         <v>800</v>
       </c>
       <c r="G52" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="H52" s="3">
         <v>700</v>
@@ -3191,22 +3311,22 @@
         <v>700</v>
       </c>
       <c r="J52" s="3">
+        <v>700</v>
+      </c>
+      <c r="K52" s="3">
         <v>600</v>
-      </c>
-      <c r="K52" s="3">
-        <v>700</v>
       </c>
       <c r="L52" s="3">
         <v>700</v>
       </c>
       <c r="M52" s="3">
-        <v>400</v>
+        <v>700</v>
       </c>
       <c r="N52" s="3">
         <v>400</v>
       </c>
       <c r="O52" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="P52" s="3">
         <v>500</v>
@@ -3214,8 +3334,8 @@
       <c r="Q52" s="3">
         <v>500</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>10</v>
+      <c r="R52" s="3">
+        <v>500</v>
       </c>
       <c r="S52" s="3" t="s">
         <v>10</v>
@@ -3229,8 +3349,11 @@
       <c r="V52" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3291,56 +3414,59 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>194400</v>
+      </c>
+      <c r="E54" s="3">
         <v>198000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>217300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>231500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>230200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>232400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>241300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>256300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>267200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>281300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>281100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>287400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>294800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>78900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>76200</v>
       </c>
-      <c r="R54" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="S54" s="3" t="s">
         <v>10</v>
       </c>
@@ -3353,8 +3479,11 @@
       <c r="V54" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W54" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3377,8 +3506,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3401,56 +3531,57 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E57" s="3">
         <v>4000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>5200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>6500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>5100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>6500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>8500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>6800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>8600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>7500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>4700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>8000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>6100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>4300</v>
       </c>
-      <c r="R57" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="S57" s="3" t="s">
         <v>10</v>
       </c>
@@ -3463,31 +3594,34 @@
       <c r="V57" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W57" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>1900</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>1900</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>1900</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>1900</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -3496,7 +3630,7 @@
         <v>0</v>
       </c>
       <c r="M58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N58" s="3">
         <v>100</v>
@@ -3510,8 +3644,8 @@
       <c r="Q58" s="3">
         <v>100</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>10</v>
+      <c r="R58" s="3">
+        <v>100</v>
       </c>
       <c r="S58" s="3" t="s">
         <v>10</v>
@@ -3525,56 +3659,59 @@
       <c r="V58" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>16400</v>
+        <v>3500</v>
       </c>
       <c r="E59" s="3">
-        <v>15000</v>
+        <v>4000</v>
       </c>
       <c r="F59" s="3">
-        <v>17800</v>
+        <v>3500</v>
       </c>
       <c r="G59" s="3">
-        <v>14600</v>
+        <v>4300</v>
       </c>
       <c r="H59" s="3">
-        <v>14800</v>
+        <v>3000</v>
       </c>
       <c r="I59" s="3">
-        <v>13800</v>
+        <v>3400</v>
       </c>
       <c r="J59" s="3">
+        <v>4300</v>
+      </c>
+      <c r="K59" s="3">
         <v>14200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>15400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>14300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>12000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>13900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>12700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>10200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>7500</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="S59" s="3" t="s">
         <v>10</v>
       </c>
@@ -3587,56 +3724,59 @@
       <c r="V59" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>21000</v>
+      </c>
+      <c r="E60" s="3">
         <v>20500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>17000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>23100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>21100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>20000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>20400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>22800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>22300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>22900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>19600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>18600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>20700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>16500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>11900</v>
       </c>
-      <c r="R60" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="S60" s="3" t="s">
         <v>10</v>
       </c>
@@ -3649,31 +3789,34 @@
       <c r="V60" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>100</v>
+        <v>5900</v>
       </c>
       <c r="E61" s="3">
-        <v>100</v>
+        <v>6400</v>
       </c>
       <c r="F61" s="3">
-        <v>200</v>
+        <v>6900</v>
       </c>
       <c r="G61" s="3">
-        <v>200</v>
+        <v>7300</v>
       </c>
       <c r="H61" s="3">
-        <v>200</v>
+        <v>7700</v>
       </c>
       <c r="I61" s="3">
-        <v>200</v>
+        <v>8100</v>
       </c>
       <c r="J61" s="3">
-        <v>200</v>
+        <v>8600</v>
       </c>
       <c r="K61" s="3">
         <v>200</v>
@@ -3682,7 +3825,7 @@
         <v>200</v>
       </c>
       <c r="M61" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="N61" s="3">
         <v>0</v>
@@ -3694,11 +3837,11 @@
         <v>0</v>
       </c>
       <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3">
         <v>100</v>
       </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
       <c r="S61" s="3">
         <v>0</v>
       </c>
@@ -3711,56 +3854,59 @@
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>6500</v>
+        <v>200</v>
       </c>
       <c r="E62" s="3">
-        <v>7000</v>
+        <v>200</v>
       </c>
       <c r="F62" s="3">
-        <v>7900</v>
+        <v>300</v>
       </c>
       <c r="G62" s="3">
-        <v>7900</v>
+        <v>800</v>
       </c>
       <c r="H62" s="3">
-        <v>8400</v>
+        <v>400</v>
       </c>
       <c r="I62" s="3">
-        <v>8900</v>
+        <v>400</v>
       </c>
       <c r="J62" s="3">
+        <v>500</v>
+      </c>
+      <c r="K62" s="3">
         <v>9700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>9900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>10300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>700</v>
-      </c>
-      <c r="N62" s="3">
-        <v>100</v>
       </c>
       <c r="O62" s="3">
         <v>100</v>
       </c>
       <c r="P62" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q62" s="3">
         <v>400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>600</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="S62" s="3" t="s">
         <v>10</v>
       </c>
@@ -3773,8 +3919,11 @@
       <c r="V62" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3835,8 +3984,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3897,8 +4049,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3959,8 +4114,11 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -3968,47 +4126,47 @@
         <v>27100</v>
       </c>
       <c r="E66" s="3">
+        <v>27100</v>
+      </c>
+      <c r="F66" s="3">
         <v>24100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>31200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>29200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>28500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>29500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>32700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>32400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>33500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>20200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>18700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>20800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>16900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>12600</v>
       </c>
-      <c r="R66" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="S66" s="3" t="s">
         <v>10</v>
       </c>
@@ -4021,8 +4179,11 @@
       <c r="V66" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W66" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4045,8 +4206,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4107,8 +4269,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4169,8 +4334,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4211,14 +4379,14 @@
         <v>0</v>
       </c>
       <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3">
         <v>160900</v>
       </c>
-      <c r="Q70" s="3">
+      <c r="R70" s="3">
         <v>160800</v>
       </c>
-      <c r="R70" s="3">
-        <v>0</v>
-      </c>
       <c r="S70" s="3">
         <v>0</v>
       </c>
@@ -4231,8 +4399,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4293,56 +4464,59 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-272200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-263100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-251200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-240400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-234500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-233500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-218600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-198200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-179500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-159500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-139300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-127500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-118400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-109100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-106000</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="S72" s="3" t="s">
         <v>10</v>
       </c>
@@ -4355,8 +4529,11 @@
       <c r="V72" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W72" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4417,8 +4594,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4479,8 +4659,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4541,56 +4724,59 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>167300</v>
+      </c>
+      <c r="E76" s="3">
         <v>170900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>193200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>200300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>201000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>203900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>211800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>223600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>234800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>247800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>260800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>268700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>274000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-98800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-97200</v>
       </c>
-      <c r="R76" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="S76" s="3" t="s">
         <v>10</v>
       </c>
@@ -4603,8 +4789,11 @@
       <c r="V76" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W76" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4665,137 +4854,146 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
     </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-10800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-10600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-5800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-1000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-14900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-20400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-18700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-20100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-20200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-11800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-9100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-9200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-3100</v>
-      </c>
-      <c r="Q81" s="3">
-        <v>-3000</v>
       </c>
       <c r="R81" s="3">
         <v>-3000</v>
       </c>
       <c r="S81" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="T81" s="3">
         <v>-3200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-5500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-11300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-8200</v>
       </c>
     </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4818,8 +5016,9 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4827,34 +5026,34 @@
         <v>1000</v>
       </c>
       <c r="E83" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="F83" s="3">
-        <v>1100</v>
+        <v>900</v>
       </c>
       <c r="G83" s="3">
-        <v>1100</v>
+        <v>-300</v>
       </c>
       <c r="H83" s="3">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="I83" s="3">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="J83" s="3">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="K83" s="3">
         <v>900</v>
       </c>
       <c r="L83" s="3">
+        <v>900</v>
+      </c>
+      <c r="M83" s="3">
         <v>700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>500</v>
-      </c>
-      <c r="N83" s="3">
-        <v>400</v>
       </c>
       <c r="O83" s="3">
         <v>400</v>
@@ -4865,23 +5064,26 @@
       <c r="Q83" s="3">
         <v>400</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>10</v>
+      <c r="R83" s="3">
+        <v>400</v>
       </c>
       <c r="S83" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="T83" s="3">
+      <c r="T83" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="U83" s="3">
         <v>800</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="V83" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4942,8 +5144,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5004,8 +5209,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5066,8 +5274,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5128,8 +5339,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5190,70 +5404,76 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-7300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>3200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-6900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-7100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-14800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-9400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-14500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-10800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-11400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-2800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-8600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-5700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-4500</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="S89" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="T89" s="3">
+      <c r="T89" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="U89" s="3">
         <v>-15100</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="V89" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W89" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5276,70 +5496,74 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-700</v>
+        <v>-900</v>
       </c>
       <c r="E91" s="3">
         <v>-700</v>
       </c>
       <c r="F91" s="3">
+        <v>-700</v>
+      </c>
+      <c r="G91" s="3">
         <v>-1300</v>
       </c>
-      <c r="G91" s="3">
-        <v>-15100</v>
-      </c>
       <c r="H91" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="I91" s="3">
         <v>-1700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-800</v>
-      </c>
-      <c r="O91" s="3">
-        <v>-900</v>
       </c>
       <c r="P91" s="3">
         <v>-900</v>
       </c>
       <c r="Q91" s="3">
+        <v>-900</v>
+      </c>
+      <c r="R91" s="3">
         <v>-600</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="S91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="T91" s="3">
+      <c r="T91" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="U91" s="3">
         <v>-1000</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="V91" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5400,8 +5624,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5462,70 +5689,76 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-700</v>
+        <v>-50800</v>
       </c>
       <c r="E94" s="3">
         <v>-700</v>
       </c>
       <c r="F94" s="3">
+        <v>-700</v>
+      </c>
+      <c r="G94" s="3">
         <v>-1300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-15100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-2000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-5900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-800</v>
-      </c>
-      <c r="O94" s="3">
-        <v>-900</v>
       </c>
       <c r="P94" s="3">
         <v>-900</v>
       </c>
       <c r="Q94" s="3">
+        <v>-900</v>
+      </c>
+      <c r="R94" s="3">
         <v>-600</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="S94" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="T94" s="3">
+      <c r="T94" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="U94" s="3">
         <v>-1000</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="V94" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5548,31 +5781,32 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -5610,8 +5844,11 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5672,8 +5909,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5734,8 +5974,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5796,93 +6039,99 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-17400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-2900</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>700</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>1200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>221000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>100</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="S100" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="T100" s="3">
+      <c r="T100" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="U100" s="3">
         <v>16900</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="V100" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W100" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -5920,66 +6169,72 @@
       <c r="V101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-53500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-18700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-10900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-21300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-8700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-15600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-9900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-15100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-10400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-16900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-3000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>211500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-6600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-4900</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="S102" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="T102" s="3">
+      <c r="T102" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="U102" s="3">
         <v>800</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="V102" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="W102" s="3" t="s">
         <v>10</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LAW_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LAW_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="92">
   <si>
     <t>LAW</t>
   </si>
@@ -656,302 +656,314 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>37000</v>
+      </c>
+      <c r="E8" s="3">
         <v>36300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>36000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>35600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>35700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>34900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>34300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>33100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>32500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>34500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>33700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>34500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>33800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>29900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>29500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>21100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>19200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>17900</v>
-      </c>
-      <c r="U8" s="3">
-        <v>15700</v>
       </c>
       <c r="V8" s="3">
         <v>15700</v>
       </c>
       <c r="W8" s="3">
+        <v>15700</v>
+      </c>
+      <c r="X8" s="3">
         <v>14200</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>9500</v>
+      </c>
+      <c r="E9" s="3">
         <v>9700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>9300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>8900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>8700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>8900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>9000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>8300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>8100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>8600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>8500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>9000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>8800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>7800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>8700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>5800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>5300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>5500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>4500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>5100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>4600</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>27500</v>
+      </c>
+      <c r="E10" s="3">
         <v>26500</v>
-      </c>
-      <c r="E10" s="3">
-        <v>26700</v>
       </c>
       <c r="F10" s="3">
         <v>26700</v>
       </c>
       <c r="G10" s="3">
+        <v>26700</v>
+      </c>
+      <c r="H10" s="3">
         <v>27000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>26000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>25200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>24900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>24400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>25900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>25200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>25500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>25000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>22100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>20800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>15300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>13900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>12400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>11200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>10600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>9600</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -975,73 +987,77 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>13800</v>
+      </c>
+      <c r="E12" s="3">
         <v>12800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>12900</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>12100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>10500</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>12100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>12300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>15300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>16100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>15700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>15200</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>12300</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>10600</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>9700</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>7900</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>6300</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>6000</v>
-      </c>
-      <c r="T12" s="3">
-        <v>6200</v>
       </c>
       <c r="U12" s="3">
         <v>6200</v>
       </c>
       <c r="V12" s="3">
+        <v>6200</v>
+      </c>
+      <c r="W12" s="3">
         <v>8200</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>6900</v>
       </c>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1105,35 +1121,38 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>14800</v>
+      </c>
+      <c r="E14" s="3">
         <v>100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>400</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H14" s="3">
         <v>8200</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-7700</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>1600</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>1000</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>10</v>
       </c>
@@ -1143,61 +1162,64 @@
       <c r="N14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="R14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="S14" s="3">
         <v>0</v>
       </c>
       <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>-1100</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
       <c r="V14" s="3">
         <v>0</v>
       </c>
       <c r="W14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="E15" s="3">
         <v>1000</v>
       </c>
       <c r="F15" s="3">
+        <v>1000</v>
+      </c>
+      <c r="G15" s="3">
         <v>1100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1100</v>
-      </c>
-      <c r="I15" s="3">
-        <v>1000</v>
       </c>
       <c r="J15" s="3">
         <v>1000</v>
       </c>
       <c r="K15" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="L15" s="3">
         <v>0</v>
@@ -1235,8 +1257,11 @@
       <c r="W15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1257,138 +1282,145 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>48300</v>
+      </c>
+      <c r="E17" s="3">
         <v>47000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>48000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>47900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>35200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>45500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>49700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>54400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>52600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>54500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>53700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>46200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>42800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>38900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>32500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>24000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>22100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>20900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>21000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>26900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>22500</v>
       </c>
     </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-11300</v>
+      </c>
+      <c r="E18" s="3">
         <v>-10700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-12000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-12300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-10600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-15400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-21300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-20100</v>
-      </c>
-      <c r="L18" s="3">
-        <v>-20000</v>
       </c>
       <c r="M18" s="3">
         <v>-20000</v>
       </c>
       <c r="N18" s="3">
+        <v>-20000</v>
+      </c>
+      <c r="O18" s="3">
         <v>-11700</v>
-      </c>
-      <c r="O18" s="3">
-        <v>-9000</v>
       </c>
       <c r="P18" s="3">
         <v>-9000</v>
       </c>
       <c r="Q18" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="R18" s="3">
         <v>-3000</v>
-      </c>
-      <c r="R18" s="3">
-        <v>-2900</v>
       </c>
       <c r="S18" s="3">
         <v>-2900</v>
       </c>
       <c r="T18" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="U18" s="3">
         <v>-3000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-5300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-11200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-8300</v>
       </c>
     </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1412,17 +1444,18 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E20" s="3">
         <v>-200</v>
       </c>
-      <c r="E20" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="F20" s="3" t="s">
         <v>10</v>
       </c>
@@ -1432,32 +1465,32 @@
       <c r="H20" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
+      <c r="I20" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="J20" s="3">
         <v>0</v>
       </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>1500</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>-200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-100</v>
-      </c>
-      <c r="O20" s="3">
-        <v>-200</v>
       </c>
       <c r="P20" s="3">
         <v>-200</v>
       </c>
       <c r="Q20" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="R20" s="3">
         <v>0</v>
@@ -1466,110 +1499,116 @@
         <v>0</v>
       </c>
       <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>-200</v>
-      </c>
-      <c r="U20" s="3">
-        <v>-100</v>
       </c>
       <c r="V20" s="3">
         <v>-100</v>
       </c>
       <c r="W20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="X20" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-10800</v>
+      </c>
+      <c r="E21" s="3">
         <v>-9600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-11000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-11300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-9500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-14400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-20300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-17700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-19100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-19400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-11400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-8700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-8800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-2600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-2500</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="T21" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="U21" s="3">
+      <c r="U21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="V21" s="3">
         <v>-4700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-10800</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X21" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E22" s="3">
+      <c r="D22" s="3">
+        <v>500</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F22" s="3">
         <v>100</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>200</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>-100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>300</v>
       </c>
-      <c r="I22" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="J22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1607,78 +1646,84 @@
       <c r="W22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-25200</v>
+      </c>
+      <c r="E23" s="3">
         <v>-9000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-10700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-10500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-5600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-1000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-14900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-20300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-18600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-20000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-20100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-11800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-9100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-9200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-3000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-2900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-3000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-3200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-5500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-11200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-8200</v>
       </c>
     </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E24" s="3">
         <v>100</v>
@@ -1687,23 +1732,23 @@
         <v>100</v>
       </c>
       <c r="G24" s="3">
+        <v>100</v>
+      </c>
+      <c r="H24" s="3">
         <v>300</v>
-      </c>
-      <c r="H24" s="3">
-        <v>100</v>
       </c>
       <c r="I24" s="3">
         <v>100</v>
       </c>
       <c r="J24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3">
         <v>100</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
       <c r="M24" s="3">
         <v>0</v>
       </c>
@@ -1737,8 +1782,11 @@
       <c r="W24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1802,138 +1850,147 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-25200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-9200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-10800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-10600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-5800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-1000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-14900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-20400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-18700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-20100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-20200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-11800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-9100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-9200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-3100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-2900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-3000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-3200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-5500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-11200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-8200</v>
       </c>
     </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-25200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-9200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-10800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-10600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-5800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-1000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-14900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-20400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-18700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-20100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-20200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-11800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-9100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-9200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-3100</v>
-      </c>
-      <c r="R27" s="3">
-        <v>-3000</v>
       </c>
       <c r="S27" s="3">
         <v>-3000</v>
       </c>
       <c r="T27" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="U27" s="3">
         <v>-3200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-5500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-11300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-8200</v>
       </c>
     </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1997,8 +2054,11 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2062,8 +2122,11 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2127,8 +2190,11 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2192,17 +2258,20 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E32" s="3">
         <v>200</v>
       </c>
-      <c r="E32" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="F32" s="3" t="s">
         <v>10</v>
       </c>
@@ -2212,32 +2281,32 @@
       <c r="H32" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
+      <c r="I32" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="J32" s="3">
         <v>0</v>
       </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>-1500</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>100</v>
-      </c>
-      <c r="O32" s="3">
-        <v>200</v>
       </c>
       <c r="P32" s="3">
         <v>200</v>
       </c>
       <c r="Q32" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="R32" s="3">
         <v>0</v>
@@ -2246,84 +2315,90 @@
         <v>0</v>
       </c>
       <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>200</v>
-      </c>
-      <c r="U32" s="3">
-        <v>100</v>
       </c>
       <c r="V32" s="3">
         <v>100</v>
       </c>
       <c r="W32" s="3">
+        <v>100</v>
+      </c>
+      <c r="X32" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-25200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-9200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-10800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-10600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-5800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-1000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-14900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-20400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-18700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-20100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-20200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-11800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-9100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-9200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-3100</v>
-      </c>
-      <c r="R33" s="3">
-        <v>-3000</v>
       </c>
       <c r="S33" s="3">
         <v>-3000</v>
       </c>
       <c r="T33" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="U33" s="3">
         <v>-3200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-5500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-11300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-8200</v>
       </c>
     </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2387,143 +2462,152 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-25200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-9200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-10800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-10600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-5800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-1000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-14900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-20400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-18700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-20100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-20200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-11800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-9100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-9200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-3100</v>
-      </c>
-      <c r="R35" s="3">
-        <v>-3000</v>
       </c>
       <c r="S35" s="3">
         <v>-3000</v>
       </c>
       <c r="T35" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="U35" s="3">
         <v>-3200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-5500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-11300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-8200</v>
       </c>
     </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
     </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2547,8 +2631,9 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2572,59 +2657,60 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>52800</v>
+      </c>
+      <c r="E41" s="3">
         <v>76500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>130000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>148700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>159600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>157700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>178900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>187600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>203200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>213100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>228200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>238600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>255500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>258500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>47000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>53600</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="T41" s="3" t="s">
         <v>10</v>
       </c>
@@ -2637,17 +2723,20 @@
       <c r="W41" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X41" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>76400</v>
+      </c>
+      <c r="E42" s="3">
         <v>50200</v>
       </c>
-      <c r="E42" s="3">
-        <v>0</v>
-      </c>
       <c r="F42" s="3">
         <v>0</v>
       </c>
@@ -2702,59 +2791,62 @@
       <c r="W42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>23100</v>
+      </c>
+      <c r="E43" s="3">
         <v>24000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>25300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>24500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>27000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>27100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>24600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>23900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>22700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>22200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>24300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>24900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>20700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>23200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>21200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>15000</v>
       </c>
-      <c r="S43" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="T43" s="3" t="s">
         <v>10</v>
       </c>
@@ -2767,8 +2859,11 @@
       <c r="W43" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X43" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2793,8 +2888,8 @@
       <c r="J44" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -2832,8 +2927,11 @@
       <c r="W44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2849,42 +2947,42 @@
       <c r="G45" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I45" s="3">
         <v>6300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>3700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>4900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>5600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>6400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>4600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>6600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>4300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1400</v>
       </c>
-      <c r="S45" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="T45" s="3" t="s">
         <v>10</v>
       </c>
@@ -2897,59 +2995,62 @@
       <c r="W45" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X45" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>156900</v>
+      </c>
+      <c r="E46" s="3">
         <v>157100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>160200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>178600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>192300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>191000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>207200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>216400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>231500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>241800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>255400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>267200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>280900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>288200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>72600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>70000</v>
       </c>
-      <c r="S46" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="T46" s="3" t="s">
         <v>10</v>
       </c>
@@ -2962,8 +3063,11 @@
       <c r="W46" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X46" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2988,8 +3092,8 @@
       <c r="J47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -3027,59 +3131,62 @@
       <c r="W47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>10500</v>
+      </c>
+      <c r="E48" s="3">
         <v>16100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>16600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>17400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>11000</v>
-      </c>
-      <c r="H48" s="3">
-        <v>17800</v>
       </c>
       <c r="I48" s="3">
         <v>17800</v>
       </c>
       <c r="J48" s="3">
+        <v>17800</v>
+      </c>
+      <c r="K48" s="3">
         <v>17400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>17300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>17800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>18200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>6500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>6200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>6100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>5900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>5600</v>
       </c>
-      <c r="S48" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="T48" s="3" t="s">
         <v>10</v>
       </c>
@@ -3092,47 +3199,50 @@
       <c r="W48" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X48" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>20400</v>
+        <v>12100</v>
       </c>
       <c r="E49" s="3">
         <v>20400</v>
       </c>
       <c r="F49" s="3">
+        <v>20400</v>
+      </c>
+      <c r="G49" s="3">
         <v>20500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>27400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>20600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>6700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>6800</v>
-      </c>
-      <c r="K49" s="3">
-        <v>6900</v>
       </c>
       <c r="L49" s="3">
         <v>6900</v>
       </c>
       <c r="M49" s="3">
+        <v>6900</v>
+      </c>
+      <c r="N49" s="3">
         <v>7000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>7100</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="P49" s="3" t="s">
         <v>10</v>
       </c>
@@ -3145,8 +3255,8 @@
       <c r="S49" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="T49" s="3">
-        <v>0</v>
+      <c r="T49" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="U49" s="3">
         <v>0</v>
@@ -3157,8 +3267,11 @@
       <c r="W49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3222,8 +3335,11 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3287,8 +3403,11 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3305,7 +3424,7 @@
         <v>800</v>
       </c>
       <c r="H52" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="I52" s="3">
         <v>700</v>
@@ -3314,22 +3433,22 @@
         <v>700</v>
       </c>
       <c r="K52" s="3">
+        <v>700</v>
+      </c>
+      <c r="L52" s="3">
         <v>600</v>
-      </c>
-      <c r="L52" s="3">
-        <v>700</v>
       </c>
       <c r="M52" s="3">
         <v>700</v>
       </c>
       <c r="N52" s="3">
-        <v>400</v>
+        <v>700</v>
       </c>
       <c r="O52" s="3">
         <v>400</v>
       </c>
       <c r="P52" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="Q52" s="3">
         <v>500</v>
@@ -3337,8 +3456,8 @@
       <c r="R52" s="3">
         <v>500</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>10</v>
+      <c r="S52" s="3">
+        <v>500</v>
       </c>
       <c r="T52" s="3" t="s">
         <v>10</v>
@@ -3352,8 +3471,11 @@
       <c r="W52" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X52" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3417,59 +3539,62 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>180300</v>
+      </c>
+      <c r="E54" s="3">
         <v>194400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>198000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>217300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>231500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>230200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>232400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>241300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>256300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>267200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>281300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>281100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>287400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>294800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>78900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>76200</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="T54" s="3" t="s">
         <v>10</v>
       </c>
@@ -3482,8 +3607,11 @@
       <c r="W54" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X54" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3507,8 +3635,9 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3532,59 +3661,60 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E57" s="3">
         <v>3400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>4000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>5200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>6500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>5100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>6500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>8500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>6800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>8600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>7500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>4700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>8000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>6100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>4300</v>
       </c>
-      <c r="S57" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="T57" s="3" t="s">
         <v>10</v>
       </c>
@@ -3597,34 +3727,37 @@
       <c r="W57" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X57" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1900</v>
+        <v>2300</v>
       </c>
       <c r="E58" s="3">
         <v>1900</v>
       </c>
       <c r="F58" s="3">
+        <v>1900</v>
+      </c>
+      <c r="G58" s="3">
         <v>2000</v>
-      </c>
-      <c r="G58" s="3">
-        <v>1900</v>
       </c>
       <c r="H58" s="3">
         <v>1900</v>
       </c>
       <c r="I58" s="3">
-        <v>2000</v>
+        <v>1900</v>
       </c>
       <c r="J58" s="3">
         <v>2000</v>
       </c>
       <c r="K58" s="3">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="L58" s="3">
         <v>0</v>
@@ -3633,7 +3766,7 @@
         <v>0</v>
       </c>
       <c r="N58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O58" s="3">
         <v>100</v>
@@ -3647,8 +3780,8 @@
       <c r="R58" s="3">
         <v>100</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>10</v>
+      <c r="S58" s="3">
+        <v>100</v>
       </c>
       <c r="T58" s="3" t="s">
         <v>10</v>
@@ -3662,59 +3795,62 @@
       <c r="W58" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E59" s="3">
         <v>3500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>4000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>3500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>4300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>3000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>3400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>4300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>14200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>15400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>14300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>12000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>13900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>12700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>10200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>7500</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="T59" s="3" t="s">
         <v>10</v>
       </c>
@@ -3727,59 +3863,62 @@
       <c r="W59" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X59" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>25700</v>
+      </c>
+      <c r="E60" s="3">
         <v>21000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>20500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>17000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>23100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>21100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>20000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>20400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>22800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>22300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>22900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>19600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>18600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>20700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>16500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>11900</v>
       </c>
-      <c r="S60" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="T60" s="3" t="s">
         <v>10</v>
       </c>
@@ -3792,34 +3931,37 @@
       <c r="W60" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X60" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E61" s="3">
         <v>5900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>6400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>6900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>7300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>7700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>8100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>8600</v>
-      </c>
-      <c r="K61" s="3">
-        <v>200</v>
       </c>
       <c r="L61" s="3">
         <v>200</v>
@@ -3828,7 +3970,7 @@
         <v>200</v>
       </c>
       <c r="N61" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="O61" s="3">
         <v>0</v>
@@ -3840,11 +3982,11 @@
         <v>0</v>
       </c>
       <c r="R61" s="3">
+        <v>0</v>
+      </c>
+      <c r="S61" s="3">
         <v>100</v>
       </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
       <c r="T61" s="3">
         <v>0</v>
       </c>
@@ -3857,59 +3999,62 @@
       <c r="W61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E62" s="3">
         <v>200</v>
       </c>
       <c r="F62" s="3">
+        <v>200</v>
+      </c>
+      <c r="G62" s="3">
         <v>300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>800</v>
-      </c>
-      <c r="H62" s="3">
-        <v>400</v>
       </c>
       <c r="I62" s="3">
         <v>400</v>
       </c>
       <c r="J62" s="3">
+        <v>400</v>
+      </c>
+      <c r="K62" s="3">
         <v>500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>9700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>9900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>10300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>700</v>
-      </c>
-      <c r="O62" s="3">
-        <v>100</v>
       </c>
       <c r="P62" s="3">
         <v>100</v>
       </c>
       <c r="Q62" s="3">
+        <v>100</v>
+      </c>
+      <c r="R62" s="3">
         <v>400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>600</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="T62" s="3" t="s">
         <v>10</v>
       </c>
@@ -3922,8 +4067,11 @@
       <c r="W62" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X62" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3987,8 +4135,11 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4052,8 +4203,11 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4117,59 +4271,62 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>27100</v>
+        <v>32800</v>
       </c>
       <c r="E66" s="3">
         <v>27100</v>
       </c>
       <c r="F66" s="3">
+        <v>27100</v>
+      </c>
+      <c r="G66" s="3">
         <v>24100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>31200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>29200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>28500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>29500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>32700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>32400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>33500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>20200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>18700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>20800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>16900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>12600</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="T66" s="3" t="s">
         <v>10</v>
       </c>
@@ -4182,8 +4339,11 @@
       <c r="W66" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X66" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4207,8 +4367,9 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4272,8 +4433,11 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4337,8 +4501,11 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4382,14 +4549,14 @@
         <v>0</v>
       </c>
       <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3">
         <v>160900</v>
       </c>
-      <c r="R70" s="3">
+      <c r="S70" s="3">
         <v>160800</v>
       </c>
-      <c r="S70" s="3">
-        <v>0</v>
-      </c>
       <c r="T70" s="3">
         <v>0</v>
       </c>
@@ -4402,8 +4569,11 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4467,59 +4637,62 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-297400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-272200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-263100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-251200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-240400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-234500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-233500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-218600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-198200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-179500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-159500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-139300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-127500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-118400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-109100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-106000</v>
       </c>
-      <c r="S72" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="T72" s="3" t="s">
         <v>10</v>
       </c>
@@ -4532,8 +4705,11 @@
       <c r="W72" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X72" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4597,8 +4773,11 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4662,8 +4841,11 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4727,59 +4909,62 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>147500</v>
+      </c>
+      <c r="E76" s="3">
         <v>167300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>170900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>193200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>200300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>201000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>203900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>211800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>223600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>234800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>247800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>260800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>268700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>274000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-98800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-97200</v>
       </c>
-      <c r="S76" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="T76" s="3" t="s">
         <v>10</v>
       </c>
@@ -4792,8 +4977,11 @@
       <c r="W76" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X76" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4857,143 +5045,152 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
     </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-25200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-9200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-10800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-10600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-5800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-1000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-14900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-20400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-18700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-20100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-20200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-11800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-9100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-9200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-3100</v>
-      </c>
-      <c r="R81" s="3">
-        <v>-3000</v>
       </c>
       <c r="S81" s="3">
         <v>-3000</v>
       </c>
       <c r="T81" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="U81" s="3">
         <v>-3200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-5500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-11300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-8200</v>
       </c>
     </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5017,46 +5214,47 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1000</v>
+        <v>-600</v>
       </c>
       <c r="E83" s="3">
         <v>1000</v>
       </c>
       <c r="F83" s="3">
+        <v>1000</v>
+      </c>
+      <c r="G83" s="3">
         <v>900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>-300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>500</v>
-      </c>
-      <c r="K83" s="3">
-        <v>900</v>
       </c>
       <c r="L83" s="3">
         <v>900</v>
       </c>
       <c r="M83" s="3">
+        <v>900</v>
+      </c>
+      <c r="N83" s="3">
         <v>700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>500</v>
-      </c>
-      <c r="O83" s="3">
-        <v>400</v>
       </c>
       <c r="P83" s="3">
         <v>400</v>
@@ -5067,23 +5265,26 @@
       <c r="R83" s="3">
         <v>400</v>
       </c>
-      <c r="S83" s="3" t="s">
-        <v>10</v>
+      <c r="S83" s="3">
+        <v>400</v>
       </c>
       <c r="T83" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="U83" s="3">
+      <c r="U83" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="V83" s="3">
         <v>800</v>
       </c>
-      <c r="V83" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="W83" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X83" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5147,8 +5348,11 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5212,8 +5416,11 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5277,8 +5484,11 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5342,8 +5552,11 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5407,73 +5620,79 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E89" s="3">
         <v>-2900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-7300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>3200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-6900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-7100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-14800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-9400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-14500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-10800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-11400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-2800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-8600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-5700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-4500</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="T89" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="U89" s="3">
+      <c r="U89" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="V89" s="3">
         <v>-15100</v>
       </c>
-      <c r="V89" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="W89" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X89" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5497,73 +5716,77 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-900</v>
-      </c>
-      <c r="E91" s="3">
-        <v>-700</v>
       </c>
       <c r="F91" s="3">
         <v>-700</v>
       </c>
       <c r="G91" s="3">
+        <v>-700</v>
+      </c>
+      <c r="H91" s="3">
         <v>-1300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-800</v>
-      </c>
-      <c r="P91" s="3">
-        <v>-900</v>
       </c>
       <c r="Q91" s="3">
         <v>-900</v>
       </c>
       <c r="R91" s="3">
+        <v>-900</v>
+      </c>
+      <c r="S91" s="3">
         <v>-600</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="T91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="U91" s="3">
+      <c r="U91" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="V91" s="3">
         <v>-1000</v>
       </c>
-      <c r="V91" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="W91" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X91" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5627,8 +5850,11 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5692,73 +5918,79 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-25900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-50800</v>
-      </c>
-      <c r="E94" s="3">
-        <v>-700</v>
       </c>
       <c r="F94" s="3">
         <v>-700</v>
       </c>
       <c r="G94" s="3">
+        <v>-700</v>
+      </c>
+      <c r="H94" s="3">
         <v>-1300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-15100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-2000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-5900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-800</v>
-      </c>
-      <c r="P94" s="3">
-        <v>-900</v>
       </c>
       <c r="Q94" s="3">
         <v>-900</v>
       </c>
       <c r="R94" s="3">
+        <v>-900</v>
+      </c>
+      <c r="S94" s="3">
         <v>-600</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="T94" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="U94" s="3">
+      <c r="U94" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="V94" s="3">
         <v>-1000</v>
       </c>
-      <c r="V94" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="W94" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X94" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5782,8 +6014,9 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5808,8 +6041,8 @@
       <c r="J96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -5847,8 +6080,11 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5912,8 +6148,11 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5977,8 +6216,11 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6042,73 +6284,79 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
         <v>200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-17400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-2900</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
       <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>700</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>1200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>1600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>221000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>100</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="T100" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="U100" s="3">
+      <c r="U100" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="V100" s="3">
         <v>16900</v>
       </c>
-      <c r="V100" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="W100" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X100" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6133,8 +6381,8 @@
       <c r="J101" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -6172,69 +6420,75 @@
       <c r="W101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-23800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-53500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-18700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-10900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-21300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-8700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-15600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-9900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-15100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-10400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-16900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-3000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>211500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-6600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-4900</v>
       </c>
-      <c r="S102" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="T102" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="U102" s="3">
+      <c r="U102" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="V102" s="3">
         <v>800</v>
       </c>
-      <c r="V102" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="W102" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="X102" s="3" t="s">
         <v>10</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LAW_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LAW_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="92">
   <si>
     <t>LAW</t>
   </si>
@@ -656,178 +656,185 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>36700</v>
+      </c>
+      <c r="E8" s="3">
         <v>37000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>36300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>36000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>35600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>35700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>34900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>34300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>33100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>32500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>34500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>33700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>34500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>33800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>29900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>29500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>21100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>19200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>17900</v>
-      </c>
-      <c r="V8" s="3">
-        <v>15700</v>
       </c>
       <c r="W8" s="3">
         <v>15700</v>
       </c>
       <c r="X8" s="3">
+        <v>15700</v>
+      </c>
+      <c r="Y8" s="3">
         <v>14200</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -835,135 +842,141 @@
         <v>9500</v>
       </c>
       <c r="E9" s="3">
+        <v>9500</v>
+      </c>
+      <c r="F9" s="3">
         <v>9700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>9300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>8900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>8700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>8900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>9000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>8300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>8100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>8600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>8500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>9000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>8800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>7800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>8700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>5800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>5300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>5500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>4500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>5100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>4600</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>27200</v>
+      </c>
+      <c r="E10" s="3">
         <v>27500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>26500</v>
-      </c>
-      <c r="F10" s="3">
-        <v>26700</v>
       </c>
       <c r="G10" s="3">
         <v>26700</v>
       </c>
       <c r="H10" s="3">
+        <v>26700</v>
+      </c>
+      <c r="I10" s="3">
         <v>27000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>26000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>25200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>24900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>24400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>25900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>25200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>25500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>25000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>22100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>20800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>15300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>13900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>12400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>11200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>10600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>9600</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -988,76 +1001,80 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>14300</v>
+      </c>
+      <c r="E12" s="3">
         <v>13800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>12800</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>12900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>12100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>10500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>12100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>12300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>15300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>16100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>15700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>15200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>12300</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>10600</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>9700</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>7900</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>6300</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>6000</v>
-      </c>
-      <c r="U12" s="3">
-        <v>6200</v>
       </c>
       <c r="V12" s="3">
         <v>6200</v>
       </c>
       <c r="W12" s="3">
+        <v>6200</v>
+      </c>
+      <c r="X12" s="3">
         <v>8200</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>6900</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1124,38 +1141,41 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" s="3">
         <v>14800</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>400</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I14" s="3">
         <v>8200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-7700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>1600</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>1000</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="M14" s="3" t="s">
         <v>10</v>
       </c>
@@ -1165,64 +1185,67 @@
       <c r="O14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="S14" s="3">
-        <v>0</v>
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="T14" s="3">
         <v>0</v>
       </c>
       <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
         <v>-1100</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
-      </c>
       <c r="W14" s="3">
         <v>0</v>
       </c>
       <c r="X14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>900</v>
+      </c>
+      <c r="E15" s="3">
         <v>500</v>
-      </c>
-      <c r="E15" s="3">
-        <v>1000</v>
       </c>
       <c r="F15" s="3">
         <v>1000</v>
       </c>
       <c r="G15" s="3">
+        <v>1000</v>
+      </c>
+      <c r="H15" s="3">
         <v>1100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1100</v>
-      </c>
-      <c r="J15" s="3">
-        <v>1000</v>
       </c>
       <c r="K15" s="3">
         <v>1000</v>
       </c>
       <c r="L15" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="M15" s="3">
         <v>0</v>
@@ -1260,8 +1283,11 @@
       <c r="X15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1283,144 +1309,151 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>49300</v>
+      </c>
+      <c r="E17" s="3">
         <v>48300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>47000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>48000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>47900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>35200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>45500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>49700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>54400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>52600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>54500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>53700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>46200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>42800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>38900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>32500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>24000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>22100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>20900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>21000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>26900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>22500</v>
       </c>
     </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-12600</v>
+      </c>
+      <c r="E18" s="3">
         <v>-11300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-10700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-12000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-12300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-10600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-15400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-21300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-20100</v>
-      </c>
-      <c r="M18" s="3">
-        <v>-20000</v>
       </c>
       <c r="N18" s="3">
         <v>-20000</v>
       </c>
       <c r="O18" s="3">
+        <v>-20000</v>
+      </c>
+      <c r="P18" s="3">
         <v>-11700</v>
-      </c>
-      <c r="P18" s="3">
-        <v>-9000</v>
       </c>
       <c r="Q18" s="3">
         <v>-9000</v>
       </c>
       <c r="R18" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="S18" s="3">
         <v>-3000</v>
-      </c>
-      <c r="S18" s="3">
-        <v>-2900</v>
       </c>
       <c r="T18" s="3">
         <v>-2900</v>
       </c>
       <c r="U18" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="V18" s="3">
         <v>-3000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-5300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-11200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-8300</v>
       </c>
     </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1445,20 +1478,21 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E20" s="3">
+      <c r="E20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F20" s="3">
         <v>-200</v>
       </c>
-      <c r="F20" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="G20" s="3" t="s">
         <v>10</v>
       </c>
@@ -1468,32 +1502,32 @@
       <c r="I20" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
+      <c r="J20" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
       </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>1500</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>-200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-100</v>
-      </c>
-      <c r="P20" s="3">
-        <v>-200</v>
       </c>
       <c r="Q20" s="3">
         <v>-200</v>
       </c>
       <c r="R20" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="S20" s="3">
         <v>0</v>
@@ -1502,116 +1536,122 @@
         <v>0</v>
       </c>
       <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>-200</v>
-      </c>
-      <c r="V20" s="3">
-        <v>-100</v>
       </c>
       <c r="W20" s="3">
         <v>-100</v>
       </c>
       <c r="X20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Y20" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-11700</v>
+      </c>
+      <c r="E21" s="3">
         <v>-10800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-9600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-11000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-11300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-9500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-14400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-20300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-17700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-19100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-19400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-11400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-8700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-8800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-2600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-2500</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="V21" s="3">
+      <c r="V21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="W21" s="3">
         <v>-4700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-10800</v>
       </c>
-      <c r="X21" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y21" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
+      <c r="D22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E22" s="3">
         <v>500</v>
       </c>
-      <c r="E22" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F22" s="3">
+      <c r="F22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G22" s="3">
         <v>100</v>
       </c>
-      <c r="G22" s="3">
-        <v>200</v>
-      </c>
-      <c r="H22" s="3">
+      <c r="H22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I22" s="3">
         <v>-100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>300</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="K22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1649,84 +1689,90 @@
       <c r="X22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-11300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-25200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-9000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-10700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-10500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-5600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-1000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-14900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-20300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-18600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-20000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-20100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-11800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-9100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-9200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-3000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-2900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-3000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-3200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-5500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-11200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-8200</v>
       </c>
     </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F24" s="3">
         <v>100</v>
@@ -1735,23 +1781,23 @@
         <v>100</v>
       </c>
       <c r="H24" s="3">
+        <v>100</v>
+      </c>
+      <c r="I24" s="3">
         <v>300</v>
-      </c>
-      <c r="I24" s="3">
-        <v>100</v>
       </c>
       <c r="J24" s="3">
         <v>100</v>
       </c>
       <c r="K24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
         <v>100</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
       <c r="N24" s="3">
         <v>0</v>
       </c>
@@ -1785,8 +1831,11 @@
       <c r="X24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1853,144 +1902,153 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-11400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-25200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-9200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-10800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-10600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-5800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-1000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-14900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-20400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-18700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-20100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-20200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-11800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-9100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-9200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-3100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-2900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-3000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-3200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-5500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-11200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-8200</v>
       </c>
     </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-11400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-25200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-9200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-10800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-10600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-5800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-1000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-14900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-20400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-18700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-20100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-20200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-11800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-9100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-9200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-3100</v>
-      </c>
-      <c r="S27" s="3">
-        <v>-3000</v>
       </c>
       <c r="T27" s="3">
         <v>-3000</v>
       </c>
       <c r="U27" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="V27" s="3">
         <v>-3200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-5500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-11300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-8200</v>
       </c>
     </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2057,8 +2115,11 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2125,8 +2186,11 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2193,8 +2257,11 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2261,20 +2328,23 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E32" s="3">
+      <c r="E32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F32" s="3">
         <v>200</v>
       </c>
-      <c r="F32" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="G32" s="3" t="s">
         <v>10</v>
       </c>
@@ -2284,32 +2354,32 @@
       <c r="I32" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
+      <c r="J32" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>
       </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>-1500</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>100</v>
-      </c>
-      <c r="P32" s="3">
-        <v>200</v>
       </c>
       <c r="Q32" s="3">
         <v>200</v>
       </c>
       <c r="R32" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="S32" s="3">
         <v>0</v>
@@ -2318,87 +2388,93 @@
         <v>0</v>
       </c>
       <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>200</v>
-      </c>
-      <c r="V32" s="3">
-        <v>100</v>
       </c>
       <c r="W32" s="3">
         <v>100</v>
       </c>
       <c r="X32" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y32" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-11400</v>
+      </c>
+      <c r="E33" s="3">
         <v>-25200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-9200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-10800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-10600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-5800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-1000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-14900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-20400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-18700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-20100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-20200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-11800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-9100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-9200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-3100</v>
-      </c>
-      <c r="S33" s="3">
-        <v>-3000</v>
       </c>
       <c r="T33" s="3">
         <v>-3000</v>
       </c>
       <c r="U33" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="V33" s="3">
         <v>-3200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-5500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-11300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-8200</v>
       </c>
     </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2465,149 +2541,158 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-11400</v>
+      </c>
+      <c r="E35" s="3">
         <v>-25200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-9200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-10800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-10600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-5800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-1000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-14900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-20400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-18700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-20100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-20200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-11800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-9100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-9200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-3100</v>
-      </c>
-      <c r="S35" s="3">
-        <v>-3000</v>
       </c>
       <c r="T35" s="3">
         <v>-3000</v>
       </c>
       <c r="U35" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="V35" s="3">
         <v>-3200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-5500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-11300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-8200</v>
       </c>
     </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
     </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2632,8 +2717,9 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2658,62 +2744,63 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>34500</v>
+      </c>
+      <c r="E41" s="3">
         <v>52800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>76500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>130000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>148700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>159600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>157700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>178900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>187600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>203200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>213100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>228200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>238600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>255500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>258500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>47000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>53600</v>
       </c>
-      <c r="T41" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="U41" s="3" t="s">
         <v>10</v>
       </c>
@@ -2726,20 +2813,23 @@
       <c r="X41" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y41" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>84300</v>
+      </c>
+      <c r="E42" s="3">
         <v>76400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>50200</v>
       </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
       <c r="G42" s="3">
         <v>0</v>
       </c>
@@ -2794,62 +2884,65 @@
       <c r="X42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>22300</v>
+      </c>
+      <c r="E43" s="3">
         <v>23100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>24000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>25300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>24500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>27000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>27100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>24600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>23900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>22700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>22200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>24300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>24900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>20700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>23200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>21200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>15000</v>
       </c>
-      <c r="T43" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="U43" s="3" t="s">
         <v>10</v>
       </c>
@@ -2862,8 +2955,11 @@
       <c r="X43" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y43" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2891,8 +2987,8 @@
       <c r="K44" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -2930,8 +3026,11 @@
       <c r="X44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2950,42 +3049,42 @@
       <c r="H45" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I45" s="3">
+      <c r="I45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J45" s="3">
         <v>6300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>3700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>4900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>5600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>6400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>3700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>4600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>6600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>4300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1400</v>
       </c>
-      <c r="T45" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="U45" s="3" t="s">
         <v>10</v>
       </c>
@@ -2998,62 +3097,65 @@
       <c r="X45" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y45" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>145600</v>
+      </c>
+      <c r="E46" s="3">
         <v>156900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>157100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>160200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>178600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>192300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>191000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>207200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>216400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>231500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>241800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>255400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>267200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>280900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>288200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>72600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>70000</v>
       </c>
-      <c r="T46" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="U46" s="3" t="s">
         <v>10</v>
       </c>
@@ -3066,8 +3168,11 @@
       <c r="X46" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y46" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3095,8 +3200,8 @@
       <c r="K47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -3134,62 +3239,65 @@
       <c r="X47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>15400</v>
+      </c>
+      <c r="E48" s="3">
         <v>10500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>16100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>16600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>17400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>11000</v>
-      </c>
-      <c r="I48" s="3">
-        <v>17800</v>
       </c>
       <c r="J48" s="3">
         <v>17800</v>
       </c>
       <c r="K48" s="3">
+        <v>17800</v>
+      </c>
+      <c r="L48" s="3">
         <v>17400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>17300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>17800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>18200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>6500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>6200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>6100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>5900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>5600</v>
       </c>
-      <c r="T48" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="U48" s="3" t="s">
         <v>10</v>
       </c>
@@ -3202,50 +3310,53 @@
       <c r="X48" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y48" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E49" s="3">
         <v>12100</v>
-      </c>
-      <c r="E49" s="3">
-        <v>20400</v>
       </c>
       <c r="F49" s="3">
         <v>20400</v>
       </c>
       <c r="G49" s="3">
+        <v>20400</v>
+      </c>
+      <c r="H49" s="3">
         <v>20500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>27400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>20600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>6700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>6800</v>
-      </c>
-      <c r="L49" s="3">
-        <v>6900</v>
       </c>
       <c r="M49" s="3">
         <v>6900</v>
       </c>
       <c r="N49" s="3">
+        <v>6900</v>
+      </c>
+      <c r="O49" s="3">
         <v>7000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>7100</v>
       </c>
-      <c r="P49" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Q49" s="3" t="s">
         <v>10</v>
       </c>
@@ -3258,8 +3369,8 @@
       <c r="T49" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="U49" s="3">
-        <v>0</v>
+      <c r="U49" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="V49" s="3">
         <v>0</v>
@@ -3270,8 +3381,11 @@
       <c r="X49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3338,8 +3452,11 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3406,8 +3523,11 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3427,7 +3547,7 @@
         <v>800</v>
       </c>
       <c r="I52" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="J52" s="3">
         <v>700</v>
@@ -3436,22 +3556,22 @@
         <v>700</v>
       </c>
       <c r="L52" s="3">
+        <v>700</v>
+      </c>
+      <c r="M52" s="3">
         <v>600</v>
-      </c>
-      <c r="M52" s="3">
-        <v>700</v>
       </c>
       <c r="N52" s="3">
         <v>700</v>
       </c>
       <c r="O52" s="3">
-        <v>400</v>
+        <v>700</v>
       </c>
       <c r="P52" s="3">
         <v>400</v>
       </c>
       <c r="Q52" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="R52" s="3">
         <v>500</v>
@@ -3459,8 +3579,8 @@
       <c r="S52" s="3">
         <v>500</v>
       </c>
-      <c r="T52" s="3" t="s">
-        <v>10</v>
+      <c r="T52" s="3">
+        <v>500</v>
       </c>
       <c r="U52" s="3" t="s">
         <v>10</v>
@@ -3474,8 +3594,11 @@
       <c r="X52" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y52" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3542,62 +3665,65 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>168000</v>
+      </c>
+      <c r="E54" s="3">
         <v>180300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>194400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>198000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>217300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>231500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>230200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>232400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>241300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>256300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>267200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>281300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>281100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>287400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>294800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>78900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>76200</v>
       </c>
-      <c r="T54" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="U54" s="3" t="s">
         <v>10</v>
       </c>
@@ -3610,8 +3736,11 @@
       <c r="X54" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y54" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3636,8 +3765,9 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3662,62 +3792,63 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E57" s="3">
         <v>4000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>4000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>5200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>6500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>5100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>6500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>8500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>6800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>8600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>7500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>4700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>8000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>6100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>4300</v>
       </c>
-      <c r="T57" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="U57" s="3" t="s">
         <v>10</v>
       </c>
@@ -3730,37 +3861,40 @@
       <c r="X57" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y57" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E58" s="3">
         <v>2300</v>
-      </c>
-      <c r="E58" s="3">
-        <v>1900</v>
       </c>
       <c r="F58" s="3">
         <v>1900</v>
       </c>
       <c r="G58" s="3">
+        <v>1900</v>
+      </c>
+      <c r="H58" s="3">
         <v>2000</v>
-      </c>
-      <c r="H58" s="3">
-        <v>1900</v>
       </c>
       <c r="I58" s="3">
         <v>1900</v>
       </c>
       <c r="J58" s="3">
-        <v>2000</v>
+        <v>1900</v>
       </c>
       <c r="K58" s="3">
         <v>2000</v>
       </c>
       <c r="L58" s="3">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="M58" s="3">
         <v>0</v>
@@ -3769,7 +3903,7 @@
         <v>0</v>
       </c>
       <c r="O58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P58" s="3">
         <v>100</v>
@@ -3783,8 +3917,8 @@
       <c r="S58" s="3">
         <v>100</v>
       </c>
-      <c r="T58" s="3" t="s">
-        <v>10</v>
+      <c r="T58" s="3">
+        <v>100</v>
       </c>
       <c r="U58" s="3" t="s">
         <v>10</v>
@@ -3798,62 +3932,65 @@
       <c r="X58" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E59" s="3">
         <v>4300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>3500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>4000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>3500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>4300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>3000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>3400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>4300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>14200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>15400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>14300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>12000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>13900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>12700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>10200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>7500</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="U59" s="3" t="s">
         <v>10</v>
       </c>
@@ -3866,62 +4003,65 @@
       <c r="X59" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y59" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>19400</v>
+      </c>
+      <c r="E60" s="3">
         <v>25700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>21000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>20500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>17000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>23100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>21100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>20000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>20400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>22800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>22300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>22900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>19600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>18600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>20700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>16500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>11900</v>
       </c>
-      <c r="T60" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="U60" s="3" t="s">
         <v>10</v>
       </c>
@@ -3934,37 +4074,40 @@
       <c r="X60" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y60" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E61" s="3">
         <v>7000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>5900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>6400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>6900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>7300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>7700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>8100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>8600</v>
-      </c>
-      <c r="L61" s="3">
-        <v>200</v>
       </c>
       <c r="M61" s="3">
         <v>200</v>
@@ -3973,7 +4116,7 @@
         <v>200</v>
       </c>
       <c r="O61" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="P61" s="3">
         <v>0</v>
@@ -3985,11 +4128,11 @@
         <v>0</v>
       </c>
       <c r="S61" s="3">
+        <v>0</v>
+      </c>
+      <c r="T61" s="3">
         <v>100</v>
       </c>
-      <c r="T61" s="3">
-        <v>0</v>
-      </c>
       <c r="U61" s="3">
         <v>0</v>
       </c>
@@ -4002,8 +4145,11 @@
       <c r="X61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4011,53 +4157,53 @@
         <v>100</v>
       </c>
       <c r="E62" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F62" s="3">
         <v>200</v>
       </c>
       <c r="G62" s="3">
+        <v>200</v>
+      </c>
+      <c r="H62" s="3">
         <v>300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>800</v>
-      </c>
-      <c r="I62" s="3">
-        <v>400</v>
       </c>
       <c r="J62" s="3">
         <v>400</v>
       </c>
       <c r="K62" s="3">
+        <v>400</v>
+      </c>
+      <c r="L62" s="3">
         <v>500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>9700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>9900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>10300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>700</v>
-      </c>
-      <c r="P62" s="3">
-        <v>100</v>
       </c>
       <c r="Q62" s="3">
         <v>100</v>
       </c>
       <c r="R62" s="3">
+        <v>100</v>
+      </c>
+      <c r="S62" s="3">
         <v>400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>600</v>
       </c>
-      <c r="T62" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="U62" s="3" t="s">
         <v>10</v>
       </c>
@@ -4070,8 +4216,11 @@
       <c r="X62" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y62" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4138,8 +4287,11 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4206,8 +4358,11 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4274,62 +4429,65 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>25900</v>
+      </c>
+      <c r="E66" s="3">
         <v>32800</v>
-      </c>
-      <c r="E66" s="3">
-        <v>27100</v>
       </c>
       <c r="F66" s="3">
         <v>27100</v>
       </c>
       <c r="G66" s="3">
+        <v>27100</v>
+      </c>
+      <c r="H66" s="3">
         <v>24100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>31200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>29200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>28500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>29500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>32700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>32400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>33500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>20200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>18700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>20800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>16900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>12600</v>
       </c>
-      <c r="T66" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="U66" s="3" t="s">
         <v>10</v>
       </c>
@@ -4342,8 +4500,11 @@
       <c r="X66" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y66" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4368,8 +4529,9 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4436,8 +4598,11 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4504,8 +4669,11 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4552,14 +4720,14 @@
         <v>0</v>
       </c>
       <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3">
         <v>160900</v>
       </c>
-      <c r="S70" s="3">
+      <c r="T70" s="3">
         <v>160800</v>
       </c>
-      <c r="T70" s="3">
-        <v>0</v>
-      </c>
       <c r="U70" s="3">
         <v>0</v>
       </c>
@@ -4572,8 +4740,11 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4640,62 +4811,65 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-308800</v>
+      </c>
+      <c r="E72" s="3">
         <v>-297400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-272200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-263100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-251200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-240400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-234500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-233500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-218600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-198200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-179500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-159500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-139300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-127500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-118400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-109100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-106000</v>
       </c>
-      <c r="T72" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="U72" s="3" t="s">
         <v>10</v>
       </c>
@@ -4708,8 +4882,11 @@
       <c r="X72" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y72" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4776,8 +4953,11 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4844,8 +5024,11 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4912,62 +5095,65 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>142200</v>
+      </c>
+      <c r="E76" s="3">
         <v>147500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>167300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>170900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>193200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>200300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>201000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>203900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>211800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>223600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>234800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>247800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>260800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>268700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>274000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-98800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-97200</v>
       </c>
-      <c r="T76" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="U76" s="3" t="s">
         <v>10</v>
       </c>
@@ -4980,8 +5166,11 @@
       <c r="X76" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y76" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5048,149 +5237,158 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
     </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-11400</v>
+      </c>
+      <c r="E81" s="3">
         <v>-25200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-9200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-10800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-10600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-5800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-1000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-14900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-20400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-18700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-20100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-20200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-11800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-9100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-9200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-3100</v>
-      </c>
-      <c r="S81" s="3">
-        <v>-3000</v>
       </c>
       <c r="T81" s="3">
         <v>-3000</v>
       </c>
       <c r="U81" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="V81" s="3">
         <v>-3200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-5500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-11300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-8200</v>
       </c>
     </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5215,49 +5413,50 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E83" s="3">
         <v>-600</v>
-      </c>
-      <c r="E83" s="3">
-        <v>1000</v>
       </c>
       <c r="F83" s="3">
         <v>1000</v>
       </c>
       <c r="G83" s="3">
+        <v>1000</v>
+      </c>
+      <c r="H83" s="3">
         <v>900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>-300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>500</v>
-      </c>
-      <c r="L83" s="3">
-        <v>900</v>
       </c>
       <c r="M83" s="3">
         <v>900</v>
       </c>
       <c r="N83" s="3">
+        <v>900</v>
+      </c>
+      <c r="O83" s="3">
         <v>700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>500</v>
-      </c>
-      <c r="P83" s="3">
-        <v>400</v>
       </c>
       <c r="Q83" s="3">
         <v>400</v>
@@ -5268,23 +5467,26 @@
       <c r="S83" s="3">
         <v>400</v>
       </c>
-      <c r="T83" s="3" t="s">
-        <v>10</v>
+      <c r="T83" s="3">
+        <v>400</v>
       </c>
       <c r="U83" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="V83" s="3">
+      <c r="V83" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="W83" s="3">
         <v>800</v>
       </c>
-      <c r="W83" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="X83" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y83" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5351,8 +5553,11 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5419,8 +5624,11 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5487,8 +5695,11 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5555,8 +5766,11 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5623,76 +5837,82 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-10500</v>
+      </c>
+      <c r="E89" s="3">
         <v>2100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-2900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-7300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>3200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-6900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-7100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-14800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-9400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-14500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-10800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-11400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-2800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-8600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-5700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-4500</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="U89" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="V89" s="3">
+      <c r="V89" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="W89" s="3">
         <v>-15100</v>
       </c>
-      <c r="W89" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="X89" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y89" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5717,76 +5937,80 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-900</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-700</v>
       </c>
       <c r="G91" s="3">
         <v>-700</v>
       </c>
       <c r="H91" s="3">
+        <v>-700</v>
+      </c>
+      <c r="I91" s="3">
         <v>-1300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-800</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>-900</v>
       </c>
       <c r="R91" s="3">
         <v>-900</v>
       </c>
       <c r="S91" s="3">
+        <v>-900</v>
+      </c>
+      <c r="T91" s="3">
         <v>-600</v>
       </c>
-      <c r="T91" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="U91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="V91" s="3">
+      <c r="V91" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="W91" s="3">
         <v>-1000</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="X91" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y91" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5853,8 +6077,11 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5921,76 +6148,82 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-7700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-25900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-50800</v>
-      </c>
-      <c r="F94" s="3">
-        <v>-700</v>
       </c>
       <c r="G94" s="3">
         <v>-700</v>
       </c>
       <c r="H94" s="3">
+        <v>-700</v>
+      </c>
+      <c r="I94" s="3">
         <v>-1300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-15100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-5900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-800</v>
-      </c>
-      <c r="Q94" s="3">
-        <v>-900</v>
       </c>
       <c r="R94" s="3">
         <v>-900</v>
       </c>
       <c r="S94" s="3">
+        <v>-900</v>
+      </c>
+      <c r="T94" s="3">
         <v>-600</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="U94" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="V94" s="3">
+      <c r="V94" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="W94" s="3">
         <v>-1000</v>
       </c>
-      <c r="W94" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="X94" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y94" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6015,8 +6248,9 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6044,8 +6278,8 @@
       <c r="K96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -6083,8 +6317,11 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6151,8 +6388,11 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6219,8 +6459,11 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6287,76 +6530,82 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
         <v>200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-17400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-2900</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>700</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>1200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>1300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>221000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>100</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="U100" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="V100" s="3">
+      <c r="V100" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="W100" s="3">
         <v>16900</v>
       </c>
-      <c r="W100" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="X100" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y100" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6384,8 +6633,8 @@
       <c r="K101" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -6423,72 +6672,78 @@
       <c r="X101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-18200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-23800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-53500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-18700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-10900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-21300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-8700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-15600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-9900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-15100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-10400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-16900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-3000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>211500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-6600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-4900</v>
       </c>
-      <c r="T102" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="U102" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="V102" s="3">
+      <c r="V102" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="W102" s="3">
         <v>800</v>
       </c>
-      <c r="W102" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="X102" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y102" s="3" t="s">
         <v>10</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LAW_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LAW_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="92">
   <si>
     <t>LAW</t>
   </si>
@@ -656,327 +656,340 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>38100</v>
+      </c>
+      <c r="E8" s="3">
         <v>36700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>37000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>36300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>36000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>35600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>35700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>34900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>34300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>33100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>32500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>34500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>33700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>34500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>33800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>29900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>29500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>21100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>19200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>17900</v>
-      </c>
-      <c r="W8" s="3">
-        <v>15700</v>
       </c>
       <c r="X8" s="3">
         <v>15700</v>
       </c>
       <c r="Y8" s="3">
+        <v>15700</v>
+      </c>
+      <c r="Z8" s="3">
         <v>14200</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>9500</v>
+        <v>9700</v>
       </c>
       <c r="E9" s="3">
         <v>9500</v>
       </c>
       <c r="F9" s="3">
+        <v>9500</v>
+      </c>
+      <c r="G9" s="3">
         <v>9700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>9300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>8900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>8700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>8900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>9000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>8300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>8100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>8600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>8500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>9000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>8800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>7800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>8700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>5800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>5300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>5500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>4500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>5100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>4600</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>28400</v>
+      </c>
+      <c r="E10" s="3">
         <v>27200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>27500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>26500</v>
-      </c>
-      <c r="G10" s="3">
-        <v>26700</v>
       </c>
       <c r="H10" s="3">
         <v>26700</v>
       </c>
       <c r="I10" s="3">
+        <v>26700</v>
+      </c>
+      <c r="J10" s="3">
         <v>27000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>26000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>25200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>24900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>24400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>25900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>25200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>25500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>25000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>22100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>20800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>15300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>13900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>12400</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>11200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>10600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>9600</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1002,79 +1015,83 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>14000</v>
+      </c>
+      <c r="E12" s="3">
         <v>14300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>13800</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>12800</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>12900</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>12100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>10500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>12100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>12300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>15300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>16100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>15700</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>15200</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>12300</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>10600</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>9700</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>7900</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>6300</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>6000</v>
-      </c>
-      <c r="V12" s="3">
-        <v>6200</v>
       </c>
       <c r="W12" s="3">
         <v>6200</v>
       </c>
       <c r="X12" s="3">
+        <v>6200</v>
+      </c>
+      <c r="Y12" s="3">
         <v>8200</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>6900</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1144,41 +1161,44 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E14" s="3">
+      <c r="D14" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14" s="3">
         <v>14800</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>400</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J14" s="3">
         <v>8200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-7700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>1600</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>1000</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="N14" s="3" t="s">
         <v>10</v>
       </c>
@@ -1188,35 +1208,38 @@
       <c r="P14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="T14" s="3">
-        <v>0</v>
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="U14" s="3">
         <v>0</v>
       </c>
       <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
         <v>-1100</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
       <c r="X14" s="3">
         <v>0</v>
       </c>
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1224,31 +1247,31 @@
         <v>900</v>
       </c>
       <c r="E15" s="3">
+        <v>900</v>
+      </c>
+      <c r="F15" s="3">
         <v>500</v>
-      </c>
-      <c r="F15" s="3">
-        <v>1000</v>
       </c>
       <c r="G15" s="3">
         <v>1000</v>
       </c>
       <c r="H15" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I15" s="3">
         <v>1100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1100</v>
-      </c>
-      <c r="K15" s="3">
-        <v>1000</v>
       </c>
       <c r="L15" s="3">
         <v>1000</v>
       </c>
       <c r="M15" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="N15" s="3">
         <v>0</v>
@@ -1286,8 +1309,11 @@
       <c r="Y15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1310,150 +1336,157 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>48300</v>
+      </c>
+      <c r="E17" s="3">
         <v>49300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>48300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>47000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>48000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>47900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>35200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>45500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>49700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>54400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>52600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>54500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>53700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>46200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>42800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>38900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>32500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>24000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>22100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>20900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>21000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>26900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>22500</v>
       </c>
     </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="E18" s="3">
         <v>-12600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-11300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-10700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-12000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-12300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-10600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-15400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-21300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-20100</v>
-      </c>
-      <c r="N18" s="3">
-        <v>-20000</v>
       </c>
       <c r="O18" s="3">
         <v>-20000</v>
       </c>
       <c r="P18" s="3">
+        <v>-20000</v>
+      </c>
+      <c r="Q18" s="3">
         <v>-11700</v>
-      </c>
-      <c r="Q18" s="3">
-        <v>-9000</v>
       </c>
       <c r="R18" s="3">
         <v>-9000</v>
       </c>
       <c r="S18" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="T18" s="3">
         <v>-3000</v>
-      </c>
-      <c r="T18" s="3">
-        <v>-2900</v>
       </c>
       <c r="U18" s="3">
         <v>-2900</v>
       </c>
       <c r="V18" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="W18" s="3">
         <v>-3000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-5300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-11200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-8300</v>
       </c>
     </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1479,8 +1512,9 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1490,12 +1524,12 @@
       <c r="E20" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F20" s="3">
+      <c r="F20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G20" s="3">
         <v>-200</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="H20" s="3" t="s">
         <v>10</v>
       </c>
@@ -1505,32 +1539,32 @@
       <c r="J20" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
+      <c r="K20" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="L20" s="3">
         <v>0</v>
       </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>1500</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>-200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-100</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>-200</v>
       </c>
       <c r="R20" s="3">
         <v>-200</v>
       </c>
       <c r="S20" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="T20" s="3">
         <v>0</v>
@@ -1539,122 +1573,128 @@
         <v>0</v>
       </c>
       <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
         <v>-200</v>
-      </c>
-      <c r="W20" s="3">
-        <v>-100</v>
       </c>
       <c r="X20" s="3">
         <v>-100</v>
       </c>
       <c r="Y20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Z20" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-9300</v>
+      </c>
+      <c r="E21" s="3">
         <v>-11700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-10800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-9600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-11000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-11300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-9500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-14400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-20300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-17700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-19100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-19400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-11400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-8700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-8800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-2600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-2500</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="W21" s="3">
+      <c r="W21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="X21" s="3">
         <v>-4700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-10800</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z21" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E22" s="3">
+      <c r="E22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F22" s="3">
         <v>500</v>
       </c>
-      <c r="F22" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G22" s="3">
-        <v>100</v>
+      <c r="G22" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I22" s="3">
+      <c r="I22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J22" s="3">
         <v>-100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>300</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="L22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -1692,90 +1732,96 @@
       <c r="Y22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-10600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-11300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-25200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-9000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-10700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-10500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-5600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-1000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-14900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-20300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-18600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-20000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-20100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-11800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-9100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-9200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-3000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-2900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-3000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-3200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-5500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-11200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-8200</v>
       </c>
     </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>200</v>
+      </c>
+      <c r="E24" s="3">
         <v>100</v>
       </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
       <c r="F24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G24" s="3">
         <v>100</v>
@@ -1784,23 +1830,23 @@
         <v>100</v>
       </c>
       <c r="I24" s="3">
+        <v>100</v>
+      </c>
+      <c r="J24" s="3">
         <v>300</v>
-      </c>
-      <c r="J24" s="3">
-        <v>100</v>
       </c>
       <c r="K24" s="3">
         <v>100</v>
       </c>
       <c r="L24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
         <v>100</v>
       </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
       <c r="O24" s="3">
         <v>0</v>
       </c>
@@ -1834,8 +1880,11 @@
       <c r="Y24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1905,150 +1954,159 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-10800</v>
+      </c>
+      <c r="E26" s="3">
         <v>-11400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-25200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-9200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-10800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-10600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-5800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-1000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-14900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-20400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-18700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-20100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-20200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-11800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-9100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-9200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-3100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-2900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-3000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-3200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-5500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-11200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-8200</v>
       </c>
     </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-10800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-11400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-25200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-9200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-10800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-10600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-5800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-1000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-14900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-20400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-18700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-20100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-20200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-11800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-9100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-9200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-3100</v>
-      </c>
-      <c r="T27" s="3">
-        <v>-3000</v>
       </c>
       <c r="U27" s="3">
         <v>-3000</v>
       </c>
       <c r="V27" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="W27" s="3">
         <v>-3200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-5500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-11300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-8200</v>
       </c>
     </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2118,8 +2176,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2189,8 +2250,11 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2260,8 +2324,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2331,8 +2398,11 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2342,12 +2412,12 @@
       <c r="E32" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F32" s="3">
+      <c r="F32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G32" s="3">
         <v>200</v>
       </c>
-      <c r="G32" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="H32" s="3" t="s">
         <v>10</v>
       </c>
@@ -2357,32 +2427,32 @@
       <c r="J32" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
+      <c r="K32" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="L32" s="3">
         <v>0</v>
       </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>-1500</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>100</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>200</v>
       </c>
       <c r="R32" s="3">
         <v>200</v>
       </c>
       <c r="S32" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="T32" s="3">
         <v>0</v>
@@ -2391,90 +2461,96 @@
         <v>0</v>
       </c>
       <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
         <v>200</v>
-      </c>
-      <c r="W32" s="3">
-        <v>100</v>
       </c>
       <c r="X32" s="3">
         <v>100</v>
       </c>
       <c r="Y32" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z32" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-10800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-11400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-25200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-9200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-10800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-10600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-5800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-1000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-14900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-20400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-18700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-20100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-20200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-11800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-9100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-9200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-3100</v>
-      </c>
-      <c r="T33" s="3">
-        <v>-3000</v>
       </c>
       <c r="U33" s="3">
         <v>-3000</v>
       </c>
       <c r="V33" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="W33" s="3">
         <v>-3200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-5500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-11300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-8200</v>
       </c>
     </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2544,155 +2620,164 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-10800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-11400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-25200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-9200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-10800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-10600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-5800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-1000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-14900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-20400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-18700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-20100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-20200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-11800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-9100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-9200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-3100</v>
-      </c>
-      <c r="T35" s="3">
-        <v>-3000</v>
       </c>
       <c r="U35" s="3">
         <v>-3000</v>
       </c>
       <c r="V35" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="W35" s="3">
         <v>-3200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-5500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-11300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-8200</v>
       </c>
     </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
     </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2718,8 +2803,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2745,65 +2831,66 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>21700</v>
+      </c>
+      <c r="E41" s="3">
         <v>34500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>52800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>76500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>130000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>148700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>159600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>157700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>178900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>187600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>203200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>213100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>228200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>238600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>255500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>258500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>47000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>53600</v>
       </c>
-      <c r="U41" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="V41" s="3" t="s">
         <v>10</v>
       </c>
@@ -2816,23 +2903,26 @@
       <c r="Y41" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z41" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>92800</v>
+      </c>
+      <c r="E42" s="3">
         <v>84300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>76400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>50200</v>
       </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
       <c r="H42" s="3">
         <v>0</v>
       </c>
@@ -2887,65 +2977,68 @@
       <c r="Y42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>23900</v>
+      </c>
+      <c r="E43" s="3">
         <v>22300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>23100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>24000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>25300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>24500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>27000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>27100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>24600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>23900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>22700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>22200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>24300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>24900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>20700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>23200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>21200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>15000</v>
       </c>
-      <c r="U43" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="V43" s="3" t="s">
         <v>10</v>
       </c>
@@ -2958,8 +3051,11 @@
       <c r="Y43" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2990,8 +3086,8 @@
       <c r="L44" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -3029,8 +3125,11 @@
       <c r="Y44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3052,42 +3151,42 @@
       <c r="I45" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="J45" s="3">
+      <c r="J45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K45" s="3">
         <v>6300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>3700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>4900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>5600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>6400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>3000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>3700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>4600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>6600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>4300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1400</v>
       </c>
-      <c r="U45" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="V45" s="3" t="s">
         <v>10</v>
       </c>
@@ -3100,65 +3199,68 @@
       <c r="Y45" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>142900</v>
+      </c>
+      <c r="E46" s="3">
         <v>145600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>156900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>157100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>160200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>178600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>192300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>191000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>207200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>216400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>231500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>241800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>255400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>267200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>280900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>288200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>72600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>70000</v>
       </c>
-      <c r="U46" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="V46" s="3" t="s">
         <v>10</v>
       </c>
@@ -3171,8 +3273,11 @@
       <c r="Y46" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3203,8 +3308,8 @@
       <c r="L47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -3242,65 +3347,68 @@
       <c r="Y47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>14900</v>
+      </c>
+      <c r="E48" s="3">
         <v>15400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>10500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>16100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>16600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>17400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>11000</v>
-      </c>
-      <c r="J48" s="3">
-        <v>17800</v>
       </c>
       <c r="K48" s="3">
         <v>17800</v>
       </c>
       <c r="L48" s="3">
+        <v>17800</v>
+      </c>
+      <c r="M48" s="3">
         <v>17400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>17300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>17800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>18200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>6500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>6200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>6100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>5900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>5600</v>
       </c>
-      <c r="U48" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="V48" s="3" t="s">
         <v>10</v>
       </c>
@@ -3313,8 +3421,11 @@
       <c r="Y48" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3322,44 +3433,44 @@
         <v>6200</v>
       </c>
       <c r="E49" s="3">
+        <v>6200</v>
+      </c>
+      <c r="F49" s="3">
         <v>12100</v>
-      </c>
-      <c r="F49" s="3">
-        <v>20400</v>
       </c>
       <c r="G49" s="3">
         <v>20400</v>
       </c>
       <c r="H49" s="3">
+        <v>20400</v>
+      </c>
+      <c r="I49" s="3">
         <v>20500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>27400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>20600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>6700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>6800</v>
-      </c>
-      <c r="M49" s="3">
-        <v>6900</v>
       </c>
       <c r="N49" s="3">
         <v>6900</v>
       </c>
       <c r="O49" s="3">
+        <v>6900</v>
+      </c>
+      <c r="P49" s="3">
         <v>7000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>7100</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="R49" s="3" t="s">
         <v>10</v>
       </c>
@@ -3372,8 +3483,8 @@
       <c r="U49" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="V49" s="3">
-        <v>0</v>
+      <c r="V49" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="W49" s="3">
         <v>0</v>
@@ -3384,8 +3495,11 @@
       <c r="Y49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3455,8 +3569,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3526,8 +3643,11 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3550,7 +3670,7 @@
         <v>800</v>
       </c>
       <c r="J52" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="K52" s="3">
         <v>700</v>
@@ -3559,22 +3679,22 @@
         <v>700</v>
       </c>
       <c r="M52" s="3">
+        <v>700</v>
+      </c>
+      <c r="N52" s="3">
         <v>600</v>
-      </c>
-      <c r="N52" s="3">
-        <v>700</v>
       </c>
       <c r="O52" s="3">
         <v>700</v>
       </c>
       <c r="P52" s="3">
-        <v>400</v>
+        <v>700</v>
       </c>
       <c r="Q52" s="3">
         <v>400</v>
       </c>
       <c r="R52" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="S52" s="3">
         <v>500</v>
@@ -3582,8 +3702,8 @@
       <c r="T52" s="3">
         <v>500</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>10</v>
+      <c r="U52" s="3">
+        <v>500</v>
       </c>
       <c r="V52" s="3" t="s">
         <v>10</v>
@@ -3597,8 +3717,11 @@
       <c r="Y52" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3668,65 +3791,68 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>164900</v>
+      </c>
+      <c r="E54" s="3">
         <v>168000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>180300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>194400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>198000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>217300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>231500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>230200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>232400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>241300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>256300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>267200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>281300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>281100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>287400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>294800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>78900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>76200</v>
       </c>
-      <c r="U54" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="V54" s="3" t="s">
         <v>10</v>
       </c>
@@ -3739,8 +3865,11 @@
       <c r="Y54" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z54" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3766,8 +3895,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3793,65 +3923,66 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E57" s="3">
         <v>5400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>4000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>4000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>5200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>6500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>5100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>6500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>8500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>6800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>8600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>7500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>4700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>8000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>6100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>4300</v>
       </c>
-      <c r="U57" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="V57" s="3" t="s">
         <v>10</v>
       </c>
@@ -3864,40 +3995,43 @@
       <c r="Y57" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z57" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E58" s="3">
         <v>2500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2300</v>
-      </c>
-      <c r="F58" s="3">
-        <v>1900</v>
       </c>
       <c r="G58" s="3">
         <v>1900</v>
       </c>
       <c r="H58" s="3">
+        <v>1900</v>
+      </c>
+      <c r="I58" s="3">
         <v>2000</v>
-      </c>
-      <c r="I58" s="3">
-        <v>1900</v>
       </c>
       <c r="J58" s="3">
         <v>1900</v>
       </c>
       <c r="K58" s="3">
-        <v>2000</v>
+        <v>1900</v>
       </c>
       <c r="L58" s="3">
         <v>2000</v>
       </c>
       <c r="M58" s="3">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="N58" s="3">
         <v>0</v>
@@ -3906,7 +4040,7 @@
         <v>0</v>
       </c>
       <c r="P58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q58" s="3">
         <v>100</v>
@@ -3920,8 +4054,8 @@
       <c r="T58" s="3">
         <v>100</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>10</v>
+      <c r="U58" s="3">
+        <v>100</v>
       </c>
       <c r="V58" s="3" t="s">
         <v>10</v>
@@ -3935,65 +4069,68 @@
       <c r="Y58" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E59" s="3">
         <v>3900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>4300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>3500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>4000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>3500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>4300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>3000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>3400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>4300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>14200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>15400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>14300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>12000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>13900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>12700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>10200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>7500</v>
       </c>
-      <c r="U59" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="V59" s="3" t="s">
         <v>10</v>
       </c>
@@ -4006,65 +4143,68 @@
       <c r="Y59" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z59" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>21200</v>
+      </c>
+      <c r="E60" s="3">
         <v>19400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>25700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>21000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>20500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>17000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>23100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>21100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>20000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>20400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>22800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>22300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>22900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>19600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>18600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>20700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>16500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>11900</v>
       </c>
-      <c r="U60" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="V60" s="3" t="s">
         <v>10</v>
       </c>
@@ -4077,40 +4217,43 @@
       <c r="Y60" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E61" s="3">
         <v>6300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>7000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>5900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>6400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>6900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>7300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>7700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>8100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>8600</v>
-      </c>
-      <c r="M61" s="3">
-        <v>200</v>
       </c>
       <c r="N61" s="3">
         <v>200</v>
@@ -4119,7 +4262,7 @@
         <v>200</v>
       </c>
       <c r="P61" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="Q61" s="3">
         <v>0</v>
@@ -4131,11 +4274,11 @@
         <v>0</v>
       </c>
       <c r="T61" s="3">
+        <v>0</v>
+      </c>
+      <c r="U61" s="3">
         <v>100</v>
       </c>
-      <c r="U61" s="3">
-        <v>0</v>
-      </c>
       <c r="V61" s="3">
         <v>0</v>
       </c>
@@ -4148,8 +4291,11 @@
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4160,53 +4306,53 @@
         <v>100</v>
       </c>
       <c r="F62" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G62" s="3">
         <v>200</v>
       </c>
       <c r="H62" s="3">
+        <v>200</v>
+      </c>
+      <c r="I62" s="3">
         <v>300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>800</v>
-      </c>
-      <c r="J62" s="3">
-        <v>400</v>
       </c>
       <c r="K62" s="3">
         <v>400</v>
       </c>
       <c r="L62" s="3">
+        <v>400</v>
+      </c>
+      <c r="M62" s="3">
         <v>500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>9700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>9900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>10300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>700</v>
-      </c>
-      <c r="Q62" s="3">
-        <v>100</v>
       </c>
       <c r="R62" s="3">
         <v>100</v>
       </c>
       <c r="S62" s="3">
+        <v>100</v>
+      </c>
+      <c r="T62" s="3">
         <v>400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>600</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="V62" s="3" t="s">
         <v>10</v>
       </c>
@@ -4219,8 +4365,11 @@
       <c r="Y62" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4290,8 +4439,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4361,8 +4513,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4432,65 +4587,68 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>27000</v>
+      </c>
+      <c r="E66" s="3">
         <v>25900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>32800</v>
-      </c>
-      <c r="F66" s="3">
-        <v>27100</v>
       </c>
       <c r="G66" s="3">
         <v>27100</v>
       </c>
       <c r="H66" s="3">
+        <v>27100</v>
+      </c>
+      <c r="I66" s="3">
         <v>24100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>31200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>29200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>28500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>29500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>32700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>32400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>33500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>20200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>18700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>20800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>16900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>12600</v>
       </c>
-      <c r="U66" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="V66" s="3" t="s">
         <v>10</v>
       </c>
@@ -4503,8 +4661,11 @@
       <c r="Y66" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z66" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4530,8 +4691,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4601,8 +4763,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4672,8 +4837,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4723,14 +4891,14 @@
         <v>0</v>
       </c>
       <c r="S70" s="3">
+        <v>0</v>
+      </c>
+      <c r="T70" s="3">
         <v>160900</v>
       </c>
-      <c r="T70" s="3">
+      <c r="U70" s="3">
         <v>160800</v>
       </c>
-      <c r="U70" s="3">
-        <v>0</v>
-      </c>
       <c r="V70" s="3">
         <v>0</v>
       </c>
@@ -4743,8 +4911,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4814,65 +4985,68 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-319600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-308800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-297400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-272200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-263100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-251200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-240400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-234500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-233500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-218600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-198200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-179500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-159500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-139300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-127500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-118400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-109100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-106000</v>
       </c>
-      <c r="U72" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="V72" s="3" t="s">
         <v>10</v>
       </c>
@@ -4885,8 +5059,11 @@
       <c r="Y72" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z72" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4956,8 +5133,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5027,8 +5207,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5098,65 +5281,68 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>137900</v>
+      </c>
+      <c r="E76" s="3">
         <v>142200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>147500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>167300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>170900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>193200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>200300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>201000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>203900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>211800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>223600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>234800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>247800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>260800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>268700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>274000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-98800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-97200</v>
       </c>
-      <c r="U76" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="V76" s="3" t="s">
         <v>10</v>
       </c>
@@ -5169,8 +5355,11 @@
       <c r="Y76" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z76" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5240,155 +5429,164 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
     </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-10800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-11400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-25200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-9200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-10800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-10600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-5800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-1000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-14900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-20400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-18700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-20100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-20200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-11800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-9100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-9200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-3100</v>
-      </c>
-      <c r="T81" s="3">
-        <v>-3000</v>
       </c>
       <c r="U81" s="3">
         <v>-3000</v>
       </c>
       <c r="V81" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="W81" s="3">
         <v>-3200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-5500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-11300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-8200</v>
       </c>
     </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5414,8 +5612,9 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5423,43 +5622,43 @@
         <v>1000</v>
       </c>
       <c r="E83" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F83" s="3">
         <v>-600</v>
-      </c>
-      <c r="F83" s="3">
-        <v>1000</v>
       </c>
       <c r="G83" s="3">
         <v>1000</v>
       </c>
       <c r="H83" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I83" s="3">
         <v>900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>-300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>500</v>
-      </c>
-      <c r="M83" s="3">
-        <v>900</v>
       </c>
       <c r="N83" s="3">
         <v>900</v>
       </c>
       <c r="O83" s="3">
+        <v>900</v>
+      </c>
+      <c r="P83" s="3">
         <v>700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>500</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>400</v>
       </c>
       <c r="R83" s="3">
         <v>400</v>
@@ -5470,23 +5669,26 @@
       <c r="T83" s="3">
         <v>400</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>10</v>
+      <c r="U83" s="3">
+        <v>400</v>
       </c>
       <c r="V83" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="W83" s="3">
+      <c r="W83" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="X83" s="3">
         <v>800</v>
       </c>
-      <c r="X83" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Y83" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5556,8 +5758,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5627,8 +5832,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5698,8 +5906,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5769,8 +5980,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5840,79 +6054,85 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="E89" s="3">
         <v>-10500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>2100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-2900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-7300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>3200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-6900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-7100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-14800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-9400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-14500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-10800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-11400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-2800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-8600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-5700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-4500</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="V89" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="W89" s="3">
+      <c r="W89" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="X89" s="3">
         <v>-15100</v>
       </c>
-      <c r="X89" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Y89" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z89" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5938,79 +6158,83 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-900</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-700</v>
       </c>
       <c r="H91" s="3">
         <v>-700</v>
       </c>
       <c r="I91" s="3">
+        <v>-700</v>
+      </c>
+      <c r="J91" s="3">
         <v>-1300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-800</v>
-      </c>
-      <c r="R91" s="3">
-        <v>-900</v>
       </c>
       <c r="S91" s="3">
         <v>-900</v>
       </c>
       <c r="T91" s="3">
+        <v>-900</v>
+      </c>
+      <c r="U91" s="3">
         <v>-600</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="V91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="W91" s="3">
+      <c r="W91" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="X91" s="3">
         <v>-1000</v>
       </c>
-      <c r="X91" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Y91" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6080,8 +6304,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6151,79 +6378,85 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-8600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-7700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-25900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-50800</v>
-      </c>
-      <c r="G94" s="3">
-        <v>-700</v>
       </c>
       <c r="H94" s="3">
         <v>-700</v>
       </c>
       <c r="I94" s="3">
+        <v>-700</v>
+      </c>
+      <c r="J94" s="3">
         <v>-1300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-15100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-5900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-800</v>
-      </c>
-      <c r="R94" s="3">
-        <v>-900</v>
       </c>
       <c r="S94" s="3">
         <v>-900</v>
       </c>
       <c r="T94" s="3">
+        <v>-900</v>
+      </c>
+      <c r="U94" s="3">
         <v>-600</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="V94" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="W94" s="3">
+      <c r="W94" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="X94" s="3">
         <v>-1000</v>
       </c>
-      <c r="X94" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Y94" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z94" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6249,8 +6482,9 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6281,8 +6515,8 @@
       <c r="L96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -6320,8 +6554,11 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6391,8 +6628,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6462,8 +6702,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6533,79 +6776,85 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
         <v>-100</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
       <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-17400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-2900</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>700</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>1200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>221000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>100</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="V100" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="W100" s="3">
+      <c r="W100" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="X100" s="3">
         <v>16900</v>
       </c>
-      <c r="X100" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Y100" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z100" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6636,8 +6885,8 @@
       <c r="L101" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -6675,75 +6924,81 @@
       <c r="Y101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-12900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-18200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-23800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-53500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-18700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-10900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-21300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-8700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-15600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-9900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-15100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-10400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-16900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-3000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>211500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-6600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-4900</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="V102" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="W102" s="3">
+      <c r="W102" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="X102" s="3">
         <v>800</v>
       </c>
-      <c r="X102" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Y102" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z102" s="3" t="s">
         <v>10</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LAW_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LAW_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="92">
   <si>
     <t>LAW</t>
   </si>
@@ -656,276 +656,285 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>41200</v>
+      </c>
+      <c r="E8" s="3">
         <v>40900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>38100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>36700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>37000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>36300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>36000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>35600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>35700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>34900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>34300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>33100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>32500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>34500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>33700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>34500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>33800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>29900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>29500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>21100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>19200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>17900</v>
-      </c>
-      <c r="Y8" s="3">
-        <v>15700</v>
       </c>
       <c r="Z8" s="3">
         <v>15700</v>
       </c>
       <c r="AA8" s="3">
+        <v>15700</v>
+      </c>
+      <c r="AB8" s="3">
         <v>14200</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>10200</v>
+      </c>
+      <c r="E9" s="3">
         <v>10000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>9700</v>
-      </c>
-      <c r="F9" s="3">
-        <v>9500</v>
       </c>
       <c r="G9" s="3">
         <v>9500</v>
       </c>
       <c r="H9" s="3">
+        <v>9500</v>
+      </c>
+      <c r="I9" s="3">
         <v>9700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>9300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>8900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>8700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>8900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>9000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>8300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>8100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>8600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>8500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>9000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>8800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>7800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>8700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>5800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>5300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>5500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>4500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>5100</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>4600</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -933,76 +942,79 @@
         <v>30900</v>
       </c>
       <c r="E10" s="3">
+        <v>30900</v>
+      </c>
+      <c r="F10" s="3">
         <v>28400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>27200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>27500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>26500</v>
-      </c>
-      <c r="I10" s="3">
-        <v>26700</v>
       </c>
       <c r="J10" s="3">
         <v>26700</v>
       </c>
       <c r="K10" s="3">
+        <v>26700</v>
+      </c>
+      <c r="L10" s="3">
         <v>27000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>26000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>25200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>24900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>24400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>25900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>25200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>25500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>25000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>22100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>20800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>15300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>13900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>12400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>11200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>10600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>9600</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1030,85 +1042,89 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E12" s="3">
         <v>13400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>14000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>14300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>13800</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>12800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>12900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>12100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>10500</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>12100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>12300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>15300</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>16100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>15700</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>15200</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>12300</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>10600</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>9700</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>7900</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>6300</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>6000</v>
-      </c>
-      <c r="X12" s="3">
-        <v>6200</v>
       </c>
       <c r="Y12" s="3">
         <v>6200</v>
       </c>
       <c r="Z12" s="3">
+        <v>6200</v>
+      </c>
+      <c r="AA12" s="3">
         <v>8200</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>6900</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1184,47 +1200,50 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
         <v>7000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>1600</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G14" s="3">
-        <v>14800</v>
+      <c r="G14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="H14" s="3">
+        <v>15500</v>
+      </c>
+      <c r="I14" s="3">
         <v>100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>400</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L14" s="3">
         <v>8200</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-7700</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>1600</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>1000</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="P14" s="3" t="s">
         <v>10</v>
       </c>
@@ -1234,40 +1253,43 @@
       <c r="R14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
+      <c r="S14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="T14" s="3">
         <v>0</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="V14" s="3">
-        <v>0</v>
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="W14" s="3">
         <v>0</v>
       </c>
       <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
         <v>-1100</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
       <c r="Z14" s="3">
         <v>0</v>
       </c>
       <c r="AA14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>900</v>
+        <v>400</v>
       </c>
       <c r="E15" s="3">
         <v>900</v>
@@ -1276,31 +1298,31 @@
         <v>900</v>
       </c>
       <c r="G15" s="3">
+        <v>900</v>
+      </c>
+      <c r="H15" s="3">
         <v>500</v>
-      </c>
-      <c r="H15" s="3">
-        <v>1000</v>
       </c>
       <c r="I15" s="3">
         <v>1000</v>
       </c>
       <c r="J15" s="3">
+        <v>1000</v>
+      </c>
+      <c r="K15" s="3">
         <v>1100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>1100</v>
-      </c>
-      <c r="M15" s="3">
-        <v>1000</v>
       </c>
       <c r="N15" s="3">
         <v>1000</v>
       </c>
       <c r="O15" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="P15" s="3">
         <v>0</v>
@@ -1338,8 +1360,11 @@
       <c r="AA15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1364,162 +1389,169 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>50400</v>
+      </c>
+      <c r="E17" s="3">
         <v>48400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>48300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>49300</v>
       </c>
-      <c r="G17" s="3">
-        <v>48300</v>
-      </c>
       <c r="H17" s="3">
+        <v>47600</v>
+      </c>
+      <c r="I17" s="3">
         <v>47000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>48000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>47900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>35200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>45500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>49700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>54400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>52600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>54500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>53700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>46200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>42800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>38900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>32500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>24000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>22100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>20900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>21000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>26900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>22500</v>
       </c>
     </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="E18" s="3">
         <v>-7400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-10200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-12600</v>
       </c>
-      <c r="G18" s="3">
-        <v>-11300</v>
-      </c>
       <c r="H18" s="3">
+        <v>-10600</v>
+      </c>
+      <c r="I18" s="3">
         <v>-10700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-12000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-12300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-10600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-15400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-21300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-20100</v>
-      </c>
-      <c r="P18" s="3">
-        <v>-20000</v>
       </c>
       <c r="Q18" s="3">
         <v>-20000</v>
       </c>
       <c r="R18" s="3">
+        <v>-20000</v>
+      </c>
+      <c r="S18" s="3">
         <v>-11700</v>
-      </c>
-      <c r="S18" s="3">
-        <v>-9000</v>
       </c>
       <c r="T18" s="3">
         <v>-9000</v>
       </c>
       <c r="U18" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="V18" s="3">
         <v>-3000</v>
-      </c>
-      <c r="V18" s="3">
-        <v>-2900</v>
       </c>
       <c r="W18" s="3">
         <v>-2900</v>
       </c>
       <c r="X18" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="Y18" s="3">
         <v>-3000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-5300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-11200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-8300</v>
       </c>
     </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1547,8 +1579,9 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1579,32 +1612,32 @@
       <c r="L20" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
+      <c r="M20" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="N20" s="3">
         <v>0</v>
       </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>1500</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>-200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-100</v>
-      </c>
-      <c r="S20" s="3">
-        <v>-200</v>
       </c>
       <c r="T20" s="3">
         <v>-200</v>
       </c>
       <c r="U20" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="V20" s="3">
         <v>0</v>
@@ -1613,96 +1646,102 @@
         <v>0</v>
       </c>
       <c r="X20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
         <v>-200</v>
-      </c>
-      <c r="Y20" s="3">
-        <v>-100</v>
       </c>
       <c r="Z20" s="3">
         <v>-100</v>
       </c>
       <c r="AA20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AB20" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="E21" s="3">
         <v>-6500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-9300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-11700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
+        <v>-10100</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-9700</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="K21" s="3">
+        <v>-11300</v>
+      </c>
+      <c r="L21" s="3">
+        <v>1100</v>
+      </c>
+      <c r="M21" s="3">
+        <v>-9500</v>
+      </c>
+      <c r="N21" s="3">
+        <v>-14400</v>
+      </c>
+      <c r="O21" s="3">
+        <v>-20300</v>
+      </c>
+      <c r="P21" s="3">
+        <v>-17700</v>
+      </c>
+      <c r="Q21" s="3">
+        <v>-19100</v>
+      </c>
+      <c r="R21" s="3">
+        <v>-19400</v>
+      </c>
+      <c r="S21" s="3">
+        <v>-11400</v>
+      </c>
+      <c r="T21" s="3">
+        <v>-8700</v>
+      </c>
+      <c r="U21" s="3">
+        <v>-8800</v>
+      </c>
+      <c r="V21" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="W21" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="X21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z21" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="AA21" s="3">
         <v>-10800</v>
       </c>
-      <c r="H21" s="3">
-        <v>-9700</v>
-      </c>
-      <c r="I21" s="3">
-        <v>-11000</v>
-      </c>
-      <c r="J21" s="3">
-        <v>-11300</v>
-      </c>
-      <c r="K21" s="3">
-        <v>1100</v>
-      </c>
-      <c r="L21" s="3">
-        <v>-9500</v>
-      </c>
-      <c r="M21" s="3">
-        <v>-14400</v>
-      </c>
-      <c r="N21" s="3">
-        <v>-20300</v>
-      </c>
-      <c r="O21" s="3">
-        <v>-17700</v>
-      </c>
-      <c r="P21" s="3">
-        <v>-19100</v>
-      </c>
-      <c r="Q21" s="3">
-        <v>-19400</v>
-      </c>
-      <c r="R21" s="3">
-        <v>-11400</v>
-      </c>
-      <c r="S21" s="3">
-        <v>-8700</v>
-      </c>
-      <c r="T21" s="3">
-        <v>-8800</v>
-      </c>
-      <c r="U21" s="3">
-        <v>-2600</v>
-      </c>
-      <c r="V21" s="3">
-        <v>-2500</v>
-      </c>
-      <c r="W21" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="X21" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y21" s="3">
-        <v>-4700</v>
-      </c>
-      <c r="Z21" s="3">
-        <v>-10800</v>
-      </c>
-      <c r="AA21" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB21" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1715,8 +1754,8 @@
       <c r="F22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G22" s="3">
-        <v>500</v>
+      <c r="G22" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>10</v>
@@ -1727,20 +1766,20 @@
       <c r="J22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K22" s="3">
+      <c r="K22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L22" s="3">
         <v>-100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>300</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="N22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
@@ -1778,102 +1817,108 @@
       <c r="AA22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="E23" s="3">
         <v>-13500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-10600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-11300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-25200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-9000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-10700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-10500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-5600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-1000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-14900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-20300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-18600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-20000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-20100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-11800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-9100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-9200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-3000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-2900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-3000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-3200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-5500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-11200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-8200</v>
       </c>
     </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>300</v>
+      </c>
+      <c r="E24" s="3">
         <v>100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>100</v>
       </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
       <c r="H24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I24" s="3">
         <v>100</v>
@@ -1882,23 +1927,23 @@
         <v>100</v>
       </c>
       <c r="K24" s="3">
+        <v>100</v>
+      </c>
+      <c r="L24" s="3">
         <v>300</v>
-      </c>
-      <c r="L24" s="3">
-        <v>100</v>
       </c>
       <c r="M24" s="3">
         <v>100</v>
       </c>
       <c r="N24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3">
         <v>100</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
-      </c>
       <c r="Q24" s="3">
         <v>0</v>
       </c>
@@ -1932,8 +1977,11 @@
       <c r="AA24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2009,162 +2057,171 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-8500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-13700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-10800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-11400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-25200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-9200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-10800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-10600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-5800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-1000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-14900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-20400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-18700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-20100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-20200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-11800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-9100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-9200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-3100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-2900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-3000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-3200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-5500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-11200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-8200</v>
       </c>
     </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-8500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-13700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-10800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-11400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-25200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-9200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-10800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-10600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-5800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-1000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-14900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-20400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-18700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-20100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-20200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-11800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-9100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-9200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-3100</v>
-      </c>
-      <c r="V27" s="3">
-        <v>-3000</v>
       </c>
       <c r="W27" s="3">
         <v>-3000</v>
       </c>
       <c r="X27" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="Y27" s="3">
         <v>-3200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-5500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-11300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-8200</v>
       </c>
     </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2240,8 +2297,11 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2317,8 +2377,11 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2394,8 +2457,11 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2471,8 +2537,11 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2503,32 +2572,32 @@
       <c r="L32" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
+      <c r="M32" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="N32" s="3">
         <v>0</v>
       </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>-1500</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>100</v>
-      </c>
-      <c r="S32" s="3">
-        <v>200</v>
       </c>
       <c r="T32" s="3">
         <v>200</v>
       </c>
       <c r="U32" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="V32" s="3">
         <v>0</v>
@@ -2537,96 +2606,102 @@
         <v>0</v>
       </c>
       <c r="X32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
         <v>200</v>
-      </c>
-      <c r="Y32" s="3">
-        <v>100</v>
       </c>
       <c r="Z32" s="3">
         <v>100</v>
       </c>
       <c r="AA32" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB32" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-8500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-13700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-10800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-11400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-25200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-9200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-10800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-10600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-5800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-1000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-14900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-20400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-18700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-20100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-20200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-11800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-9100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-9200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-3100</v>
-      </c>
-      <c r="V33" s="3">
-        <v>-3000</v>
       </c>
       <c r="W33" s="3">
         <v>-3000</v>
       </c>
       <c r="X33" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="Y33" s="3">
         <v>-3200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-5500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-11300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-8200</v>
       </c>
     </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2702,167 +2777,176 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-8500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-13700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-10800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-11400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-25200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-9200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-10800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-10600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-5800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-1000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-14900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-20400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-18700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-20100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-20200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-11800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-9100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-9200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-3100</v>
-      </c>
-      <c r="V35" s="3">
-        <v>-3000</v>
       </c>
       <c r="W35" s="3">
         <v>-3000</v>
       </c>
       <c r="X35" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="Y35" s="3">
         <v>-3200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-5500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-11300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-8200</v>
       </c>
     </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
     </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2890,8 +2974,9 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2919,71 +3004,72 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>19700</v>
+      </c>
+      <c r="E41" s="3">
         <v>28800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>21700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>34500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>52800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>76500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>130000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>148700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>159600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>157700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>178900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>187600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>203200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>213100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>228200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>238600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>255500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>258500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>47000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>53600</v>
       </c>
-      <c r="W41" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="X41" s="3" t="s">
         <v>10</v>
       </c>
@@ -2996,29 +3082,32 @@
       <c r="AA41" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB41" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>94900</v>
+      </c>
+      <c r="E42" s="3">
         <v>84700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>92800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>84300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>76400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>50200</v>
       </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
       <c r="J42" s="3">
         <v>0</v>
       </c>
@@ -3073,71 +3162,74 @@
       <c r="AA42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>33700</v>
+      </c>
+      <c r="E43" s="3">
         <v>33500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>23900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>22300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>23100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>24000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>25300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>24500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>27000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>27100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>24600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>23900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>22700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>22200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>24300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>24900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>20700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>23200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>21200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>15000</v>
       </c>
-      <c r="W43" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="X43" s="3" t="s">
         <v>10</v>
       </c>
@@ -3150,8 +3242,11 @@
       <c r="AA43" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB43" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3188,8 +3283,8 @@
       <c r="N44" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -3227,8 +3322,11 @@
       <c r="AA44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3256,42 +3354,42 @@
       <c r="K45" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M45" s="3">
         <v>6300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>4900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>5600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>6400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>3000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>3700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>4600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>6600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>4300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1400</v>
       </c>
-      <c r="W45" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="X45" s="3" t="s">
         <v>10</v>
       </c>
@@ -3304,71 +3402,74 @@
       <c r="AA45" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB45" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>153000</v>
+      </c>
+      <c r="E46" s="3">
         <v>153100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>142900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>145600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>156900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>157100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>160200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>178600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>192300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>191000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>207200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>216400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>231500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>241800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>255400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>267200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>280900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>288200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>72600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>70000</v>
       </c>
-      <c r="W46" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="X46" s="3" t="s">
         <v>10</v>
       </c>
@@ -3381,8 +3482,11 @@
       <c r="AA46" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB46" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3419,8 +3523,8 @@
       <c r="N47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
@@ -3458,71 +3562,74 @@
       <c r="AA47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E48" s="3">
         <v>14700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>14900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>15400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>10500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>16100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>16600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>17400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>11000</v>
-      </c>
-      <c r="L48" s="3">
-        <v>17800</v>
       </c>
       <c r="M48" s="3">
         <v>17800</v>
       </c>
       <c r="N48" s="3">
+        <v>17800</v>
+      </c>
+      <c r="O48" s="3">
         <v>17400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>17300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>17800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>18200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>6500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>6200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>6100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>5900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>5600</v>
       </c>
-      <c r="W48" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="X48" s="3" t="s">
         <v>10</v>
       </c>
@@ -3535,59 +3642,62 @@
       <c r="AA48" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB48" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>12200</v>
+      </c>
+      <c r="E49" s="3">
         <v>6100</v>
-      </c>
-      <c r="E49" s="3">
-        <v>6200</v>
       </c>
       <c r="F49" s="3">
         <v>6200</v>
       </c>
       <c r="G49" s="3">
+        <v>6200</v>
+      </c>
+      <c r="H49" s="3">
         <v>12100</v>
-      </c>
-      <c r="H49" s="3">
-        <v>20400</v>
       </c>
       <c r="I49" s="3">
         <v>20400</v>
       </c>
       <c r="J49" s="3">
+        <v>20400</v>
+      </c>
+      <c r="K49" s="3">
         <v>20500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>27400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>20600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>6700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>6800</v>
-      </c>
-      <c r="O49" s="3">
-        <v>6900</v>
       </c>
       <c r="P49" s="3">
         <v>6900</v>
       </c>
       <c r="Q49" s="3">
+        <v>6900</v>
+      </c>
+      <c r="R49" s="3">
         <v>7000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>7100</v>
       </c>
-      <c r="S49" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="T49" s="3" t="s">
         <v>10</v>
       </c>
@@ -3600,8 +3710,8 @@
       <c r="W49" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="X49" s="3">
-        <v>0</v>
+      <c r="X49" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Y49" s="3">
         <v>0</v>
@@ -3612,8 +3722,11 @@
       <c r="AA49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3689,8 +3802,11 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3766,8 +3882,11 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3796,7 +3915,7 @@
         <v>800</v>
       </c>
       <c r="L52" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="M52" s="3">
         <v>700</v>
@@ -3805,22 +3924,22 @@
         <v>700</v>
       </c>
       <c r="O52" s="3">
+        <v>700</v>
+      </c>
+      <c r="P52" s="3">
         <v>600</v>
-      </c>
-      <c r="P52" s="3">
-        <v>700</v>
       </c>
       <c r="Q52" s="3">
         <v>700</v>
       </c>
       <c r="R52" s="3">
-        <v>400</v>
+        <v>700</v>
       </c>
       <c r="S52" s="3">
         <v>400</v>
       </c>
       <c r="T52" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="U52" s="3">
         <v>500</v>
@@ -3828,8 +3947,8 @@
       <c r="V52" s="3">
         <v>500</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>10</v>
+      <c r="W52" s="3">
+        <v>500</v>
       </c>
       <c r="X52" s="3" t="s">
         <v>10</v>
@@ -3843,8 +3962,11 @@
       <c r="AA52" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB52" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3920,71 +4042,74 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>173600</v>
+      </c>
+      <c r="E54" s="3">
         <v>174800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>164900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>168000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>180300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>194400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>198000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>217300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>231500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>230200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>232400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>241300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>256300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>267200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>281300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>281100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>287400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>294800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>78900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>76200</v>
       </c>
-      <c r="W54" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="X54" s="3" t="s">
         <v>10</v>
       </c>
@@ -3997,8 +4122,11 @@
       <c r="AA54" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB54" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4026,8 +4154,9 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4055,71 +4184,72 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E57" s="3">
         <v>3500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>5400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>4000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>4000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>5200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>6500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>5100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>6500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>8500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>6800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>8600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>7500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>4700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>8000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>6100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>4300</v>
       </c>
-      <c r="W57" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="X57" s="3" t="s">
         <v>10</v>
       </c>
@@ -4132,46 +4262,49 @@
       <c r="AA57" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB57" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>2600</v>
+        <v>2700</v>
       </c>
       <c r="E58" s="3">
         <v>2600</v>
       </c>
       <c r="F58" s="3">
+        <v>2600</v>
+      </c>
+      <c r="G58" s="3">
         <v>2500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2300</v>
-      </c>
-      <c r="H58" s="3">
-        <v>1900</v>
       </c>
       <c r="I58" s="3">
         <v>1900</v>
       </c>
       <c r="J58" s="3">
+        <v>1900</v>
+      </c>
+      <c r="K58" s="3">
         <v>2000</v>
-      </c>
-      <c r="K58" s="3">
-        <v>1900</v>
       </c>
       <c r="L58" s="3">
         <v>1900</v>
       </c>
       <c r="M58" s="3">
-        <v>2000</v>
+        <v>1900</v>
       </c>
       <c r="N58" s="3">
         <v>2000</v>
       </c>
       <c r="O58" s="3">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="P58" s="3">
         <v>0</v>
@@ -4180,7 +4313,7 @@
         <v>0</v>
       </c>
       <c r="R58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S58" s="3">
         <v>100</v>
@@ -4194,8 +4327,8 @@
       <c r="V58" s="3">
         <v>100</v>
       </c>
-      <c r="W58" s="3" t="s">
-        <v>10</v>
+      <c r="W58" s="3">
+        <v>100</v>
       </c>
       <c r="X58" s="3" t="s">
         <v>10</v>
@@ -4209,71 +4342,74 @@
       <c r="AA58" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E59" s="3">
         <v>4300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>3500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>3900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>4300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>3500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>4000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>3500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>4300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>3000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>3400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>4300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>14200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>15400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>14300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>12000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>13900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>12700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>10200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>7500</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="X59" s="3" t="s">
         <v>10</v>
       </c>
@@ -4286,71 +4422,74 @@
       <c r="AA59" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB59" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>40400</v>
+      </c>
+      <c r="E60" s="3">
         <v>39000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>21200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>19400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>25700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>21000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>20500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>17000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>23100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>21100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>20000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>20400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>22800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>22300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>22900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>19600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>18600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>20700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>16500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>11900</v>
       </c>
-      <c r="W60" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="X60" s="3" t="s">
         <v>10</v>
       </c>
@@ -4363,46 +4502,49 @@
       <c r="AA60" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB60" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E61" s="3">
         <v>5000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>5700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>6300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>7000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>5900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>6400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>6900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>7300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>7700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>8100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>8600</v>
-      </c>
-      <c r="O61" s="3">
-        <v>200</v>
       </c>
       <c r="P61" s="3">
         <v>200</v>
@@ -4411,7 +4553,7 @@
         <v>200</v>
       </c>
       <c r="R61" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="S61" s="3">
         <v>0</v>
@@ -4423,11 +4565,11 @@
         <v>0</v>
       </c>
       <c r="V61" s="3">
+        <v>0</v>
+      </c>
+      <c r="W61" s="3">
         <v>100</v>
       </c>
-      <c r="W61" s="3">
-        <v>0</v>
-      </c>
       <c r="X61" s="3">
         <v>0</v>
       </c>
@@ -4440,13 +4582,16 @@
       <c r="AA61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>100</v>
+        <v>800</v>
       </c>
       <c r="E62" s="3">
         <v>100</v>
@@ -4458,53 +4603,53 @@
         <v>100</v>
       </c>
       <c r="H62" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I62" s="3">
         <v>200</v>
       </c>
       <c r="J62" s="3">
+        <v>200</v>
+      </c>
+      <c r="K62" s="3">
         <v>300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>800</v>
-      </c>
-      <c r="L62" s="3">
-        <v>400</v>
       </c>
       <c r="M62" s="3">
         <v>400</v>
       </c>
       <c r="N62" s="3">
+        <v>400</v>
+      </c>
+      <c r="O62" s="3">
         <v>500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>9700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>9900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>10300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>700</v>
-      </c>
-      <c r="S62" s="3">
-        <v>100</v>
       </c>
       <c r="T62" s="3">
         <v>100</v>
       </c>
       <c r="U62" s="3">
+        <v>100</v>
+      </c>
+      <c r="V62" s="3">
         <v>400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>600</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="X62" s="3" t="s">
         <v>10</v>
       </c>
@@ -4517,8 +4662,11 @@
       <c r="AA62" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB62" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4594,8 +4742,11 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4671,8 +4822,11 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4748,71 +4902,74 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>45500</v>
+      </c>
+      <c r="E66" s="3">
         <v>44100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>27000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>25900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>32800</v>
-      </c>
-      <c r="H66" s="3">
-        <v>27100</v>
       </c>
       <c r="I66" s="3">
         <v>27100</v>
       </c>
       <c r="J66" s="3">
+        <v>27100</v>
+      </c>
+      <c r="K66" s="3">
         <v>24100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>31200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>29200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>28500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>29500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>32700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>32400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>33500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>20200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>18700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>20800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>16900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>12600</v>
       </c>
-      <c r="W66" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="X66" s="3" t="s">
         <v>10</v>
       </c>
@@ -4825,8 +4982,11 @@
       <c r="AA66" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB66" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4854,8 +5014,9 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4931,8 +5092,11 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5008,8 +5172,11 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5065,14 +5232,14 @@
         <v>0</v>
       </c>
       <c r="U70" s="3">
+        <v>0</v>
+      </c>
+      <c r="V70" s="3">
         <v>160900</v>
       </c>
-      <c r="V70" s="3">
+      <c r="W70" s="3">
         <v>160800</v>
       </c>
-      <c r="W70" s="3">
-        <v>0</v>
-      </c>
       <c r="X70" s="3">
         <v>0</v>
       </c>
@@ -5085,8 +5252,11 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5162,71 +5332,74 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-341800</v>
+      </c>
+      <c r="E72" s="3">
         <v>-333300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-319600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-308800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-297400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-272200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-263100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-251200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-240400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-234500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-233500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-218600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-198200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-179500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-159500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-139300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-127500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-118400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-109100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-106000</v>
       </c>
-      <c r="W72" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="X72" s="3" t="s">
         <v>10</v>
       </c>
@@ -5239,8 +5412,11 @@
       <c r="AA72" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB72" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5316,8 +5492,11 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5393,8 +5572,11 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5470,71 +5652,74 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>128100</v>
+      </c>
+      <c r="E76" s="3">
         <v>130600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>137900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>142200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>147500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>167300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>170900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>193200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>200300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>201000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>203900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>211800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>223600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>234800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>247800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>260800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>268700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>274000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-98800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-97200</v>
       </c>
-      <c r="W76" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="X76" s="3" t="s">
         <v>10</v>
       </c>
@@ -5547,8 +5732,11 @@
       <c r="AA76" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB76" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5624,167 +5812,176 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
     </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-8500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-13700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-10800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-11400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-25200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-9200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-10800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-10600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-5800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-1000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-14900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-20400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-18700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-20100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-20200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-11800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-9100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-9200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-3100</v>
-      </c>
-      <c r="V81" s="3">
-        <v>-3000</v>
       </c>
       <c r="W81" s="3">
         <v>-3000</v>
       </c>
       <c r="X81" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="Y81" s="3">
         <v>-3200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-5500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-11300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-8200</v>
       </c>
     </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5812,58 +6009,59 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E83" s="3">
         <v>900</v>
-      </c>
-      <c r="E83" s="3">
-        <v>1000</v>
       </c>
       <c r="F83" s="3">
         <v>1000</v>
       </c>
       <c r="G83" s="3">
+        <v>1000</v>
+      </c>
+      <c r="H83" s="3">
         <v>-600</v>
-      </c>
-      <c r="H83" s="3">
-        <v>1000</v>
       </c>
       <c r="I83" s="3">
         <v>1000</v>
       </c>
       <c r="J83" s="3">
+        <v>1000</v>
+      </c>
+      <c r="K83" s="3">
         <v>900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>-300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>500</v>
-      </c>
-      <c r="O83" s="3">
-        <v>900</v>
       </c>
       <c r="P83" s="3">
         <v>900</v>
       </c>
       <c r="Q83" s="3">
+        <v>900</v>
+      </c>
+      <c r="R83" s="3">
         <v>700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>500</v>
-      </c>
-      <c r="S83" s="3">
-        <v>400</v>
       </c>
       <c r="T83" s="3">
         <v>400</v>
@@ -5874,23 +6072,26 @@
       <c r="V83" s="3">
         <v>400</v>
       </c>
-      <c r="W83" s="3" t="s">
-        <v>10</v>
+      <c r="W83" s="3">
+        <v>400</v>
       </c>
       <c r="X83" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Y83" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z83" s="3">
         <v>800</v>
       </c>
-      <c r="Z83" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AA83" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB83" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5966,8 +6167,11 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6043,8 +6247,11 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6120,8 +6327,11 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6197,8 +6407,11 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6274,85 +6487,91 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>800</v>
+      </c>
+      <c r="E89" s="3">
         <v>-1000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-4200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-10500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>2100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-2900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-7300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>3200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-6900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-7100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-14800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-9400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-14500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-10800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-11400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-2800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-8600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-5700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-4500</v>
       </c>
-      <c r="W89" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="X89" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Y89" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z89" s="3">
         <v>-15100</v>
       </c>
-      <c r="Z89" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AA89" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB89" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6380,85 +6599,89 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-900</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-700</v>
       </c>
       <c r="J91" s="3">
         <v>-700</v>
       </c>
       <c r="K91" s="3">
+        <v>-700</v>
+      </c>
+      <c r="L91" s="3">
         <v>-1300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-800</v>
-      </c>
-      <c r="T91" s="3">
-        <v>-900</v>
       </c>
       <c r="U91" s="3">
         <v>-900</v>
       </c>
       <c r="V91" s="3">
+        <v>-900</v>
+      </c>
+      <c r="W91" s="3">
         <v>-600</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="X91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Y91" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z91" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z91" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AA91" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB91" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6534,8 +6757,11 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6611,85 +6837,91 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-9900</v>
+      </c>
+      <c r="E94" s="3">
         <v>8000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-8600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-7700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-25900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-50800</v>
-      </c>
-      <c r="I94" s="3">
-        <v>-700</v>
       </c>
       <c r="J94" s="3">
         <v>-700</v>
       </c>
       <c r="K94" s="3">
+        <v>-700</v>
+      </c>
+      <c r="L94" s="3">
         <v>-1300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-15100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-2000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-5900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-800</v>
-      </c>
-      <c r="T94" s="3">
-        <v>-900</v>
       </c>
       <c r="U94" s="3">
         <v>-900</v>
       </c>
       <c r="V94" s="3">
+        <v>-900</v>
+      </c>
+      <c r="W94" s="3">
         <v>-600</v>
       </c>
-      <c r="W94" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="X94" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Y94" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z94" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z94" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AA94" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB94" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6717,8 +6949,9 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6755,8 +6988,8 @@
       <c r="N96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -6794,8 +7027,11 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6871,8 +7107,11 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6948,8 +7187,11 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7025,85 +7267,91 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
         <v>200</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
       <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>-100</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
       <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-17400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-2900</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>700</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
       <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>1200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>1600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>221000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>100</v>
       </c>
-      <c r="W100" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="X100" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Y100" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z100" s="3">
         <v>16900</v>
       </c>
-      <c r="Z100" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AA100" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB100" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7140,8 +7388,8 @@
       <c r="N101" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -7179,81 +7427,87 @@
       <c r="AA101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="E102" s="3">
         <v>7100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-12900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-18200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-23800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-53500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-18700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-10900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-21300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-8700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-15600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-9900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-15100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-10400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-16900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-3000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>211500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-6600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-4900</v>
       </c>
-      <c r="W102" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="X102" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Y102" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z102" s="3">
         <v>800</v>
       </c>
-      <c r="Z102" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AA102" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB102" s="3" t="s">
         <v>10</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LAW_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LAW_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="92">
   <si>
     <t>LAW</t>
   </si>
@@ -656,365 +656,378 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AB102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>41900</v>
+      </c>
+      <c r="E8" s="3">
         <v>41200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>40900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>38100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>36700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>37000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>36300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>36000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>35600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>35700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>34900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>34300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>33100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>32500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>34500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>33700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>34500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>33800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>29900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>29500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>21100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>19200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>17900</v>
-      </c>
-      <c r="Z8" s="3">
-        <v>15700</v>
       </c>
       <c r="AA8" s="3">
         <v>15700</v>
       </c>
       <c r="AB8" s="3">
+        <v>15700</v>
+      </c>
+      <c r="AC8" s="3">
         <v>14200</v>
       </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>10800</v>
+      </c>
+      <c r="E9" s="3">
         <v>10200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>10000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>9700</v>
-      </c>
-      <c r="G9" s="3">
-        <v>9500</v>
       </c>
       <c r="H9" s="3">
         <v>9500</v>
       </c>
       <c r="I9" s="3">
+        <v>9500</v>
+      </c>
+      <c r="J9" s="3">
         <v>9700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>9300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>8900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>8700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>8900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>9000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>8300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>8100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>8600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>8500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>9000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>8800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>7800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>8700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>5800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>5300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>5500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>4500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>5100</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>4600</v>
       </c>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>30900</v>
+        <v>31100</v>
       </c>
       <c r="E10" s="3">
         <v>30900</v>
       </c>
       <c r="F10" s="3">
+        <v>30900</v>
+      </c>
+      <c r="G10" s="3">
         <v>28400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>27200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>27500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>26500</v>
-      </c>
-      <c r="J10" s="3">
-        <v>26700</v>
       </c>
       <c r="K10" s="3">
         <v>26700</v>
       </c>
       <c r="L10" s="3">
+        <v>26700</v>
+      </c>
+      <c r="M10" s="3">
         <v>27000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>26000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>25200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>24900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>24400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>25900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>25200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>25500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>25000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>22100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>20800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>15300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>13900</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>12400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>11200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>10600</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>9600</v>
       </c>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1043,88 +1056,92 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>14700</v>
+      </c>
+      <c r="E12" s="3">
         <v>15000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>13400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>14000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>14300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>13800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>12800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>12900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>12100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>10500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>12100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>12300</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>15300</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>16100</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>15700</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>15200</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>12300</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>10600</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>9700</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>7900</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>6300</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>6000</v>
-      </c>
-      <c r="Y12" s="3">
-        <v>6200</v>
       </c>
       <c r="Z12" s="3">
         <v>6200</v>
       </c>
       <c r="AA12" s="3">
+        <v>6200</v>
+      </c>
+      <c r="AB12" s="3">
         <v>8200</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>6900</v>
       </c>
     </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1203,50 +1220,53 @@
       <c r="AB13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
         <v>7000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>1600</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I14" s="3">
         <v>15500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>400</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M14" s="3">
         <v>8200</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-7700</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>1600</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>1000</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Q14" s="3" t="s">
         <v>10</v>
       </c>
@@ -1256,43 +1276,46 @@
       <c r="S14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
+      <c r="T14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="U14" s="3">
         <v>0</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="W14" s="3">
-        <v>0</v>
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="X14" s="3">
         <v>0</v>
       </c>
       <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
         <v>-1100</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
       <c r="AA14" s="3">
         <v>0</v>
       </c>
       <c r="AB14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E15" s="3">
         <v>400</v>
-      </c>
-      <c r="E15" s="3">
-        <v>900</v>
       </c>
       <c r="F15" s="3">
         <v>900</v>
@@ -1301,31 +1324,31 @@
         <v>900</v>
       </c>
       <c r="H15" s="3">
+        <v>900</v>
+      </c>
+      <c r="I15" s="3">
         <v>500</v>
-      </c>
-      <c r="I15" s="3">
-        <v>1000</v>
       </c>
       <c r="J15" s="3">
         <v>1000</v>
       </c>
       <c r="K15" s="3">
+        <v>1000</v>
+      </c>
+      <c r="L15" s="3">
         <v>1100</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>600</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>1100</v>
-      </c>
-      <c r="N15" s="3">
-        <v>1000</v>
       </c>
       <c r="O15" s="3">
         <v>1000</v>
       </c>
       <c r="P15" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Q15" s="3">
         <v>0</v>
@@ -1363,8 +1386,11 @@
       <c r="AB15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1390,168 +1416,175 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
-    </row>
-    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>52000</v>
+      </c>
+      <c r="E17" s="3">
         <v>50400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>48400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>48300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>49300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>47600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>47000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>48000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>47900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>35200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>45500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>49700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>54400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>52600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>54500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>53700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>46200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>42800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>38900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>32500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>24000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>22100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>20900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>21000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>26900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>22500</v>
       </c>
     </row>
-    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-10100</v>
+      </c>
+      <c r="E18" s="3">
         <v>-9200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-7400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-10200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-12600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-10600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-10700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-12000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-12300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-10600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-15400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-21300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-20100</v>
-      </c>
-      <c r="Q18" s="3">
-        <v>-20000</v>
       </c>
       <c r="R18" s="3">
         <v>-20000</v>
       </c>
       <c r="S18" s="3">
+        <v>-20000</v>
+      </c>
+      <c r="T18" s="3">
         <v>-11700</v>
-      </c>
-      <c r="T18" s="3">
-        <v>-9000</v>
       </c>
       <c r="U18" s="3">
         <v>-9000</v>
       </c>
       <c r="V18" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="W18" s="3">
         <v>-3000</v>
-      </c>
-      <c r="W18" s="3">
-        <v>-2900</v>
       </c>
       <c r="X18" s="3">
         <v>-2900</v>
       </c>
       <c r="Y18" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="Z18" s="3">
         <v>-3000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-5300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-11200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-8300</v>
       </c>
     </row>
-    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1580,8 +1613,9 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
-    </row>
-    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1615,32 +1649,32 @@
       <c r="M20" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
+      <c r="N20" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="O20" s="3">
         <v>0</v>
       </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>1500</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>-200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-100</v>
-      </c>
-      <c r="T20" s="3">
-        <v>-200</v>
       </c>
       <c r="U20" s="3">
         <v>-200</v>
       </c>
       <c r="V20" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="W20" s="3">
         <v>0</v>
@@ -1649,99 +1683,105 @@
         <v>0</v>
       </c>
       <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
         <v>-200</v>
-      </c>
-      <c r="Z20" s="3">
-        <v>-100</v>
       </c>
       <c r="AA20" s="3">
         <v>-100</v>
       </c>
       <c r="AB20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AC20" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="E21" s="3">
         <v>-8900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-6500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-9300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-11700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-10100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-9700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-11000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-11300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-9500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-14400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-20300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-17700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-19100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-19400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-11400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-8700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-8800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-2600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-2500</v>
       </c>
-      <c r="X21" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Y21" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="Z21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA21" s="3">
         <v>-4700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-10800</v>
       </c>
-      <c r="AB21" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC21" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1769,20 +1809,20 @@
       <c r="K22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L22" s="3">
+      <c r="L22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M22" s="3">
         <v>-100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>300</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="O22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="P22" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
@@ -1820,108 +1860,114 @@
       <c r="AB22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-9500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-8200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-13500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-10600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-11300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-25200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-9000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-10700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-10500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-5600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-1000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-14900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-20300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-18600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-20000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-20100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-11800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-9100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-9200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-3000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-2900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-3000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-3200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-5500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-11200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-8200</v>
       </c>
     </row>
-    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>100</v>
+      </c>
+      <c r="E24" s="3">
         <v>300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>100</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
       <c r="I24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J24" s="3">
         <v>100</v>
@@ -1930,23 +1976,23 @@
         <v>100</v>
       </c>
       <c r="L24" s="3">
+        <v>100</v>
+      </c>
+      <c r="M24" s="3">
         <v>300</v>
-      </c>
-      <c r="M24" s="3">
-        <v>100</v>
       </c>
       <c r="N24" s="3">
         <v>100</v>
       </c>
       <c r="O24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3">
         <v>100</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
-      </c>
       <c r="R24" s="3">
         <v>0</v>
       </c>
@@ -1980,8 +2026,11 @@
       <c r="AB24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2060,168 +2109,177 @@
       <c r="AB25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-9600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-8500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-13700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-10800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-11400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-25200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-9200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-10800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-10600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-5800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-1000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-14900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-20400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-18700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-20100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-20200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-11800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-9100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-9200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-3100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-2900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-3000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-3200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-5500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-11200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-8200</v>
       </c>
     </row>
-    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-9600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-8500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-13700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-10800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-11400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-25200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-9200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-10800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-10600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-5800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-1000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-14900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-20400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-18700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-20100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-20200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-11800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-9100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-9200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-3100</v>
-      </c>
-      <c r="W27" s="3">
-        <v>-3000</v>
       </c>
       <c r="X27" s="3">
         <v>-3000</v>
       </c>
       <c r="Y27" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="Z27" s="3">
         <v>-3200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-5500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-11300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-8200</v>
       </c>
     </row>
-    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2300,8 +2358,11 @@
       <c r="AB28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2380,8 +2441,11 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2460,8 +2524,11 @@
       <c r="AB30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2540,8 +2607,11 @@
       <c r="AB31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2575,32 +2645,32 @@
       <c r="M32" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
+      <c r="N32" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="O32" s="3">
         <v>0</v>
       </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>100</v>
-      </c>
-      <c r="T32" s="3">
-        <v>200</v>
       </c>
       <c r="U32" s="3">
         <v>200</v>
       </c>
       <c r="V32" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="W32" s="3">
         <v>0</v>
@@ -2609,99 +2679,105 @@
         <v>0</v>
       </c>
       <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
         <v>200</v>
-      </c>
-      <c r="Z32" s="3">
-        <v>100</v>
       </c>
       <c r="AA32" s="3">
         <v>100</v>
       </c>
       <c r="AB32" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC32" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-9600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-8500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-13700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-10800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-11400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-25200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-9200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-10800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-10600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-5800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-1000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-14900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-20400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-18700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-20100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-20200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-11800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-9100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-9200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-3100</v>
-      </c>
-      <c r="W33" s="3">
-        <v>-3000</v>
       </c>
       <c r="X33" s="3">
         <v>-3000</v>
       </c>
       <c r="Y33" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="Z33" s="3">
         <v>-3200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-5500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-11300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-8200</v>
       </c>
     </row>
-    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2780,173 +2856,182 @@
       <c r="AB34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-9600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-8500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-13700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-10800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-11400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-25200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-9200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-10800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-10600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-5800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-1000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-14900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-20400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-18700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-20100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-20200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-11800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-9100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-9200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-3100</v>
-      </c>
-      <c r="W35" s="3">
-        <v>-3000</v>
       </c>
       <c r="X35" s="3">
         <v>-3000</v>
       </c>
       <c r="Y35" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="Z35" s="3">
         <v>-3200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-5500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-11300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-8200</v>
       </c>
     </row>
-    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
     </row>
-    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2975,8 +3060,9 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
-    </row>
-    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3005,74 +3091,75 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
-    </row>
-    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>17600</v>
+      </c>
+      <c r="E41" s="3">
         <v>19700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>28800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>21700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>34500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>52800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>76500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>130000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>148700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>159600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>157700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>178900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>187600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>203200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>213100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>228200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>238600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>255500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>258500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>47000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>53600</v>
       </c>
-      <c r="X41" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Y41" s="3" t="s">
         <v>10</v>
       </c>
@@ -3085,32 +3172,35 @@
       <c r="AB41" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC41" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>85400</v>
+      </c>
+      <c r="E42" s="3">
         <v>94900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>84700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>92800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>84300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>76400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>50200</v>
       </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
       <c r="K42" s="3">
         <v>0</v>
       </c>
@@ -3165,74 +3255,77 @@
       <c r="AB42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>34900</v>
+      </c>
+      <c r="E43" s="3">
         <v>33700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>33500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>23900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>22300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>23100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>24000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>25300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>24500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>27000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>27100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>24600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>23900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>22700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>22200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>24300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>24900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>20700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>23200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>21200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>15000</v>
       </c>
-      <c r="X43" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Y43" s="3" t="s">
         <v>10</v>
       </c>
@@ -3245,8 +3338,11 @@
       <c r="AB43" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC43" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3286,8 +3382,8 @@
       <c r="O44" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="P44" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -3325,8 +3421,11 @@
       <c r="AB44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3357,42 +3456,42 @@
       <c r="L45" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N45" s="3">
         <v>6300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>4900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>5600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>6400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>3000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>3700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>4600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>6600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>4300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1400</v>
       </c>
-      <c r="X45" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Y45" s="3" t="s">
         <v>10</v>
       </c>
@@ -3405,74 +3504,77 @@
       <c r="AB45" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC45" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>142500</v>
+      </c>
+      <c r="E46" s="3">
         <v>153000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>153100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>142900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>145600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>156900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>157100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>160200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>178600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>192300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>191000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>207200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>216400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>231500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>241800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>255400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>267200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>280900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>288200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>72600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>70000</v>
       </c>
-      <c r="X46" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Y46" s="3" t="s">
         <v>10</v>
       </c>
@@ -3485,8 +3587,11 @@
       <c r="AB46" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC46" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3526,8 +3631,8 @@
       <c r="O47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="P47" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -3565,74 +3670,77 @@
       <c r="AB47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>12900</v>
+      </c>
+      <c r="E48" s="3">
         <v>7600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>14700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>14900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>15400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>10500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>16100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>16600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>17400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>11000</v>
-      </c>
-      <c r="M48" s="3">
-        <v>17800</v>
       </c>
       <c r="N48" s="3">
         <v>17800</v>
       </c>
       <c r="O48" s="3">
+        <v>17800</v>
+      </c>
+      <c r="P48" s="3">
         <v>17400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>17300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>17800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>18200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>6500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>6200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>6100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>5900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>5600</v>
       </c>
-      <c r="X48" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Y48" s="3" t="s">
         <v>10</v>
       </c>
@@ -3645,62 +3753,65 @@
       <c r="AB48" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC48" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E49" s="3">
         <v>12200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>6100</v>
-      </c>
-      <c r="F49" s="3">
-        <v>6200</v>
       </c>
       <c r="G49" s="3">
         <v>6200</v>
       </c>
       <c r="H49" s="3">
+        <v>6200</v>
+      </c>
+      <c r="I49" s="3">
         <v>12100</v>
-      </c>
-      <c r="I49" s="3">
-        <v>20400</v>
       </c>
       <c r="J49" s="3">
         <v>20400</v>
       </c>
       <c r="K49" s="3">
+        <v>20400</v>
+      </c>
+      <c r="L49" s="3">
         <v>20500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>27400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>20600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>6700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>6800</v>
-      </c>
-      <c r="P49" s="3">
-        <v>6900</v>
       </c>
       <c r="Q49" s="3">
         <v>6900</v>
       </c>
       <c r="R49" s="3">
+        <v>6900</v>
+      </c>
+      <c r="S49" s="3">
         <v>7000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>7100</v>
       </c>
-      <c r="T49" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="U49" s="3" t="s">
         <v>10</v>
       </c>
@@ -3713,8 +3824,8 @@
       <c r="X49" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Y49" s="3">
-        <v>0</v>
+      <c r="Y49" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Z49" s="3">
         <v>0</v>
@@ -3725,8 +3836,11 @@
       <c r="AB49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3805,8 +3919,11 @@
       <c r="AB50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3885,13 +4002,16 @@
       <c r="AB51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="E52" s="3">
         <v>800</v>
@@ -3918,7 +4038,7 @@
         <v>800</v>
       </c>
       <c r="M52" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="N52" s="3">
         <v>700</v>
@@ -3927,22 +4047,22 @@
         <v>700</v>
       </c>
       <c r="P52" s="3">
+        <v>700</v>
+      </c>
+      <c r="Q52" s="3">
         <v>600</v>
-      </c>
-      <c r="Q52" s="3">
-        <v>700</v>
       </c>
       <c r="R52" s="3">
         <v>700</v>
       </c>
       <c r="S52" s="3">
-        <v>400</v>
+        <v>700</v>
       </c>
       <c r="T52" s="3">
         <v>400</v>
       </c>
       <c r="U52" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="V52" s="3">
         <v>500</v>
@@ -3950,8 +4070,8 @@
       <c r="W52" s="3">
         <v>500</v>
       </c>
-      <c r="X52" s="3" t="s">
-        <v>10</v>
+      <c r="X52" s="3">
+        <v>500</v>
       </c>
       <c r="Y52" s="3" t="s">
         <v>10</v>
@@ -3965,8 +4085,11 @@
       <c r="AB52" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC52" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4045,74 +4168,77 @@
       <c r="AB53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>162400</v>
+      </c>
+      <c r="E54" s="3">
         <v>173600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>174800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>164900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>168000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>180300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>194400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>198000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>217300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>231500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>230200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>232400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>241300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>256300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>267200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>281300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>281100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>287400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>294800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>78900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>76200</v>
       </c>
-      <c r="X54" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Y54" s="3" t="s">
         <v>10</v>
       </c>
@@ -4125,8 +4251,11 @@
       <c r="AB54" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC54" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4155,8 +4284,9 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
-    </row>
-    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4185,74 +4315,75 @@
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
-    </row>
-    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E57" s="3">
         <v>3900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>5400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>4000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>4000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>5200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>6500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>5100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>6500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>8500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>6800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>8600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>7500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>4700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>8000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>6100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>4300</v>
       </c>
-      <c r="X57" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Y57" s="3" t="s">
         <v>10</v>
       </c>
@@ -4265,8 +4396,11 @@
       <c r="AB57" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC57" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4274,40 +4408,40 @@
         <v>2700</v>
       </c>
       <c r="E58" s="3">
-        <v>2600</v>
+        <v>2700</v>
       </c>
       <c r="F58" s="3">
         <v>2600</v>
       </c>
       <c r="G58" s="3">
+        <v>2600</v>
+      </c>
+      <c r="H58" s="3">
         <v>2500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2300</v>
-      </c>
-      <c r="I58" s="3">
-        <v>1900</v>
       </c>
       <c r="J58" s="3">
         <v>1900</v>
       </c>
       <c r="K58" s="3">
+        <v>1900</v>
+      </c>
+      <c r="L58" s="3">
         <v>2000</v>
-      </c>
-      <c r="L58" s="3">
-        <v>1900</v>
       </c>
       <c r="M58" s="3">
         <v>1900</v>
       </c>
       <c r="N58" s="3">
-        <v>2000</v>
+        <v>1900</v>
       </c>
       <c r="O58" s="3">
         <v>2000</v>
       </c>
       <c r="P58" s="3">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="Q58" s="3">
         <v>0</v>
@@ -4316,7 +4450,7 @@
         <v>0</v>
       </c>
       <c r="S58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T58" s="3">
         <v>100</v>
@@ -4330,8 +4464,8 @@
       <c r="W58" s="3">
         <v>100</v>
       </c>
-      <c r="X58" s="3" t="s">
-        <v>10</v>
+      <c r="X58" s="3">
+        <v>100</v>
       </c>
       <c r="Y58" s="3" t="s">
         <v>10</v>
@@ -4345,74 +4479,77 @@
       <c r="AB58" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC58" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E59" s="3">
         <v>5400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>4300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>3500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>3900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>4300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>3500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>4000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>3500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>4300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>3000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>3400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>4300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>14200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>15400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>14300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>12000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>13900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>12700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>10200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>7500</v>
       </c>
-      <c r="X59" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Y59" s="3" t="s">
         <v>10</v>
       </c>
@@ -4425,74 +4562,77 @@
       <c r="AB59" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC59" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>34000</v>
+      </c>
+      <c r="E60" s="3">
         <v>40400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>39000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>21200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>19400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>25700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>21000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>20500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>17000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>23100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>21100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>20000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>20400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>22800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>22300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>22900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>19600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>18600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>20700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>16500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>11900</v>
       </c>
-      <c r="X60" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Y60" s="3" t="s">
         <v>10</v>
       </c>
@@ -4505,49 +4645,52 @@
       <c r="AB60" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC60" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E61" s="3">
         <v>4300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>5000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>5700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>6300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>7000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>5900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>6400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>6900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>7300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>7700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>8100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>8600</v>
-      </c>
-      <c r="P61" s="3">
-        <v>200</v>
       </c>
       <c r="Q61" s="3">
         <v>200</v>
@@ -4556,7 +4699,7 @@
         <v>200</v>
       </c>
       <c r="S61" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="T61" s="3">
         <v>0</v>
@@ -4568,11 +4711,11 @@
         <v>0</v>
       </c>
       <c r="W61" s="3">
+        <v>0</v>
+      </c>
+      <c r="X61" s="3">
         <v>100</v>
       </c>
-      <c r="X61" s="3">
-        <v>0</v>
-      </c>
       <c r="Y61" s="3">
         <v>0</v>
       </c>
@@ -4585,8 +4728,11 @@
       <c r="AB61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4594,7 +4740,7 @@
         <v>800</v>
       </c>
       <c r="E62" s="3">
-        <v>100</v>
+        <v>800</v>
       </c>
       <c r="F62" s="3">
         <v>100</v>
@@ -4606,53 +4752,53 @@
         <v>100</v>
       </c>
       <c r="I62" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="J62" s="3">
         <v>200</v>
       </c>
       <c r="K62" s="3">
+        <v>200</v>
+      </c>
+      <c r="L62" s="3">
         <v>300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>800</v>
-      </c>
-      <c r="M62" s="3">
-        <v>400</v>
       </c>
       <c r="N62" s="3">
         <v>400</v>
       </c>
       <c r="O62" s="3">
+        <v>400</v>
+      </c>
+      <c r="P62" s="3">
         <v>500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>9700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>9900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>10300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>700</v>
-      </c>
-      <c r="T62" s="3">
-        <v>100</v>
       </c>
       <c r="U62" s="3">
         <v>100</v>
       </c>
       <c r="V62" s="3">
+        <v>100</v>
+      </c>
+      <c r="W62" s="3">
         <v>400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>600</v>
       </c>
-      <c r="X62" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Y62" s="3" t="s">
         <v>10</v>
       </c>
@@ -4665,8 +4811,11 @@
       <c r="AB62" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC62" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4745,8 +4894,11 @@
       <c r="AB63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4825,8 +4977,11 @@
       <c r="AB64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4905,74 +5060,77 @@
       <c r="AB65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>38400</v>
+      </c>
+      <c r="E66" s="3">
         <v>45500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>44100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>27000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>25900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>32800</v>
-      </c>
-      <c r="I66" s="3">
-        <v>27100</v>
       </c>
       <c r="J66" s="3">
         <v>27100</v>
       </c>
       <c r="K66" s="3">
+        <v>27100</v>
+      </c>
+      <c r="L66" s="3">
         <v>24100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>31200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>29200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>28500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>29500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>32700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>32400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>33500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>20200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>18700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>20800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>16900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>12600</v>
       </c>
-      <c r="X66" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Y66" s="3" t="s">
         <v>10</v>
       </c>
@@ -4985,8 +5143,11 @@
       <c r="AB66" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC66" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5015,8 +5176,9 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
-    </row>
-    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5095,8 +5257,11 @@
       <c r="AB68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5175,8 +5340,11 @@
       <c r="AB69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5235,14 +5403,14 @@
         <v>0</v>
       </c>
       <c r="V70" s="3">
+        <v>0</v>
+      </c>
+      <c r="W70" s="3">
         <v>160900</v>
       </c>
-      <c r="W70" s="3">
+      <c r="X70" s="3">
         <v>160800</v>
       </c>
-      <c r="X70" s="3">
-        <v>0</v>
-      </c>
       <c r="Y70" s="3">
         <v>0</v>
       </c>
@@ -5255,8 +5423,11 @@
       <c r="AB70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5335,74 +5506,77 @@
       <c r="AB71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-351400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-341800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-333300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-319600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-308800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-297400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-272200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-263100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-251200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-240400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-234500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-233500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-218600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-198200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-179500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-159500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-139300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-127500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-118400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-109100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-106000</v>
       </c>
-      <c r="X72" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Y72" s="3" t="s">
         <v>10</v>
       </c>
@@ -5415,8 +5589,11 @@
       <c r="AB72" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC72" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5495,8 +5672,11 @@
       <c r="AB73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5575,8 +5755,11 @@
       <c r="AB74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5655,74 +5838,77 @@
       <c r="AB75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>123900</v>
+      </c>
+      <c r="E76" s="3">
         <v>128100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>130600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>137900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>142200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>147500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>167300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>170900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>193200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>200300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>201000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>203900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>211800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>223600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>234800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>247800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>260800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>268700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>274000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-98800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-97200</v>
       </c>
-      <c r="X76" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Y76" s="3" t="s">
         <v>10</v>
       </c>
@@ -5735,8 +5921,11 @@
       <c r="AB76" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC76" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5815,173 +6004,182 @@
       <c r="AB77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
     </row>
-    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-9600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-8500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-13700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-10800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-11400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-25200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-9200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-10800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-10600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-5800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-1000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-14900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-20400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-18700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-20100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-20200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-11800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-9100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-9200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-3100</v>
-      </c>
-      <c r="W81" s="3">
-        <v>-3000</v>
       </c>
       <c r="X81" s="3">
         <v>-3000</v>
       </c>
       <c r="Y81" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="Z81" s="3">
         <v>-3200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-5500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-11300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-8200</v>
       </c>
     </row>
-    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6010,61 +6208,62 @@
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
-    </row>
-    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>800</v>
+      </c>
+      <c r="E83" s="3">
         <v>-1100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>900</v>
-      </c>
-      <c r="F83" s="3">
-        <v>1000</v>
       </c>
       <c r="G83" s="3">
         <v>1000</v>
       </c>
       <c r="H83" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I83" s="3">
         <v>-600</v>
-      </c>
-      <c r="I83" s="3">
-        <v>1000</v>
       </c>
       <c r="J83" s="3">
         <v>1000</v>
       </c>
       <c r="K83" s="3">
+        <v>1000</v>
+      </c>
+      <c r="L83" s="3">
         <v>900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>-300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>500</v>
-      </c>
-      <c r="P83" s="3">
-        <v>900</v>
       </c>
       <c r="Q83" s="3">
         <v>900</v>
       </c>
       <c r="R83" s="3">
+        <v>900</v>
+      </c>
+      <c r="S83" s="3">
         <v>700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>500</v>
-      </c>
-      <c r="T83" s="3">
-        <v>400</v>
       </c>
       <c r="U83" s="3">
         <v>400</v>
@@ -6075,23 +6274,26 @@
       <c r="W83" s="3">
         <v>400</v>
       </c>
-      <c r="X83" s="3" t="s">
-        <v>10</v>
+      <c r="X83" s="3">
+        <v>400</v>
       </c>
       <c r="Y83" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="Z83" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA83" s="3">
         <v>800</v>
       </c>
-      <c r="AA83" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AB83" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC83" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6170,8 +6372,11 @@
       <c r="AB84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6250,8 +6455,11 @@
       <c r="AB85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6330,8 +6538,11 @@
       <c r="AB86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6410,8 +6621,11 @@
       <c r="AB87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6490,88 +6704,94 @@
       <c r="AB88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-11700</v>
+      </c>
+      <c r="E89" s="3">
         <v>800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-1000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-4200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-10500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>2100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-2900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-7300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>3200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-6900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-7100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-14800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-9400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-14500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-10800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-11400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-2800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-8600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-5700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-4500</v>
       </c>
-      <c r="X89" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Y89" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="Z89" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA89" s="3">
         <v>-15100</v>
       </c>
-      <c r="AA89" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AB89" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC89" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6600,88 +6820,92 @@
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
-    </row>
-    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-900</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-700</v>
       </c>
       <c r="K91" s="3">
         <v>-700</v>
       </c>
       <c r="L91" s="3">
+        <v>-700</v>
+      </c>
+      <c r="M91" s="3">
         <v>-1300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-800</v>
-      </c>
-      <c r="U91" s="3">
-        <v>-900</v>
       </c>
       <c r="V91" s="3">
         <v>-900</v>
       </c>
       <c r="W91" s="3">
+        <v>-900</v>
+      </c>
+      <c r="X91" s="3">
         <v>-600</v>
       </c>
-      <c r="X91" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Y91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="Z91" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA91" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA91" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AB91" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC91" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6760,8 +6984,11 @@
       <c r="AB92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6840,88 +7067,94 @@
       <c r="AB93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>9600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-9900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>8000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-8600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-7700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-25900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-50800</v>
-      </c>
-      <c r="J94" s="3">
-        <v>-700</v>
       </c>
       <c r="K94" s="3">
         <v>-700</v>
       </c>
       <c r="L94" s="3">
+        <v>-700</v>
+      </c>
+      <c r="M94" s="3">
         <v>-1300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-15100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-2000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-5900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-800</v>
-      </c>
-      <c r="U94" s="3">
-        <v>-900</v>
       </c>
       <c r="V94" s="3">
         <v>-900</v>
       </c>
       <c r="W94" s="3">
+        <v>-900</v>
+      </c>
+      <c r="X94" s="3">
         <v>-600</v>
       </c>
-      <c r="X94" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Y94" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="Z94" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA94" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA94" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AB94" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC94" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6950,8 +7183,9 @@
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
-    </row>
-    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6991,8 +7225,8 @@
       <c r="O96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -7030,8 +7264,11 @@
       <c r="AB96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7110,8 +7347,11 @@
       <c r="AB97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7190,8 +7430,11 @@
       <c r="AB98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7270,88 +7513,94 @@
       <c r="AB99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
         <v>200</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>-100</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-17400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-2900</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>700</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
       <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>1200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>1300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>1600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>221000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>100</v>
       </c>
-      <c r="X100" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Y100" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="Z100" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA100" s="3">
         <v>16900</v>
       </c>
-      <c r="AA100" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AB100" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC100" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7391,8 +7640,8 @@
       <c r="O101" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="P101" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -7430,84 +7679,90 @@
       <c r="AB101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-9100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>7100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-12900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-18200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-23800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-53500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-18700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-10900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-21300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-8700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-15600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-9900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-15100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-10400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-16900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-3000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>211500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-6600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-4900</v>
       </c>
-      <c r="X102" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Y102" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="Z102" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA102" s="3">
         <v>800</v>
       </c>
-      <c r="AA102" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AB102" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC102" s="3" t="s">
         <v>10</v>
       </c>
     </row>
